--- a/Files/Tracker Update.xlsx
+++ b/Files/Tracker Update.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="1053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="1073">
   <si>
     <t>TRACKER</t>
   </si>
@@ -210,7 +210,7 @@
     <t>Semantic Tags</t>
   </si>
   <si>
-    <t>header/footer/section/article/aside give meaningful structure to layout</t>
+    <t xml:space="preserve">header/footer/section/article/aside used to defined tags and helpful for seo </t>
   </si>
   <si>
     <t>HTML Responsive</t>
@@ -354,13 +354,22 @@
     <t>CSS Flex</t>
   </si>
   <si>
-    <t>display:flex makes container flexible, items align via justify-content and align-items</t>
+    <t>display:flex makes container flexible, items align via justify-content and align-items
+flex-wrap- used to decide able to wrap or not in flex
+align-content - work with flex wrap
+order:1 or 2 or 3 -&gt; used to visual order
+flex-grow:1 -&gt; used to how much one item can grow if extra space available
+flex-shrink:0 -&gt; used to how much one item can shrink if space is less
+flex-basis:200px or 25% -&gt; used to set initial width before shrink or grow
+flex: flex-grow flex-shrink flex-basis -&gt; shortand flex: 1 1 200px</t>
   </si>
   <si>
     <t>CSS Grid</t>
   </si>
   <si>
-    <t>display:grid creates a 2D layout using rows and columns</t>
+    <t>display:grid creates a 2D layout using rows and columns
+placed-items: used to center a items
+placed-content: used to center a content</t>
   </si>
   <si>
     <t>Backgrounds</t>
@@ -468,6 +477,9 @@
     <t>Conditional Operators</t>
   </si>
   <si>
+    <t>Ternary operator shortand for if like age &gt;18 ? allowed: not-allowed</t>
+  </si>
+  <si>
     <t>JS Strings</t>
   </si>
   <si>
@@ -657,6 +669,12 @@
     <t>same as localStorage but clears when browser tab is closed</t>
   </si>
   <si>
+    <t>Cookies</t>
+  </si>
+  <si>
+    <t>send to server automaticaly, and have some expiry time duration or it can act as session</t>
+  </si>
+  <si>
     <t>Modules</t>
   </si>
   <si>
@@ -1512,19 +1530,41 @@
     <t>String Methods</t>
   </si>
   <si>
-    <t>length, charAt, concat, at, slice, toUpperCase, toLowerCase, isWellFormed, toWellFormed, trim, trimStart, trimEnd, padStart, padEnd, repeat, replace, replaceAll, split</t>
+    <t>length - lenght of the string 
+charAt() , at() -charat and at same thing but charAT supports -1 values reverse but at not
+concat - concat the string
+slice- return selected text between parameters like slice(0,4)
+toUpperCase, toLowerCase
+charCodeAt() and CodePointAt  - both same return ascii values but additionaliy codepointat supports emojies though
+isWellFormed - check string wellformed or not,
+toWellFormed - try to make string well formed and complicated string view as � like this
+ trim - used to trim, trimStart - trim from start, trimEnd - trim at end, 
+padStart, padEnd - used to add characters untill reaches a certian lenght padStart(padlimit,"padstring"),repeat, replace, replaceAll, split</t>
   </si>
   <si>
     <t>JS Function</t>
   </si>
   <si>
-    <t>declaration, call, apply, bind, closure, IIFE</t>
+    <t>call -&gt; invokes immediately and set value through this mannually one by one arguments
+ apply -&gt; invokes immediately and set value through this and arguments given in array
+, bind -&gt; used to create a new fucntion with this along with permanenly bound into another variable 
+closure -&gt; inner function remembers and access outer function variables even after outer function finished
+IIFE -&gt; Immediately Invoked Function Expression</t>
   </si>
   <si>
     <t>JS Objects</t>
   </si>
   <si>
-    <t>assign, create, keys, values, preventExtension, seal, freeze, isSealed, isFrozen</t>
+    <t>Object.assign({},obj1,obj2) - used to merge to objects, 
+Object.create() - used to create another object with copy of old object and access old object properteis into it new , 
+Object.entries() - for iteration purpose
+Object.keys() - return iteration keys
+Object.values() -&gt; return iteration values, 
+preventExtension - Object.preventExtension(obj1) - can't able to add any properties after this
+Object.seal - can't able to add or delete because of seal, 
+freeze -&gt;Object.freeze() -&gt; same as seal cant delete and add , additionaly can't modify anything
+isSealed-&gt; Object.isSealed(obj1) -&gt; return true or false based sealed or not
+ isFrozen -&gt;Object.isFrozen(Ob1) -&gt;return true or false based frozen or not</t>
   </si>
   <si>
     <t>21</t>
@@ -1542,7 +1582,13 @@
     <t>Array Methods</t>
   </si>
   <si>
-    <t>pop/push add or remove from end, shift/unshift from start, splice modifies in place</t>
+    <t>pop/push add or remove from end, shift/unshift from start 
+toString - convert into string,
+join - merge array through the string parameter withing join
+copyWithIn(0,3) - copy with index and target based
+flat - for flatten the array,
+indexOf, lastIndexOf, slice, include, find,findIndex,findLast,findLastIndex,toSorted,toReversed,sort,reverse
+spilice(start,deletedCount,newArg)</t>
   </si>
   <si>
     <t>for..in</t>
@@ -3275,6 +3321,68 @@
   </si>
   <si>
     <t>Selenium, Cypress, playwrite, appium, jmeter</t>
+  </si>
+  <si>
+    <t>Javascript</t>
+  </si>
+  <si>
+    <t>JS Error Handling</t>
+  </si>
+  <si>
+    <t>Try - actual code block inside here 
+catch - error caught by this catch block which found in try block
+finally - this block runs either error caught or not
+throw - we can throw custom error with info through this throw new Error()</t>
+  </si>
+  <si>
+    <t>Nullish coalescing</t>
+  </si>
+  <si>
+    <t>?? through this left side if undefined or null right side will be print
+let score ;
+console.log(socre ?? "no score"");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arrow function </t>
+  </si>
+  <si>
+    <t xml:space="preserve">easy syntax way to represent normal function </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rest parameter </t>
+  </si>
+  <si>
+    <t>defined in last parameter and act as an array we can dynamically add values</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>key value pairs  and key must be unique and need key for any type</t>
+  </si>
+  <si>
+    <t>Set</t>
+  </si>
+  <si>
+    <t>Values only , need unique values, used to remove duplicates  in array</t>
+  </si>
+  <si>
+    <t>Map features</t>
+  </si>
+  <si>
+    <t>map.set -&gt; set values key value pairs 
+map.get -&gt; get values through keys
+map.has -&gt; check the specified key exists
+map.size -&gt; lenght of the map
+map.delete-&gt; delete through keys
+map.clear-&gt; delete overall ap values
+map.foreach(value, key) -&gt; for iteration</t>
+  </si>
+  <si>
+    <t>set features</t>
+  </si>
+  <si>
+    <t>set.add(), set.has(), set.size(), set.delete(), set.clear(), set.foreach()</t>
   </si>
 </sst>
 </file>
@@ -3380,7 +3488,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -3869,6 +3977,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -3911,6 +4028,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB0BDD8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -3921,13 +4047,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB0BDD8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="98">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -4150,10 +4285,10 @@
     <xf borderId="34" fillId="3" fontId="8" numFmtId="164" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="6" fontId="9" numFmtId="0" xfId="0">
+    <xf borderId="39" fillId="6" fontId="9" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="39" fillId="4" fontId="7" numFmtId="0" xfId="0">
+    <xf borderId="40" fillId="4" fontId="7" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="22" fillId="4" fontId="7" numFmtId="0" xfId="0">
@@ -4162,8 +4297,8 @@
     <xf borderId="36" fillId="4" fontId="7" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="21" fillId="0" fontId="10" numFmtId="0" xfId="0">
-      <alignment vertical="bottom"/>
+    <xf borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="21" fillId="4" fontId="7" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4180,19 +4315,16 @@
     <xf borderId="34" fillId="4" fontId="7" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="40" fillId="0" fontId="10" numFmtId="0" xfId="0">
+    <xf borderId="41" fillId="0" fontId="10" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="10" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf borderId="30" fillId="0" fontId="10" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="41" fillId="0" fontId="10" numFmtId="0" xfId="0">
+    <xf borderId="42" fillId="0" fontId="10" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="42" fillId="4" fontId="7" numFmtId="0" xfId="0">
+    <xf borderId="43" fillId="4" fontId="7" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="21" fillId="4" fontId="7" numFmtId="0" xfId="0">
@@ -4204,8 +4336,26 @@
     <xf borderId="29" fillId="0" fontId="10" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="43" fillId="4" fontId="7" numFmtId="0" xfId="0">
+    <xf borderId="44" fillId="6" fontId="9" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="45" fillId="4" fontId="7" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="37" fillId="4" fontId="7" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="46" fillId="0" fontId="10" numFmtId="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="37" fillId="4" fontId="7" numFmtId="164" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="35" fillId="0" fontId="10" numFmtId="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="10" numFmtId="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4226,7 +4376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-  <dimension ref="A1:F483"/>
+  <dimension ref="A1:F492"/>
   <sheetFormatPr defaultRowHeight="15.0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.03"/>
@@ -4852,7 +5002,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" customHeight="1" ht="15.0">
+    <row r="49" customHeight="1" ht="16.0">
       <c r="A49" s="11"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -4864,7 +5014,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" customHeight="1" ht="15.0">
+    <row r="50" customHeight="1" ht="108.0">
       <c r="A50" s="11"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -4876,7 +5026,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" customHeight="1" ht="15.0">
+    <row r="51" customHeight="1" ht="48.0">
       <c r="A51" s="11"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -4936,7 +5086,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" customHeight="1" ht="15.0">
+    <row r="56" customHeight="1" ht="23.0">
       <c r="A56" s="11"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
@@ -4948,7 +5098,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" customHeight="1" ht="15.0">
+    <row r="57" customHeight="1" ht="24.0">
       <c r="A57" s="15"/>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -5092,7 +5242,9 @@
       <c r="E67" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="F67" s="26"/>
+      <c r="F67" s="26" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="68" customHeight="1" ht="15.0">
       <c r="A68" s="11"/>
@@ -5100,10 +5252,10 @@
       <c r="C68" s="12"/>
       <c r="D68" s="12"/>
       <c r="E68" s="25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" customHeight="1" ht="15.0">
@@ -5112,10 +5264,10 @@
       <c r="C69" s="12"/>
       <c r="D69" s="12"/>
       <c r="E69" s="25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="70" customHeight="1" ht="15.0">
@@ -5124,30 +5276,30 @@
       <c r="C70" s="16"/>
       <c r="D70" s="16"/>
       <c r="E70" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F70" s="28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="71" customHeight="1" ht="15.0">
       <c r="A71" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>137</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="72" customHeight="1" ht="15.0">
@@ -5156,10 +5308,10 @@
       <c r="C72" s="12"/>
       <c r="D72" s="12"/>
       <c r="E72" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73" customHeight="1" ht="15.0">
@@ -5171,7 +5323,7 @@
         <v>141</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" customHeight="1" ht="15.0">
@@ -5180,10 +5332,10 @@
       <c r="C74" s="12"/>
       <c r="D74" s="12"/>
       <c r="E74" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75" customHeight="1" ht="15.0">
@@ -5192,10 +5344,10 @@
       <c r="C75" s="12"/>
       <c r="D75" s="12"/>
       <c r="E75" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="76" customHeight="1" ht="15.0">
@@ -5204,10 +5356,10 @@
       <c r="C76" s="12"/>
       <c r="D76" s="12"/>
       <c r="E76" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" customHeight="1" ht="15.0">
@@ -5216,10 +5368,10 @@
       <c r="C77" s="12"/>
       <c r="D77" s="12"/>
       <c r="E77" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" customHeight="1" ht="15.0">
@@ -5228,10 +5380,10 @@
       <c r="C78" s="12"/>
       <c r="D78" s="12"/>
       <c r="E78" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" customHeight="1" ht="15.0">
@@ -5240,10 +5392,10 @@
       <c r="C79" s="12"/>
       <c r="D79" s="12"/>
       <c r="E79" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="80" customHeight="1" ht="15.0">
@@ -5252,10 +5404,10 @@
       <c r="C80" s="12"/>
       <c r="D80" s="12"/>
       <c r="E80" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="81" customHeight="1" ht="15.0">
@@ -5264,10 +5416,10 @@
       <c r="C81" s="12"/>
       <c r="D81" s="12"/>
       <c r="E81" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="82" customHeight="1" ht="15.0">
@@ -5276,30 +5428,30 @@
       <c r="C82" s="16"/>
       <c r="D82" s="16"/>
       <c r="E82" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F82" s="18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="83" customHeight="1" ht="15.0">
       <c r="A83" s="19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C83" s="21" t="s">
         <v>137</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" customHeight="1" ht="15.0">
@@ -5308,10 +5460,10 @@
       <c r="C84" s="12"/>
       <c r="D84" s="12"/>
       <c r="E84" s="25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" customHeight="1" ht="15.0">
@@ -5320,10 +5472,10 @@
       <c r="C85" s="12"/>
       <c r="D85" s="12"/>
       <c r="E85" s="25" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" customHeight="1" ht="15.0">
@@ -5332,10 +5484,10 @@
       <c r="C86" s="12"/>
       <c r="D86" s="12"/>
       <c r="E86" s="25" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" customHeight="1" ht="15.0">
@@ -5344,10 +5496,10 @@
       <c r="C87" s="12"/>
       <c r="D87" s="12"/>
       <c r="E87" s="25" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F87" s="26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88" customHeight="1" ht="15.0">
@@ -5356,10 +5508,10 @@
       <c r="C88" s="12"/>
       <c r="D88" s="12"/>
       <c r="E88" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="89" customHeight="1" ht="15.0">
@@ -5368,10 +5520,10 @@
       <c r="C89" s="12"/>
       <c r="D89" s="12"/>
       <c r="E89" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="90" customHeight="1" ht="15.0">
@@ -5380,10 +5532,10 @@
       <c r="C90" s="12"/>
       <c r="D90" s="12"/>
       <c r="E90" s="25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="91" customHeight="1" ht="15.0">
@@ -5392,10 +5544,10 @@
       <c r="C91" s="12"/>
       <c r="D91" s="12"/>
       <c r="E91" s="25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" customHeight="1" ht="15.0">
@@ -5404,10 +5556,10 @@
       <c r="C92" s="12"/>
       <c r="D92" s="12"/>
       <c r="E92" s="25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="93" customHeight="1" ht="15.0">
@@ -5416,10 +5568,10 @@
       <c r="C93" s="12"/>
       <c r="D93" s="12"/>
       <c r="E93" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F93" s="26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="94" customHeight="1" ht="15.0">
@@ -5428,10 +5580,10 @@
       <c r="C94" s="12"/>
       <c r="D94" s="12"/>
       <c r="E94" s="25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="95" customHeight="1" ht="15.0">
@@ -5440,10 +5592,10 @@
       <c r="C95" s="12"/>
       <c r="D95" s="12"/>
       <c r="E95" s="25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" customHeight="1" ht="15.0">
@@ -5452,10 +5604,10 @@
       <c r="C96" s="12"/>
       <c r="D96" s="12"/>
       <c r="E96" s="25" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F96" s="26" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" customHeight="1" ht="15.0">
@@ -5464,10 +5616,10 @@
       <c r="C97" s="12"/>
       <c r="D97" s="12"/>
       <c r="E97" s="25" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="98" customHeight="1" ht="15.0">
@@ -5476,10 +5628,10 @@
       <c r="C98" s="12"/>
       <c r="D98" s="12"/>
       <c r="E98" s="25" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="99" customHeight="1" ht="15.0">
@@ -5488,10 +5640,10 @@
       <c r="C99" s="12"/>
       <c r="D99" s="12"/>
       <c r="E99" s="25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="100" customHeight="1" ht="15.0">
@@ -5500,10 +5652,10 @@
       <c r="C100" s="12"/>
       <c r="D100" s="12"/>
       <c r="E100" s="25" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="101" customHeight="1" ht="15.0">
@@ -5512,10 +5664,10 @@
       <c r="C101" s="12"/>
       <c r="D101" s="12"/>
       <c r="E101" s="25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="102" customHeight="1" ht="15.0">
@@ -5524,10 +5676,10 @@
       <c r="C102" s="12"/>
       <c r="D102" s="12"/>
       <c r="E102" s="25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="103" customHeight="1" ht="15.0">
@@ -5536,10 +5688,10 @@
       <c r="C103" s="12"/>
       <c r="D103" s="12"/>
       <c r="E103" s="25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="104" customHeight="1" ht="15.0">
@@ -5548,10 +5700,10 @@
       <c r="C104" s="12"/>
       <c r="D104" s="12"/>
       <c r="E104" s="25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" customHeight="1" ht="15.0">
@@ -5560,10 +5712,10 @@
       <c r="C105" s="12"/>
       <c r="D105" s="12"/>
       <c r="E105" s="25" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="106" customHeight="1" ht="15.0">
@@ -5572,10 +5724,10 @@
       <c r="C106" s="12"/>
       <c r="D106" s="12"/>
       <c r="E106" s="25" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="107" customHeight="1" ht="15.0">
@@ -5584,10 +5736,10 @@
       <c r="C107" s="12"/>
       <c r="D107" s="12"/>
       <c r="E107" s="25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="108" customHeight="1" ht="15.0">
@@ -5596,10 +5748,10 @@
       <c r="C108" s="12"/>
       <c r="D108" s="12"/>
       <c r="E108" s="25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="109" customHeight="1" ht="15.0">
@@ -5608,10 +5760,10 @@
       <c r="C109" s="12"/>
       <c r="D109" s="12"/>
       <c r="E109" s="25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="110" customHeight="1" ht="15.0">
@@ -5620,54 +5772,54 @@
       <c r="C110" s="12"/>
       <c r="D110" s="12"/>
       <c r="E110" s="25" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="111" customHeight="1" ht="15.0">
-      <c r="A111" s="15"/>
-      <c r="B111" s="16"/>
-      <c r="C111" s="16"/>
-      <c r="D111" s="16"/>
-      <c r="E111" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="F111" s="28" t="s">
+      <c r="A111" s="11"/>
+      <c r="B111" s="12"/>
+      <c r="C111" s="12"/>
+      <c r="D111" s="12"/>
+      <c r="E111" s="25" t="s">
         <v>240</v>
       </c>
+      <c r="F111" s="26" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="112" customHeight="1" ht="15.0">
-      <c r="A112" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B112" s="6" t="s">
+      <c r="A112" s="15"/>
+      <c r="B112" s="16"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="F112" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="D112" s="8" t="s">
+    </row>
+    <row r="113" customHeight="1" ht="15.0">
+      <c r="A113" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="E112" s="9" t="s">
+      <c r="B113" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F112" s="10" t="s">
+      <c r="C113" s="7" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="113" customHeight="1" ht="15.0">
-      <c r="A113" s="11"/>
-      <c r="B113" s="12"/>
-      <c r="C113" s="12"/>
-      <c r="D113" s="12"/>
-      <c r="E113" s="13" t="s">
+      <c r="D113" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="F113" s="14" t="s">
+      <c r="E113" s="9" t="s">
         <v>248</v>
+      </c>
+      <c r="F113" s="10" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="114" customHeight="1" ht="15.0">
@@ -5676,10 +5828,10 @@
       <c r="C114" s="12"/>
       <c r="D114" s="12"/>
       <c r="E114" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="115" customHeight="1" ht="15.0">
@@ -5688,10 +5840,10 @@
       <c r="C115" s="12"/>
       <c r="D115" s="12"/>
       <c r="E115" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F115" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="116" customHeight="1" ht="15.0">
@@ -5700,10 +5852,10 @@
       <c r="C116" s="12"/>
       <c r="D116" s="12"/>
       <c r="E116" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="117" customHeight="1" ht="15.0">
@@ -5712,10 +5864,10 @@
       <c r="C117" s="12"/>
       <c r="D117" s="12"/>
       <c r="E117" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F117" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="118" customHeight="1" ht="15.0">
@@ -5724,10 +5876,10 @@
       <c r="C118" s="12"/>
       <c r="D118" s="12"/>
       <c r="E118" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F118" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="119" customHeight="1" ht="15.0">
@@ -5736,10 +5888,10 @@
       <c r="C119" s="12"/>
       <c r="D119" s="12"/>
       <c r="E119" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F119" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="120" customHeight="1" ht="15.0">
@@ -5748,10 +5900,10 @@
       <c r="C120" s="12"/>
       <c r="D120" s="12"/>
       <c r="E120" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F120" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="121" customHeight="1" ht="15.0">
@@ -5760,10 +5912,10 @@
       <c r="C121" s="12"/>
       <c r="D121" s="12"/>
       <c r="E121" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F121" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="122" customHeight="1" ht="15.0">
@@ -5772,10 +5924,10 @@
       <c r="C122" s="12"/>
       <c r="D122" s="12"/>
       <c r="E122" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F122" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="123" customHeight="1" ht="15.0">
@@ -5784,74 +5936,74 @@
       <c r="C123" s="12"/>
       <c r="D123" s="12"/>
       <c r="E123" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F123" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124" customHeight="1" ht="15.0">
-      <c r="A124" s="15"/>
-      <c r="B124" s="16"/>
-      <c r="C124" s="16"/>
-      <c r="D124" s="16"/>
-      <c r="E124" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="F124" s="18" t="s">
+      <c r="A124" s="11"/>
+      <c r="B124" s="12"/>
+      <c r="C124" s="12"/>
+      <c r="D124" s="12"/>
+      <c r="E124" s="13" t="s">
         <v>270</v>
       </c>
+      <c r="F124" s="14" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="125" customHeight="1" ht="15.0">
-      <c r="A125" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="B125" s="30" t="s">
+      <c r="A125" s="15"/>
+      <c r="B125" s="16"/>
+      <c r="C125" s="16"/>
+      <c r="D125" s="16"/>
+      <c r="E125" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="C125" s="31" t="s">
+      <c r="F125" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="D125" s="32" t="s">
+    </row>
+    <row r="126" customHeight="1" ht="15.0">
+      <c r="A126" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="E125" s="33" t="s">
+      <c r="B126" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="F125" s="34" t="s">
+      <c r="C126" s="31" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="126" customHeight="1" ht="15.0">
-      <c r="A126" s="5" t="s">
+      <c r="D126" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="B126" s="6" t="s">
+      <c r="E126" s="33" t="s">
         <v>278</v>
       </c>
-      <c r="C126" s="7" t="s">
+      <c r="F126" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="D126" s="8" t="s">
+    </row>
+    <row r="127" customHeight="1" ht="15.0">
+      <c r="A127" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="E126" s="9" t="s">
+      <c r="B127" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="F126" s="10" t="s">
+      <c r="C127" s="7" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="127" customHeight="1" ht="15.0">
-      <c r="A127" s="11"/>
-      <c r="B127" s="12"/>
-      <c r="C127" s="12"/>
-      <c r="D127" s="12"/>
-      <c r="E127" s="13" t="s">
+      <c r="D127" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="F127" s="14" t="s">
+      <c r="E127" s="9" t="s">
         <v>284</v>
+      </c>
+      <c r="F127" s="10" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="128" customHeight="1" ht="15.0">
@@ -5860,98 +6012,98 @@
       <c r="C128" s="12"/>
       <c r="D128" s="12"/>
       <c r="E128" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F128" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="129" customHeight="1" ht="15.0">
-      <c r="A129" s="15"/>
-      <c r="B129" s="16"/>
-      <c r="C129" s="16"/>
-      <c r="D129" s="16"/>
-      <c r="E129" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="F129" s="18" t="s">
+      <c r="A129" s="11"/>
+      <c r="B129" s="12"/>
+      <c r="C129" s="12"/>
+      <c r="D129" s="12"/>
+      <c r="E129" s="13" t="s">
         <v>288</v>
       </c>
+      <c r="F129" s="14" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="130" customHeight="1" ht="15.0">
-      <c r="A130" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="B130" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="C130" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="D130" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="E130" s="23" t="s">
+      <c r="A130" s="15"/>
+      <c r="B130" s="16"/>
+      <c r="C130" s="16"/>
+      <c r="D130" s="16"/>
+      <c r="E130" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="F130" s="24" t="s">
+      <c r="F130" s="18" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="131" customHeight="1" ht="15.0">
-      <c r="A131" s="11"/>
-      <c r="B131" s="12"/>
-      <c r="C131" s="12"/>
-      <c r="D131" s="12"/>
-      <c r="E131" s="25" t="s">
+      <c r="A131" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="F131" s="26" t="s">
+      <c r="B131" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="C131" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="D131" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E131" s="23" t="s">
         <v>293</v>
       </c>
+      <c r="F131" s="24" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="132" customHeight="1" ht="15.0">
-      <c r="A132" s="15"/>
-      <c r="B132" s="16"/>
-      <c r="C132" s="16"/>
-      <c r="D132" s="16"/>
-      <c r="E132" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="F132" s="28" t="s">
+      <c r="A132" s="11"/>
+      <c r="B132" s="12"/>
+      <c r="C132" s="12"/>
+      <c r="D132" s="12"/>
+      <c r="E132" s="25" t="s">
         <v>295</v>
       </c>
+      <c r="F132" s="26" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="133" customHeight="1" ht="15.0">
-      <c r="A133" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D133" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="E133" s="9" t="s">
+      <c r="A133" s="15"/>
+      <c r="B133" s="16"/>
+      <c r="C133" s="16"/>
+      <c r="D133" s="16"/>
+      <c r="E133" s="27" t="s">
         <v>297</v>
       </c>
-      <c r="F133" s="10" t="s">
+      <c r="F133" s="28" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="134" customHeight="1" ht="15.0">
-      <c r="A134" s="11"/>
-      <c r="B134" s="12"/>
-      <c r="C134" s="12"/>
-      <c r="D134" s="12"/>
-      <c r="E134" s="13" t="s">
+      <c r="A134" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="F134" s="14" t="s">
+      <c r="B134" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="E134" s="9" t="s">
         <v>300</v>
+      </c>
+      <c r="F134" s="10" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="135" customHeight="1" ht="15.0">
@@ -5960,10 +6112,10 @@
       <c r="C135" s="12"/>
       <c r="D135" s="12"/>
       <c r="E135" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F135" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="136" customHeight="1" ht="15.0">
@@ -5972,10 +6124,10 @@
       <c r="C136" s="12"/>
       <c r="D136" s="12"/>
       <c r="E136" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F136" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="137" customHeight="1" ht="15.0">
@@ -5984,10 +6136,10 @@
       <c r="C137" s="12"/>
       <c r="D137" s="12"/>
       <c r="E137" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F137" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="138" customHeight="1" ht="15.0">
@@ -5996,10 +6148,10 @@
       <c r="C138" s="12"/>
       <c r="D138" s="12"/>
       <c r="E138" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F138" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="139" customHeight="1" ht="15.0">
@@ -6008,54 +6160,54 @@
       <c r="C139" s="12"/>
       <c r="D139" s="12"/>
       <c r="E139" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F139" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="140" customHeight="1" ht="15.0">
-      <c r="A140" s="15"/>
-      <c r="B140" s="16"/>
-      <c r="C140" s="16"/>
-      <c r="D140" s="16"/>
-      <c r="E140" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="F140" s="18" t="s">
+      <c r="A140" s="11"/>
+      <c r="B140" s="12"/>
+      <c r="C140" s="12"/>
+      <c r="D140" s="12"/>
+      <c r="E140" s="13" t="s">
         <v>312</v>
       </c>
+      <c r="F140" s="14" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="141" customHeight="1" ht="15.0">
-      <c r="A141" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="B141" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="C141" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="D141" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="E141" s="23" t="s">
+      <c r="A141" s="15"/>
+      <c r="B141" s="16"/>
+      <c r="C141" s="16"/>
+      <c r="D141" s="16"/>
+      <c r="E141" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="F141" s="24" t="s">
+      <c r="F141" s="18" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="142" customHeight="1" ht="15.0">
-      <c r="A142" s="11"/>
-      <c r="B142" s="12"/>
-      <c r="C142" s="12"/>
-      <c r="D142" s="12"/>
-      <c r="E142" s="25" t="s">
+      <c r="A142" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="F142" s="26" t="s">
+      <c r="B142" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="C142" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="D142" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E142" s="23" t="s">
         <v>317</v>
+      </c>
+      <c r="F142" s="24" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="143" customHeight="1" ht="15.0">
@@ -6064,10 +6216,10 @@
       <c r="C143" s="12"/>
       <c r="D143" s="12"/>
       <c r="E143" s="25" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="144" customHeight="1" ht="15.0">
@@ -6076,10 +6228,10 @@
       <c r="C144" s="12"/>
       <c r="D144" s="12"/>
       <c r="E144" s="25" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F144" s="26" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="145" customHeight="1" ht="15.0">
@@ -6088,10 +6240,10 @@
       <c r="C145" s="12"/>
       <c r="D145" s="12"/>
       <c r="E145" s="25" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F145" s="26" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="146" customHeight="1" ht="15.0">
@@ -6100,54 +6252,54 @@
       <c r="C146" s="12"/>
       <c r="D146" s="12"/>
       <c r="E146" s="25" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="147" customHeight="1" ht="15.0">
-      <c r="A147" s="15"/>
-      <c r="B147" s="16"/>
-      <c r="C147" s="16"/>
-      <c r="D147" s="16"/>
-      <c r="E147" s="27" t="s">
-        <v>326</v>
-      </c>
-      <c r="F147" s="28" t="s">
+      <c r="A147" s="11"/>
+      <c r="B147" s="12"/>
+      <c r="C147" s="12"/>
+      <c r="D147" s="12"/>
+      <c r="E147" s="25" t="s">
         <v>327</v>
       </c>
+      <c r="F147" s="26" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="148" customHeight="1" ht="15.0">
-      <c r="A148" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="B148" s="6" t="s">
+      <c r="A148" s="15"/>
+      <c r="B148" s="16"/>
+      <c r="C148" s="16"/>
+      <c r="D148" s="16"/>
+      <c r="E148" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="C148" s="7" t="s">
+      <c r="F148" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="D148" s="8" t="s">
+    </row>
+    <row r="149" customHeight="1" ht="15.0">
+      <c r="A149" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="E148" s="9" t="s">
+      <c r="B149" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="F148" s="10" t="s">
+      <c r="C149" s="7" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="149" customHeight="1" ht="15.0">
-      <c r="A149" s="11"/>
-      <c r="B149" s="12"/>
-      <c r="C149" s="12"/>
-      <c r="D149" s="12"/>
-      <c r="E149" s="13" t="s">
+      <c r="D149" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="F149" s="14" t="s">
+      <c r="E149" s="9" t="s">
         <v>335</v>
+      </c>
+      <c r="F149" s="10" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="150" customHeight="1" ht="15.0">
@@ -6156,10 +6308,10 @@
       <c r="C150" s="12"/>
       <c r="D150" s="12"/>
       <c r="E150" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F150" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="151" customHeight="1" ht="15.0">
@@ -6168,10 +6320,10 @@
       <c r="C151" s="12"/>
       <c r="D151" s="12"/>
       <c r="E151" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F151" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="152" customHeight="1" ht="15.0">
@@ -6180,54 +6332,54 @@
       <c r="C152" s="12"/>
       <c r="D152" s="12"/>
       <c r="E152" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F152" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="153" customHeight="1" ht="15.0">
-      <c r="A153" s="15"/>
-      <c r="B153" s="16"/>
-      <c r="C153" s="16"/>
-      <c r="D153" s="16"/>
-      <c r="E153" s="17" t="s">
-        <v>342</v>
-      </c>
-      <c r="F153" s="18" t="s">
+      <c r="A153" s="11"/>
+      <c r="B153" s="12"/>
+      <c r="C153" s="12"/>
+      <c r="D153" s="12"/>
+      <c r="E153" s="13" t="s">
         <v>343</v>
       </c>
+      <c r="F153" s="14" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="154" customHeight="1" ht="15.0">
-      <c r="A154" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="B154" s="20" t="s">
+      <c r="A154" s="15"/>
+      <c r="B154" s="16"/>
+      <c r="C154" s="16"/>
+      <c r="D154" s="16"/>
+      <c r="E154" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="C154" s="21" t="s">
+      <c r="F154" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="D154" s="22" t="s">
+    </row>
+    <row r="155" customHeight="1" ht="15.0">
+      <c r="A155" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="E154" s="23" t="s">
+      <c r="B155" s="20" t="s">
         <v>348</v>
       </c>
-      <c r="F154" s="24" t="s">
+      <c r="C155" s="21" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="155" customHeight="1" ht="15.0">
-      <c r="A155" s="11"/>
-      <c r="B155" s="12"/>
-      <c r="C155" s="12"/>
-      <c r="D155" s="12"/>
-      <c r="E155" s="25" t="s">
+      <c r="D155" s="22" t="s">
         <v>350</v>
       </c>
-      <c r="F155" s="26" t="s">
+      <c r="E155" s="23" t="s">
         <v>351</v>
+      </c>
+      <c r="F155" s="24" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="156" customHeight="1" ht="15.0">
@@ -6236,10 +6388,10 @@
       <c r="C156" s="12"/>
       <c r="D156" s="12"/>
       <c r="E156" s="25" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F156" s="26" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="157" customHeight="1" ht="15.0">
@@ -6248,10 +6400,10 @@
       <c r="C157" s="12"/>
       <c r="D157" s="12"/>
       <c r="E157" s="25" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F157" s="26" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="158" customHeight="1" ht="15.0">
@@ -6260,10 +6412,10 @@
       <c r="C158" s="12"/>
       <c r="D158" s="12"/>
       <c r="E158" s="25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F158" s="26" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="159" customHeight="1" ht="15.0">
@@ -6272,10 +6424,10 @@
       <c r="C159" s="12"/>
       <c r="D159" s="12"/>
       <c r="E159" s="25" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F159" s="26" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="160" customHeight="1" ht="15.0">
@@ -6284,10 +6436,10 @@
       <c r="C160" s="12"/>
       <c r="D160" s="12"/>
       <c r="E160" s="25" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F160" s="26" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="161" customHeight="1" ht="15.0">
@@ -6296,10 +6448,10 @@
       <c r="C161" s="12"/>
       <c r="D161" s="12"/>
       <c r="E161" s="25" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F161" s="26" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="162" customHeight="1" ht="15.0">
@@ -6308,10 +6460,10 @@
       <c r="C162" s="12"/>
       <c r="D162" s="12"/>
       <c r="E162" s="25" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F162" s="26" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="163" customHeight="1" ht="15.0">
@@ -6320,10 +6472,10 @@
       <c r="C163" s="12"/>
       <c r="D163" s="12"/>
       <c r="E163" s="25" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F163" s="26" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="164" customHeight="1" ht="15.0">
@@ -6332,10 +6484,10 @@
       <c r="C164" s="12"/>
       <c r="D164" s="12"/>
       <c r="E164" s="25" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F164" s="26" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="165" customHeight="1" ht="15.0">
@@ -6344,10 +6496,10 @@
       <c r="C165" s="12"/>
       <c r="D165" s="12"/>
       <c r="E165" s="25" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F165" s="26" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="166" customHeight="1" ht="15.0">
@@ -6356,54 +6508,54 @@
       <c r="C166" s="12"/>
       <c r="D166" s="12"/>
       <c r="E166" s="25" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F166" s="26" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="167" customHeight="1" ht="15.0">
-      <c r="A167" s="15"/>
-      <c r="B167" s="16"/>
-      <c r="C167" s="16"/>
-      <c r="D167" s="16"/>
-      <c r="E167" s="27" t="s">
-        <v>374</v>
-      </c>
-      <c r="F167" s="28" t="s">
+      <c r="A167" s="11"/>
+      <c r="B167" s="12"/>
+      <c r="C167" s="12"/>
+      <c r="D167" s="12"/>
+      <c r="E167" s="25" t="s">
         <v>375</v>
       </c>
+      <c r="F167" s="26" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="168" customHeight="1" ht="15.0">
-      <c r="A168" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="B168" s="6" t="s">
+      <c r="A168" s="15"/>
+      <c r="B168" s="16"/>
+      <c r="C168" s="16"/>
+      <c r="D168" s="16"/>
+      <c r="E168" s="27" t="s">
         <v>377</v>
       </c>
-      <c r="C168" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D168" s="8" t="s">
+      <c r="F168" s="28" t="s">
         <v>378</v>
       </c>
-      <c r="E168" s="9" t="s">
+    </row>
+    <row r="169" customHeight="1" ht="15.0">
+      <c r="A169" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="F168" s="10" t="s">
+      <c r="B169" s="6" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="169" customHeight="1" ht="15.0">
-      <c r="A169" s="11"/>
-      <c r="B169" s="12"/>
-      <c r="C169" s="12"/>
-      <c r="D169" s="12"/>
-      <c r="E169" s="13" t="s">
+      <c r="C169" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D169" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="F169" s="14" t="s">
+      <c r="E169" s="9" t="s">
         <v>382</v>
+      </c>
+      <c r="F169" s="10" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="170" customHeight="1" ht="15.0">
@@ -6412,10 +6564,10 @@
       <c r="C170" s="12"/>
       <c r="D170" s="12"/>
       <c r="E170" s="13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F170" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="171" customHeight="1" ht="15.0">
@@ -6424,10 +6576,10 @@
       <c r="C171" s="12"/>
       <c r="D171" s="12"/>
       <c r="E171" s="13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F171" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="172" customHeight="1" ht="15.0">
@@ -6436,54 +6588,54 @@
       <c r="C172" s="12"/>
       <c r="D172" s="12"/>
       <c r="E172" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F172" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="173" customHeight="1" ht="15.0">
-      <c r="A173" s="15"/>
-      <c r="B173" s="16"/>
-      <c r="C173" s="16"/>
-      <c r="D173" s="16"/>
-      <c r="E173" s="17" t="s">
-        <v>389</v>
-      </c>
-      <c r="F173" s="18" t="s">
+      <c r="A173" s="11"/>
+      <c r="B173" s="12"/>
+      <c r="C173" s="12"/>
+      <c r="D173" s="12"/>
+      <c r="E173" s="13" t="s">
         <v>390</v>
       </c>
+      <c r="F173" s="14" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="174" customHeight="1" ht="15.0">
-      <c r="A174" s="19" t="s">
-        <v>391</v>
-      </c>
-      <c r="B174" s="20" t="s">
+      <c r="A174" s="15"/>
+      <c r="B174" s="16"/>
+      <c r="C174" s="16"/>
+      <c r="D174" s="16"/>
+      <c r="E174" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="C174" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="D174" s="22" t="s">
+      <c r="F174" s="18" t="s">
         <v>393</v>
       </c>
-      <c r="E174" s="23" t="s">
+    </row>
+    <row r="175" customHeight="1" ht="15.0">
+      <c r="A175" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="F174" s="24" t="s">
+      <c r="B175" s="20" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="175" customHeight="1" ht="15.0">
-      <c r="A175" s="11"/>
-      <c r="B175" s="12"/>
-      <c r="C175" s="12"/>
-      <c r="D175" s="12"/>
-      <c r="E175" s="25" t="s">
+      <c r="C175" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="D175" s="22" t="s">
         <v>396</v>
       </c>
-      <c r="F175" s="26" t="s">
+      <c r="E175" s="23" t="s">
         <v>397</v>
+      </c>
+      <c r="F175" s="24" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="176" customHeight="1" ht="15.0">
@@ -6492,10 +6644,10 @@
       <c r="C176" s="12"/>
       <c r="D176" s="12"/>
       <c r="E176" s="25" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F176" s="26" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="177" customHeight="1" ht="15.0">
@@ -6504,10 +6656,10 @@
       <c r="C177" s="12"/>
       <c r="D177" s="12"/>
       <c r="E177" s="25" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F177" s="26" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="178" customHeight="1" ht="15.0">
@@ -6516,10 +6668,10 @@
       <c r="C178" s="12"/>
       <c r="D178" s="12"/>
       <c r="E178" s="25" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F178" s="26" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="179" customHeight="1" ht="15.0">
@@ -6528,10 +6680,10 @@
       <c r="C179" s="12"/>
       <c r="D179" s="12"/>
       <c r="E179" s="25" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F179" s="26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="180" customHeight="1" ht="15.0">
@@ -6540,10 +6692,10 @@
       <c r="C180" s="12"/>
       <c r="D180" s="12"/>
       <c r="E180" s="25" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F180" s="26" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="181" customHeight="1" ht="15.0">
@@ -6552,10 +6704,10 @@
       <c r="C181" s="12"/>
       <c r="D181" s="12"/>
       <c r="E181" s="25" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F181" s="26" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="182" customHeight="1" ht="15.0">
@@ -6564,10 +6716,10 @@
       <c r="C182" s="12"/>
       <c r="D182" s="12"/>
       <c r="E182" s="25" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F182" s="26" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="183" customHeight="1" ht="15.0">
@@ -6576,10 +6728,10 @@
       <c r="C183" s="12"/>
       <c r="D183" s="12"/>
       <c r="E183" s="25" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F183" s="26" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="184" customHeight="1" ht="15.0">
@@ -6588,10 +6740,10 @@
       <c r="C184" s="12"/>
       <c r="D184" s="12"/>
       <c r="E184" s="25" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F184" s="26" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="185" customHeight="1" ht="15.0">
@@ -6600,10 +6752,10 @@
       <c r="C185" s="12"/>
       <c r="D185" s="12"/>
       <c r="E185" s="25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F185" s="26" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="186" customHeight="1" ht="15.0">
@@ -6612,54 +6764,54 @@
       <c r="C186" s="12"/>
       <c r="D186" s="12"/>
       <c r="E186" s="25" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F186" s="26" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="187" customHeight="1" ht="15.0">
-      <c r="A187" s="15"/>
-      <c r="B187" s="16"/>
-      <c r="C187" s="16"/>
-      <c r="D187" s="16"/>
-      <c r="E187" s="27" t="s">
-        <v>420</v>
-      </c>
-      <c r="F187" s="28" t="s">
+      <c r="A187" s="11"/>
+      <c r="B187" s="12"/>
+      <c r="C187" s="12"/>
+      <c r="D187" s="12"/>
+      <c r="E187" s="25" t="s">
         <v>421</v>
       </c>
+      <c r="F187" s="26" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="188" customHeight="1" ht="15.0">
-      <c r="A188" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="B188" s="6" t="s">
+      <c r="A188" s="15"/>
+      <c r="B188" s="16"/>
+      <c r="C188" s="16"/>
+      <c r="D188" s="16"/>
+      <c r="E188" s="27" t="s">
         <v>423</v>
       </c>
-      <c r="C188" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D188" s="8" t="s">
+      <c r="F188" s="28" t="s">
         <v>424</v>
       </c>
-      <c r="E188" s="9" t="s">
+    </row>
+    <row r="189" customHeight="1" ht="15.0">
+      <c r="A189" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="F188" s="10" t="s">
+      <c r="B189" s="6" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="189" customHeight="1" ht="15.0">
-      <c r="A189" s="11"/>
-      <c r="B189" s="12"/>
-      <c r="C189" s="12"/>
-      <c r="D189" s="12"/>
-      <c r="E189" s="13" t="s">
+      <c r="C189" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D189" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="F189" s="14" t="s">
+      <c r="E189" s="9" t="s">
         <v>428</v>
+      </c>
+      <c r="F189" s="10" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="190" customHeight="1" ht="15.0">
@@ -6668,10 +6820,10 @@
       <c r="C190" s="12"/>
       <c r="D190" s="12"/>
       <c r="E190" s="13" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F190" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="191" customHeight="1" ht="15.0">
@@ -6680,10 +6832,10 @@
       <c r="C191" s="12"/>
       <c r="D191" s="12"/>
       <c r="E191" s="13" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F191" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" customHeight="1" ht="15.0">
@@ -6692,10 +6844,10 @@
       <c r="C192" s="12"/>
       <c r="D192" s="12"/>
       <c r="E192" s="13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F192" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="193" customHeight="1" ht="15.0">
@@ -6704,10 +6856,10 @@
       <c r="C193" s="12"/>
       <c r="D193" s="12"/>
       <c r="E193" s="13" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F193" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="194" customHeight="1" ht="15.0">
@@ -6716,10 +6868,10 @@
       <c r="C194" s="12"/>
       <c r="D194" s="12"/>
       <c r="E194" s="13" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F194" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" customHeight="1" ht="15.0">
@@ -6728,10 +6880,10 @@
       <c r="C195" s="12"/>
       <c r="D195" s="12"/>
       <c r="E195" s="13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F195" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="196" customHeight="1" ht="15.0">
@@ -6740,10 +6892,10 @@
       <c r="C196" s="12"/>
       <c r="D196" s="12"/>
       <c r="E196" s="13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F196" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="197" customHeight="1" ht="15.0">
@@ -6752,10 +6904,10 @@
       <c r="C197" s="12"/>
       <c r="D197" s="12"/>
       <c r="E197" s="13" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F197" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="198" customHeight="1" ht="15.0">
@@ -6764,10 +6916,10 @@
       <c r="C198" s="12"/>
       <c r="D198" s="12"/>
       <c r="E198" s="13" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F198" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="199" customHeight="1" ht="15.0">
@@ -6776,10 +6928,10 @@
       <c r="C199" s="12"/>
       <c r="D199" s="12"/>
       <c r="E199" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F199" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="200" customHeight="1" ht="15.0">
@@ -6788,10 +6940,10 @@
       <c r="C200" s="12"/>
       <c r="D200" s="12"/>
       <c r="E200" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F200" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="201" customHeight="1" ht="15.0">
@@ -6800,10 +6952,10 @@
       <c r="C201" s="12"/>
       <c r="D201" s="12"/>
       <c r="E201" s="13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F201" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="202" customHeight="1" ht="15.0">
@@ -6812,10 +6964,10 @@
       <c r="C202" s="12"/>
       <c r="D202" s="12"/>
       <c r="E202" s="13" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F202" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="203" customHeight="1" ht="15.0">
@@ -6824,10 +6976,10 @@
       <c r="C203" s="12"/>
       <c r="D203" s="12"/>
       <c r="E203" s="13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F203" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="204" customHeight="1" ht="15.0">
@@ -6836,10 +6988,10 @@
       <c r="C204" s="12"/>
       <c r="D204" s="12"/>
       <c r="E204" s="13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F204" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="205" customHeight="1" ht="15.0">
@@ -6848,10 +7000,10 @@
       <c r="C205" s="12"/>
       <c r="D205" s="12"/>
       <c r="E205" s="13" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F205" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="206" customHeight="1" ht="15.0">
@@ -6860,10 +7012,10 @@
       <c r="C206" s="12"/>
       <c r="D206" s="12"/>
       <c r="E206" s="13" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F206" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="207" customHeight="1" ht="15.0">
@@ -6872,10 +7024,10 @@
       <c r="C207" s="12"/>
       <c r="D207" s="12"/>
       <c r="E207" s="13" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F207" s="14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="208" customHeight="1" ht="15.0">
@@ -6884,10 +7036,10 @@
       <c r="C208" s="12"/>
       <c r="D208" s="12"/>
       <c r="E208" s="13" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F208" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="209" customHeight="1" ht="15.0">
@@ -6896,10 +7048,10 @@
       <c r="C209" s="12"/>
       <c r="D209" s="12"/>
       <c r="E209" s="13" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F209" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="210" customHeight="1" ht="15.0">
@@ -6908,10 +7060,10 @@
       <c r="C210" s="12"/>
       <c r="D210" s="12"/>
       <c r="E210" s="13" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F210" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="211" customHeight="1" ht="15.0">
@@ -6920,10 +7072,10 @@
       <c r="C211" s="12"/>
       <c r="D211" s="12"/>
       <c r="E211" s="13" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F211" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="212" customHeight="1" ht="15.0">
@@ -6932,10 +7084,10 @@
       <c r="C212" s="12"/>
       <c r="D212" s="12"/>
       <c r="E212" s="13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F212" s="14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" customHeight="1" ht="15.0">
@@ -6944,10 +7096,10 @@
       <c r="C213" s="12"/>
       <c r="D213" s="12"/>
       <c r="E213" s="13" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F213" s="14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" customHeight="1" ht="15.0">
@@ -6956,54 +7108,54 @@
       <c r="C214" s="12"/>
       <c r="D214" s="12"/>
       <c r="E214" s="13" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F214" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" customHeight="1" ht="15.0">
-      <c r="A215" s="15"/>
-      <c r="B215" s="16"/>
-      <c r="C215" s="16"/>
-      <c r="D215" s="16"/>
-      <c r="E215" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="F215" s="18" t="s">
+      <c r="A215" s="11"/>
+      <c r="B215" s="12"/>
+      <c r="C215" s="12"/>
+      <c r="D215" s="12"/>
+      <c r="E215" s="13" t="s">
         <v>480</v>
       </c>
+      <c r="F215" s="14" t="s">
+        <v>481</v>
+      </c>
     </row>
     <row r="216" customHeight="1" ht="15.0">
-      <c r="A216" s="19" t="s">
-        <v>481</v>
-      </c>
-      <c r="B216" s="20" t="s">
+      <c r="A216" s="15"/>
+      <c r="B216" s="16"/>
+      <c r="C216" s="16"/>
+      <c r="D216" s="16"/>
+      <c r="E216" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="C216" s="21" t="s">
+      <c r="F216" s="18" t="s">
         <v>483</v>
       </c>
-      <c r="D216" s="22" t="s">
+    </row>
+    <row r="217" customHeight="1" ht="15.0">
+      <c r="A217" s="19" t="s">
         <v>484</v>
       </c>
-      <c r="E216" s="23" t="s">
+      <c r="B217" s="20" t="s">
         <v>485</v>
       </c>
-      <c r="F216" s="24" t="s">
+      <c r="C217" s="21" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="217" customHeight="1" ht="15.0">
-      <c r="A217" s="11"/>
-      <c r="B217" s="12"/>
-      <c r="C217" s="12"/>
-      <c r="D217" s="12"/>
-      <c r="E217" s="25" t="s">
+      <c r="D217" s="22" t="s">
         <v>487</v>
       </c>
-      <c r="F217" s="26" t="s">
+      <c r="E217" s="23" t="s">
         <v>488</v>
+      </c>
+      <c r="F217" s="24" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="218" customHeight="1" ht="15.0">
@@ -7012,10 +7164,10 @@
       <c r="C218" s="12"/>
       <c r="D218" s="12"/>
       <c r="E218" s="25" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F218" s="26" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="219" customHeight="1" ht="15.0">
@@ -7024,10 +7176,10 @@
       <c r="C219" s="12"/>
       <c r="D219" s="12"/>
       <c r="E219" s="25" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F219" s="26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="220" customHeight="1" ht="15.0">
@@ -7036,10 +7188,10 @@
       <c r="C220" s="12"/>
       <c r="D220" s="12"/>
       <c r="E220" s="25" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F220" s="26" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="221" customHeight="1" ht="15.0">
@@ -7048,10 +7200,10 @@
       <c r="C221" s="12"/>
       <c r="D221" s="12"/>
       <c r="E221" s="25" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F221" s="26" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="222" customHeight="1" ht="15.0">
@@ -7060,66 +7212,66 @@
       <c r="C222" s="12"/>
       <c r="D222" s="12"/>
       <c r="E222" s="25" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F222" s="26" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="223" customHeight="1" ht="15.0">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" ht="136.0">
       <c r="A223" s="11"/>
       <c r="B223" s="12"/>
       <c r="C223" s="12"/>
       <c r="D223" s="12"/>
       <c r="E223" s="25" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F223" s="26" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="224" customHeight="1" ht="15.0">
-      <c r="A224" s="15"/>
-      <c r="B224" s="16"/>
-      <c r="C224" s="16"/>
-      <c r="D224" s="16"/>
-      <c r="E224" s="27" t="s">
         <v>501</v>
       </c>
-      <c r="F224" s="28" t="s">
+    </row>
+    <row r="224" customHeight="1" ht="68.0">
+      <c r="A224" s="11"/>
+      <c r="B224" s="12"/>
+      <c r="C224" s="12"/>
+      <c r="D224" s="12"/>
+      <c r="E224" s="25" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="225" customHeight="1" ht="15.0">
-      <c r="A225" s="5" t="s">
+      <c r="F224" s="26" t="s">
         <v>503</v>
       </c>
-      <c r="B225" s="6" t="s">
+    </row>
+    <row r="225" customHeight="1" ht="114.0">
+      <c r="A225" s="15"/>
+      <c r="B225" s="16"/>
+      <c r="C225" s="16"/>
+      <c r="D225" s="16"/>
+      <c r="E225" s="27" t="s">
         <v>504</v>
       </c>
-      <c r="C225" s="7" t="s">
+      <c r="F225" s="28" t="s">
         <v>505</v>
       </c>
-      <c r="D225" s="8" t="s">
+    </row>
+    <row r="226" customHeight="1" ht="127.0">
+      <c r="A226" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="E225" s="9" t="s">
+      <c r="B226" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="F225" s="10" t="s">
+      <c r="C226" s="7" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="226" customHeight="1" ht="15.0">
-      <c r="A226" s="11"/>
-      <c r="B226" s="12"/>
-      <c r="C226" s="12"/>
-      <c r="D226" s="12"/>
-      <c r="E226" s="13" t="s">
+      <c r="D226" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="F226" s="14" t="s">
+      <c r="E226" s="9" t="s">
         <v>510</v>
+      </c>
+      <c r="F226" s="10" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="227" customHeight="1" ht="15.0">
@@ -7128,10 +7280,10 @@
       <c r="C227" s="12"/>
       <c r="D227" s="12"/>
       <c r="E227" s="13" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F227" s="14" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="228" customHeight="1" ht="15.0">
@@ -7140,54 +7292,54 @@
       <c r="C228" s="12"/>
       <c r="D228" s="12"/>
       <c r="E228" s="13" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F228" s="14" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="229" customHeight="1" ht="15.0">
-      <c r="A229" s="15"/>
-      <c r="B229" s="16"/>
-      <c r="C229" s="16"/>
-      <c r="D229" s="16"/>
-      <c r="E229" s="17" t="s">
-        <v>515</v>
-      </c>
-      <c r="F229" s="18" t="s">
+      <c r="A229" s="11"/>
+      <c r="B229" s="12"/>
+      <c r="C229" s="12"/>
+      <c r="D229" s="12"/>
+      <c r="E229" s="13" t="s">
         <v>516</v>
       </c>
+      <c r="F229" s="14" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="230" customHeight="1" ht="15.0">
-      <c r="A230" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="B230" s="20" t="s">
+      <c r="A230" s="15"/>
+      <c r="B230" s="16"/>
+      <c r="C230" s="16"/>
+      <c r="D230" s="16"/>
+      <c r="E230" s="17" t="s">
         <v>518</v>
       </c>
-      <c r="C230" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="D230" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="E230" s="23" t="s">
+      <c r="F230" s="18" t="s">
         <v>519</v>
       </c>
-      <c r="F230" s="24" t="s">
+    </row>
+    <row r="231" customHeight="1" ht="15.0">
+      <c r="A231" s="19" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="231" customHeight="1" ht="15.0">
-      <c r="A231" s="11"/>
-      <c r="B231" s="12"/>
-      <c r="C231" s="12"/>
-      <c r="D231" s="12"/>
-      <c r="E231" s="25" t="s">
+      <c r="B231" s="20" t="s">
         <v>521</v>
       </c>
-      <c r="F231" s="26" t="s">
+      <c r="C231" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="D231" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E231" s="23" t="s">
         <v>522</v>
+      </c>
+      <c r="F231" s="24" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="232" customHeight="1" ht="15.0">
@@ -7196,10 +7348,10 @@
       <c r="C232" s="12"/>
       <c r="D232" s="12"/>
       <c r="E232" s="25" t="s">
-        <v>251</v>
+        <v>524</v>
       </c>
       <c r="F232" s="26" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="233" customHeight="1" ht="15.0">
@@ -7208,10 +7360,10 @@
       <c r="C233" s="12"/>
       <c r="D233" s="12"/>
       <c r="E233" s="25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F233" s="26" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="234" customHeight="1" ht="15.0">
@@ -7220,10 +7372,10 @@
       <c r="C234" s="12"/>
       <c r="D234" s="12"/>
       <c r="E234" s="25" t="s">
-        <v>189</v>
+        <v>256</v>
       </c>
       <c r="F234" s="26" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="235" customHeight="1" ht="15.0">
@@ -7232,10 +7384,10 @@
       <c r="C235" s="12"/>
       <c r="D235" s="12"/>
       <c r="E235" s="25" t="s">
-        <v>257</v>
+        <v>190</v>
       </c>
       <c r="F235" s="26" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="236" customHeight="1" ht="15.0">
@@ -7244,10 +7396,10 @@
       <c r="C236" s="12"/>
       <c r="D236" s="12"/>
       <c r="E236" s="25" t="s">
-        <v>527</v>
+        <v>260</v>
       </c>
       <c r="F236" s="26" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="237" customHeight="1" ht="15.0">
@@ -7256,10 +7408,10 @@
       <c r="C237" s="12"/>
       <c r="D237" s="12"/>
       <c r="E237" s="25" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F237" s="26" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="238" customHeight="1" ht="15.0">
@@ -7268,10 +7420,10 @@
       <c r="C238" s="12"/>
       <c r="D238" s="12"/>
       <c r="E238" s="25" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F238" s="26" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="239" customHeight="1" ht="15.0">
@@ -7280,10 +7432,10 @@
       <c r="C239" s="12"/>
       <c r="D239" s="12"/>
       <c r="E239" s="25" t="s">
-        <v>265</v>
+        <v>534</v>
       </c>
       <c r="F239" s="26" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="240" customHeight="1" ht="15.0">
@@ -7292,78 +7444,78 @@
       <c r="C240" s="12"/>
       <c r="D240" s="12"/>
       <c r="E240" s="25" t="s">
-        <v>534</v>
+        <v>268</v>
       </c>
       <c r="F240" s="26" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="241" customHeight="1" ht="27.0">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" ht="15.0">
       <c r="A241" s="11"/>
       <c r="B241" s="12"/>
       <c r="C241" s="12"/>
       <c r="D241" s="12"/>
       <c r="E241" s="25" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F241" s="26" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="242" customHeight="1" ht="27.0">
-      <c r="A242" s="15"/>
-      <c r="B242" s="16"/>
-      <c r="C242" s="16"/>
-      <c r="D242" s="16"/>
-      <c r="E242" s="27" t="s">
-        <v>537</v>
-      </c>
-      <c r="F242" s="28" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="243" customHeight="1" ht="35.0">
-      <c r="A243" s="5" t="s">
+      <c r="A242" s="11"/>
+      <c r="B242" s="12"/>
+      <c r="C242" s="12"/>
+      <c r="D242" s="12"/>
+      <c r="E242" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="F242" s="26" t="s">
         <v>539</v>
       </c>
-      <c r="B243" s="6" t="s">
+    </row>
+    <row r="243" customHeight="1" ht="27.0">
+      <c r="A243" s="15"/>
+      <c r="B243" s="16"/>
+      <c r="C243" s="16"/>
+      <c r="D243" s="16"/>
+      <c r="E243" s="27" t="s">
         <v>540</v>
       </c>
-      <c r="C243" s="7" t="s">
+      <c r="F243" s="28" t="s">
         <v>541</v>
       </c>
-      <c r="D243" s="8" t="s">
+    </row>
+    <row r="244" customHeight="1" ht="35.0">
+      <c r="A244" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="E243" s="9" t="s">
+      <c r="B244" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="F243" s="10" t="s">
+      <c r="C244" s="7" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="244" customHeight="1" ht="30.0">
-      <c r="A244" s="11"/>
-      <c r="B244" s="12"/>
-      <c r="C244" s="12"/>
-      <c r="D244" s="12"/>
-      <c r="E244" s="13" t="s">
+      <c r="D244" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="F244" s="14" t="s">
+      <c r="E244" s="9" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="245" customHeight="1" ht="42.0">
+      <c r="F244" s="10" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" ht="30.0">
       <c r="A245" s="11"/>
       <c r="B245" s="12"/>
       <c r="C245" s="12"/>
       <c r="D245" s="12"/>
       <c r="E245" s="13" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F245" s="14" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="246" customHeight="1" ht="42.0">
@@ -7372,134 +7524,134 @@
       <c r="C246" s="12"/>
       <c r="D246" s="12"/>
       <c r="E246" s="13" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F246" s="14" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="247" customHeight="1" ht="35.0">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" ht="42.0">
       <c r="A247" s="11"/>
       <c r="B247" s="12"/>
       <c r="C247" s="12"/>
       <c r="D247" s="12"/>
       <c r="E247" s="13" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F247" s="14" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="248" customHeight="1" ht="39.0">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" ht="35.0">
       <c r="A248" s="11"/>
       <c r="B248" s="12"/>
       <c r="C248" s="12"/>
       <c r="D248" s="12"/>
       <c r="E248" s="13" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F248" s="14" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="249" customHeight="1" ht="43.0">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" ht="39.0">
       <c r="A249" s="11"/>
       <c r="B249" s="12"/>
       <c r="C249" s="12"/>
       <c r="D249" s="12"/>
       <c r="E249" s="13" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F249" s="14" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="250" customHeight="1" ht="55.0">
-      <c r="A250" s="15"/>
-      <c r="B250" s="16"/>
-      <c r="C250" s="16"/>
-      <c r="D250" s="16"/>
-      <c r="E250" s="17" t="s">
         <v>557</v>
       </c>
-      <c r="F250" s="18" t="s">
+    </row>
+    <row r="250" customHeight="1" ht="43.0">
+      <c r="A250" s="11"/>
+      <c r="B250" s="12"/>
+      <c r="C250" s="12"/>
+      <c r="D250" s="12"/>
+      <c r="E250" s="13" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="251" customHeight="1" ht="89.0">
-      <c r="A251" s="19" t="s">
+      <c r="F250" s="14" t="s">
         <v>559</v>
       </c>
-      <c r="B251" s="20" t="s">
+    </row>
+    <row r="251" customHeight="1" ht="55.0">
+      <c r="A251" s="15"/>
+      <c r="B251" s="16"/>
+      <c r="C251" s="16"/>
+      <c r="D251" s="16"/>
+      <c r="E251" s="17" t="s">
         <v>560</v>
       </c>
-      <c r="C251" s="21" t="s">
+      <c r="F251" s="18" t="s">
         <v>561</v>
       </c>
-      <c r="D251" s="22" t="s">
+    </row>
+    <row r="252" customHeight="1" ht="89.0">
+      <c r="A252" s="19" t="s">
         <v>562</v>
       </c>
-      <c r="E251" s="23" t="s">
+      <c r="B252" s="20" t="s">
         <v>563</v>
       </c>
-      <c r="F251" s="24" t="s">
+      <c r="C252" s="21" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="252" customHeight="1" ht="52.0">
-      <c r="A252" s="11"/>
-      <c r="B252" s="12"/>
-      <c r="C252" s="12"/>
-      <c r="D252" s="12"/>
-      <c r="E252" s="25" t="s">
+      <c r="D252" s="22" t="s">
         <v>565</v>
       </c>
-      <c r="F252" s="26" t="s">
+      <c r="E252" s="23" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="253" customHeight="1" ht="46.0">
-      <c r="A253" s="15"/>
-      <c r="B253" s="16"/>
-      <c r="C253" s="16"/>
-      <c r="D253" s="16"/>
-      <c r="E253" s="27" t="s">
+      <c r="F252" s="24" t="s">
         <v>567</v>
       </c>
-      <c r="F253" s="28" t="s">
+    </row>
+    <row r="253" customHeight="1" ht="52.0">
+      <c r="A253" s="11"/>
+      <c r="B253" s="12"/>
+      <c r="C253" s="12"/>
+      <c r="D253" s="12"/>
+      <c r="E253" s="25" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="254" customHeight="1" ht="76.0">
-      <c r="A254" s="5" t="s">
+      <c r="F253" s="26" t="s">
         <v>569</v>
       </c>
-      <c r="B254" s="6" t="s">
+    </row>
+    <row r="254" customHeight="1" ht="46.0">
+      <c r="A254" s="15"/>
+      <c r="B254" s="16"/>
+      <c r="C254" s="16"/>
+      <c r="D254" s="16"/>
+      <c r="E254" s="27" t="s">
         <v>570</v>
       </c>
-      <c r="C254" s="7" t="s">
+      <c r="F254" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="D254" s="8" t="s">
+    </row>
+    <row r="255" customHeight="1" ht="76.0">
+      <c r="A255" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="E254" s="9" t="s">
+      <c r="B255" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="F254" s="10" t="s">
+      <c r="C255" s="7" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="255" customHeight="1" ht="54.0">
-      <c r="A255" s="11"/>
-      <c r="B255" s="12"/>
-      <c r="C255" s="12"/>
-      <c r="D255" s="12"/>
-      <c r="E255" s="13" t="s">
+      <c r="D255" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="F255" s="14" t="s">
+      <c r="E255" s="9" t="s">
         <v>576</v>
+      </c>
+      <c r="F255" s="10" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="256" customHeight="1" ht="54.0">
@@ -7508,138 +7660,138 @@
       <c r="C256" s="12"/>
       <c r="D256" s="12"/>
       <c r="E256" s="13" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F256" s="14" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="257" customHeight="1" ht="55.0">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="257" customHeight="1" ht="54.0">
       <c r="A257" s="11"/>
       <c r="B257" s="12"/>
       <c r="C257" s="12"/>
       <c r="D257" s="12"/>
       <c r="E257" s="13" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F257" s="14" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="258" customHeight="1" ht="36.0">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="258" customHeight="1" ht="55.0">
       <c r="A258" s="11"/>
       <c r="B258" s="12"/>
       <c r="C258" s="12"/>
       <c r="D258" s="12"/>
       <c r="E258" s="13" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F258" s="14" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="259" customHeight="1" ht="41.0">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="259" customHeight="1" ht="36.0">
       <c r="A259" s="11"/>
       <c r="B259" s="12"/>
       <c r="C259" s="12"/>
       <c r="D259" s="12"/>
       <c r="E259" s="13" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F259" s="14" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="260" customHeight="1" ht="31.0">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="260" customHeight="1" ht="41.0">
       <c r="A260" s="11"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12"/>
       <c r="D260" s="12"/>
       <c r="E260" s="13" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F260" s="14" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="261" customHeight="1" ht="32.0">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="261" customHeight="1" ht="31.0">
       <c r="A261" s="11"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12"/>
       <c r="D261" s="12"/>
       <c r="E261" s="13" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F261" s="14" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="262" customHeight="1" ht="42.0">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="262" customHeight="1" ht="32.0">
       <c r="A262" s="11"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12"/>
       <c r="D262" s="12"/>
       <c r="E262" s="13" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F262" s="14" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="263" customHeight="1" ht="39.0">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="263" customHeight="1" ht="42.0">
       <c r="A263" s="11"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
       <c r="D263" s="12"/>
       <c r="E263" s="13" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F263" s="14" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="264" customHeight="1" ht="49.0">
-      <c r="A264" s="15"/>
-      <c r="B264" s="16"/>
-      <c r="C264" s="16"/>
-      <c r="D264" s="16"/>
-      <c r="E264" s="17" t="s">
         <v>593</v>
       </c>
-      <c r="F264" s="18" t="s">
+    </row>
+    <row r="264" customHeight="1" ht="39.0">
+      <c r="A264" s="11"/>
+      <c r="B264" s="12"/>
+      <c r="C264" s="12"/>
+      <c r="D264" s="12"/>
+      <c r="E264" s="13" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="265" customHeight="1" ht="15.0">
-      <c r="A265" s="19" t="s">
+      <c r="F264" s="14" t="s">
         <v>595</v>
       </c>
-      <c r="B265" s="21" t="s">
+    </row>
+    <row r="265" customHeight="1" ht="49.0">
+      <c r="A265" s="15"/>
+      <c r="B265" s="16"/>
+      <c r="C265" s="16"/>
+      <c r="D265" s="16"/>
+      <c r="E265" s="17" t="s">
         <v>596</v>
       </c>
-      <c r="C265" s="21" t="s">
+      <c r="F265" s="18" t="s">
         <v>597</v>
       </c>
-      <c r="D265" s="21" t="s">
+    </row>
+    <row r="266" customHeight="1" ht="15.0">
+      <c r="A266" s="19" t="s">
         <v>598</v>
       </c>
-      <c r="E265" s="21" t="s">
+      <c r="B266" s="21" t="s">
         <v>599</v>
       </c>
-      <c r="F265" s="24" t="s">
+      <c r="C266" s="21" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="266" customHeight="1" ht="15.0">
-      <c r="A266" s="11"/>
-      <c r="B266" s="12"/>
-      <c r="C266" s="12"/>
-      <c r="D266" s="12"/>
-      <c r="E266" s="12" t="s">
+      <c r="D266" s="21" t="s">
         <v>601</v>
       </c>
-      <c r="F266" s="26" t="s">
+      <c r="E266" s="21" t="s">
         <v>602</v>
+      </c>
+      <c r="F266" s="24" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="267" customHeight="1" ht="15.0">
@@ -7648,10 +7800,10 @@
       <c r="C267" s="12"/>
       <c r="D267" s="12"/>
       <c r="E267" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F267" s="26" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="268" customHeight="1" ht="15.0">
@@ -7660,10 +7812,10 @@
       <c r="C268" s="12"/>
       <c r="D268" s="12"/>
       <c r="E268" s="12" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F268" s="26" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="269" customHeight="1" ht="15.0">
@@ -7672,54 +7824,54 @@
       <c r="C269" s="12"/>
       <c r="D269" s="12"/>
       <c r="E269" s="12" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F269" s="26" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="270" customHeight="1" ht="15.0">
-      <c r="A270" s="15"/>
-      <c r="B270" s="16"/>
-      <c r="C270" s="16"/>
-      <c r="D270" s="16"/>
-      <c r="E270" s="16" t="s">
-        <v>609</v>
-      </c>
-      <c r="F270" s="28" t="s">
+      <c r="A270" s="11"/>
+      <c r="B270" s="12"/>
+      <c r="C270" s="12"/>
+      <c r="D270" s="12"/>
+      <c r="E270" s="12" t="s">
         <v>610</v>
       </c>
+      <c r="F270" s="26" t="s">
+        <v>611</v>
+      </c>
     </row>
     <row r="271" customHeight="1" ht="15.0">
-      <c r="A271" s="5" t="s">
-        <v>611</v>
-      </c>
-      <c r="B271" s="6" t="s">
+      <c r="A271" s="15"/>
+      <c r="B271" s="16"/>
+      <c r="C271" s="16"/>
+      <c r="D271" s="16"/>
+      <c r="E271" s="16" t="s">
         <v>612</v>
       </c>
-      <c r="C271" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="D271" s="8" t="s">
+      <c r="F271" s="28" t="s">
         <v>613</v>
       </c>
-      <c r="E271" s="9" t="s">
+    </row>
+    <row r="272" customHeight="1" ht="15.0">
+      <c r="A272" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="F271" s="10" t="s">
+      <c r="B272" s="6" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="272" customHeight="1" ht="15.0">
-      <c r="A272" s="11"/>
-      <c r="B272" s="12"/>
-      <c r="C272" s="12"/>
-      <c r="D272" s="12"/>
-      <c r="E272" s="13" t="s">
+      <c r="C272" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="D272" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="F272" s="14" t="s">
+      <c r="E272" s="9" t="s">
         <v>617</v>
+      </c>
+      <c r="F272" s="10" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="273" customHeight="1" ht="15.0">
@@ -7728,10 +7880,10 @@
       <c r="C273" s="12"/>
       <c r="D273" s="12"/>
       <c r="E273" s="13" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F273" s="14" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="274" customHeight="1" ht="15.0">
@@ -7740,10 +7892,10 @@
       <c r="C274" s="12"/>
       <c r="D274" s="12"/>
       <c r="E274" s="13" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F274" s="14" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="275" customHeight="1" ht="15.0">
@@ -7752,10 +7904,10 @@
       <c r="C275" s="12"/>
       <c r="D275" s="12"/>
       <c r="E275" s="13" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F275" s="14" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="276" customHeight="1" ht="15.0">
@@ -7764,10 +7916,10 @@
       <c r="C276" s="12"/>
       <c r="D276" s="12"/>
       <c r="E276" s="13" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F276" s="14" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="277" customHeight="1" ht="15.0">
@@ -7776,10 +7928,10 @@
       <c r="C277" s="12"/>
       <c r="D277" s="12"/>
       <c r="E277" s="13" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F277" s="14" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="278" customHeight="1" ht="15.0">
@@ -7788,10 +7940,10 @@
       <c r="C278" s="12"/>
       <c r="D278" s="12"/>
       <c r="E278" s="13" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F278" s="14" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="279" customHeight="1" ht="15.0">
@@ -7800,10 +7952,10 @@
       <c r="C279" s="12"/>
       <c r="D279" s="12"/>
       <c r="E279" s="13" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F279" s="14" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="280" customHeight="1" ht="15.0">
@@ -7812,10 +7964,10 @@
       <c r="C280" s="12"/>
       <c r="D280" s="12"/>
       <c r="E280" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F280" s="14" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="281" customHeight="1" ht="15.0">
@@ -7824,10 +7976,10 @@
       <c r="C281" s="12"/>
       <c r="D281" s="12"/>
       <c r="E281" s="13" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F281" s="14" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="282" customHeight="1" ht="15.0">
@@ -7836,54 +7988,54 @@
       <c r="C282" s="12"/>
       <c r="D282" s="12"/>
       <c r="E282" s="13" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F282" s="14" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="283" customHeight="1" ht="15.0">
-      <c r="A283" s="15"/>
-      <c r="B283" s="16"/>
-      <c r="C283" s="16"/>
-      <c r="D283" s="16"/>
-      <c r="E283" s="17" t="s">
-        <v>638</v>
-      </c>
-      <c r="F283" s="18" t="s">
+      <c r="A283" s="11"/>
+      <c r="B283" s="12"/>
+      <c r="C283" s="12"/>
+      <c r="D283" s="12"/>
+      <c r="E283" s="13" t="s">
         <v>639</v>
       </c>
+      <c r="F283" s="14" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="284" customHeight="1" ht="15.0">
-      <c r="A284" s="19" t="s">
-        <v>640</v>
-      </c>
-      <c r="B284" s="20" t="s">
+      <c r="A284" s="15"/>
+      <c r="B284" s="16"/>
+      <c r="C284" s="16"/>
+      <c r="D284" s="16"/>
+      <c r="E284" s="17" t="s">
         <v>641</v>
       </c>
-      <c r="C284" s="21" t="s">
+      <c r="F284" s="18" t="s">
         <v>642</v>
       </c>
-      <c r="D284" s="22" t="s">
+    </row>
+    <row r="285" customHeight="1" ht="15.0">
+      <c r="A285" s="19" t="s">
         <v>643</v>
       </c>
-      <c r="E284" s="23" t="s">
+      <c r="B285" s="20" t="s">
         <v>644</v>
       </c>
-      <c r="F284" s="24" t="s">
+      <c r="C285" s="21" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="285" customHeight="1" ht="15.0">
-      <c r="A285" s="11"/>
-      <c r="B285" s="12"/>
-      <c r="C285" s="12"/>
-      <c r="D285" s="12"/>
-      <c r="E285" s="25" t="s">
+      <c r="D285" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="F285" s="26" t="s">
+      <c r="E285" s="23" t="s">
         <v>647</v>
+      </c>
+      <c r="F285" s="24" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="286" customHeight="1" ht="15.0">
@@ -7892,10 +8044,10 @@
       <c r="C286" s="12"/>
       <c r="D286" s="12"/>
       <c r="E286" s="25" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F286" s="26" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="287" customHeight="1" ht="15.0">
@@ -7904,10 +8056,10 @@
       <c r="C287" s="12"/>
       <c r="D287" s="12"/>
       <c r="E287" s="25" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F287" s="26" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="288" customHeight="1" ht="15.0">
@@ -7916,10 +8068,10 @@
       <c r="C288" s="12"/>
       <c r="D288" s="12"/>
       <c r="E288" s="25" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F288" s="26" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="289" customHeight="1" ht="15.0">
@@ -7928,10 +8080,10 @@
       <c r="C289" s="12"/>
       <c r="D289" s="12"/>
       <c r="E289" s="25" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F289" s="26" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="290" customHeight="1" ht="15.0">
@@ -7940,10 +8092,10 @@
       <c r="C290" s="12"/>
       <c r="D290" s="12"/>
       <c r="E290" s="25" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F290" s="26" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="291" customHeight="1" ht="15.0">
@@ -7952,10 +8104,10 @@
       <c r="C291" s="12"/>
       <c r="D291" s="12"/>
       <c r="E291" s="25" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F291" s="26" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="292" customHeight="1" ht="15.0">
@@ -7964,10 +8116,10 @@
       <c r="C292" s="12"/>
       <c r="D292" s="12"/>
       <c r="E292" s="25" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F292" s="26" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="293" customHeight="1" ht="15.0">
@@ -7976,10 +8128,10 @@
       <c r="C293" s="12"/>
       <c r="D293" s="12"/>
       <c r="E293" s="25" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F293" s="26" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="294" customHeight="1" ht="15.0">
@@ -7988,10 +8140,10 @@
       <c r="C294" s="12"/>
       <c r="D294" s="12"/>
       <c r="E294" s="25" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F294" s="26" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="295" customHeight="1" ht="15.0">
@@ -8000,10 +8152,10 @@
       <c r="C295" s="12"/>
       <c r="D295" s="12"/>
       <c r="E295" s="25" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F295" s="26" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="296" customHeight="1" ht="15.0">
@@ -8012,10 +8164,10 @@
       <c r="C296" s="12"/>
       <c r="D296" s="12"/>
       <c r="E296" s="25" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F296" s="26" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="297" customHeight="1" ht="15.0">
@@ -8024,10 +8176,10 @@
       <c r="C297" s="12"/>
       <c r="D297" s="12"/>
       <c r="E297" s="25" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F297" s="26" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="298" customHeight="1" ht="15.0">
@@ -8036,10 +8188,10 @@
       <c r="C298" s="12"/>
       <c r="D298" s="12"/>
       <c r="E298" s="25" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F298" s="26" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="299" customHeight="1" ht="15.0">
@@ -8048,10 +8200,10 @@
       <c r="C299" s="12"/>
       <c r="D299" s="12"/>
       <c r="E299" s="25" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F299" s="26" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="300" customHeight="1" ht="15.0">
@@ -8060,10 +8212,10 @@
       <c r="C300" s="12"/>
       <c r="D300" s="12"/>
       <c r="E300" s="25" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F300" s="26" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="301" customHeight="1" ht="15.0">
@@ -8072,10 +8224,10 @@
       <c r="C301" s="12"/>
       <c r="D301" s="12"/>
       <c r="E301" s="25" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F301" s="26" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="302" customHeight="1" ht="15.0">
@@ -8084,10 +8236,10 @@
       <c r="C302" s="12"/>
       <c r="D302" s="12"/>
       <c r="E302" s="25" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F302" s="26" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="303" customHeight="1" ht="15.0">
@@ -8096,10 +8248,10 @@
       <c r="C303" s="12"/>
       <c r="D303" s="12"/>
       <c r="E303" s="25" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F303" s="26" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="304" customHeight="1" ht="15.0">
@@ -8108,54 +8260,54 @@
       <c r="C304" s="12"/>
       <c r="D304" s="12"/>
       <c r="E304" s="25" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F304" s="26" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="305" customHeight="1" ht="15.0">
-      <c r="A305" s="15"/>
-      <c r="B305" s="16"/>
-      <c r="C305" s="16"/>
-      <c r="D305" s="16"/>
-      <c r="E305" s="27" t="s">
-        <v>686</v>
-      </c>
-      <c r="F305" s="28" t="s">
+      <c r="A305" s="11"/>
+      <c r="B305" s="12"/>
+      <c r="C305" s="12"/>
+      <c r="D305" s="12"/>
+      <c r="E305" s="25" t="s">
         <v>687</v>
       </c>
+      <c r="F305" s="26" t="s">
+        <v>688</v>
+      </c>
     </row>
     <row r="306" customHeight="1" ht="15.0">
-      <c r="A306" s="5" t="s">
-        <v>688</v>
-      </c>
-      <c r="B306" s="6" t="s">
+      <c r="A306" s="15"/>
+      <c r="B306" s="16"/>
+      <c r="C306" s="16"/>
+      <c r="D306" s="16"/>
+      <c r="E306" s="27" t="s">
         <v>689</v>
       </c>
-      <c r="C306" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="D306" s="8" t="s">
+      <c r="F306" s="28" t="s">
         <v>690</v>
       </c>
-      <c r="E306" s="9" t="s">
+    </row>
+    <row r="307" customHeight="1" ht="15.0">
+      <c r="A307" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="F306" s="10" t="s">
+      <c r="B307" s="6" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="307" customHeight="1" ht="15.0">
-      <c r="A307" s="11"/>
-      <c r="B307" s="12"/>
-      <c r="C307" s="12"/>
-      <c r="D307" s="12"/>
-      <c r="E307" s="13" t="s">
+      <c r="C307" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D307" s="8" t="s">
         <v>693</v>
       </c>
-      <c r="F307" s="14" t="s">
+      <c r="E307" s="9" t="s">
         <v>694</v>
+      </c>
+      <c r="F307" s="10" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="308" customHeight="1" ht="15.0">
@@ -8164,10 +8316,10 @@
       <c r="C308" s="12"/>
       <c r="D308" s="12"/>
       <c r="E308" s="13" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F308" s="14" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="309" customHeight="1" ht="15.0">
@@ -8176,10 +8328,10 @@
       <c r="C309" s="12"/>
       <c r="D309" s="12"/>
       <c r="E309" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F309" s="14" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="310" customHeight="1" ht="15.0">
@@ -8188,10 +8340,10 @@
       <c r="C310" s="12"/>
       <c r="D310" s="12"/>
       <c r="E310" s="13" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F310" s="14" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="311" customHeight="1" ht="15.0">
@@ -8200,10 +8352,10 @@
       <c r="C311" s="12"/>
       <c r="D311" s="12"/>
       <c r="E311" s="13" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F311" s="14" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="312" customHeight="1" ht="15.0">
@@ -8212,10 +8364,10 @@
       <c r="C312" s="12"/>
       <c r="D312" s="12"/>
       <c r="E312" s="13" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F312" s="14" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="313" customHeight="1" ht="15.0">
@@ -8224,10 +8376,10 @@
       <c r="C313" s="12"/>
       <c r="D313" s="12"/>
       <c r="E313" s="13" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F313" s="14" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="314" customHeight="1" ht="15.0">
@@ -8236,10 +8388,10 @@
       <c r="C314" s="12"/>
       <c r="D314" s="12"/>
       <c r="E314" s="13" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F314" s="14" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="315" customHeight="1" ht="15.0">
@@ -8248,10 +8400,10 @@
       <c r="C315" s="12"/>
       <c r="D315" s="12"/>
       <c r="E315" s="13" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F315" s="14" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="316" customHeight="1" ht="15.0">
@@ -8260,10 +8412,10 @@
       <c r="C316" s="12"/>
       <c r="D316" s="12"/>
       <c r="E316" s="13" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F316" s="14" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="317" customHeight="1" ht="15.0">
@@ -8272,54 +8424,54 @@
       <c r="C317" s="12"/>
       <c r="D317" s="12"/>
       <c r="E317" s="13" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F317" s="14" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="318" customHeight="1" ht="15.0">
-      <c r="A318" s="15"/>
-      <c r="B318" s="16"/>
-      <c r="C318" s="16"/>
-      <c r="D318" s="16"/>
-      <c r="E318" s="17" t="s">
-        <v>715</v>
-      </c>
-      <c r="F318" s="18" t="s">
+      <c r="A318" s="11"/>
+      <c r="B318" s="12"/>
+      <c r="C318" s="12"/>
+      <c r="D318" s="12"/>
+      <c r="E318" s="13" t="s">
         <v>716</v>
       </c>
+      <c r="F318" s="14" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="319" customHeight="1" ht="15.0">
-      <c r="A319" s="19" t="s">
-        <v>717</v>
-      </c>
-      <c r="B319" s="20" t="s">
-        <v>504</v>
-      </c>
-      <c r="C319" s="21" t="s">
-        <v>541</v>
-      </c>
-      <c r="D319" s="22" t="s">
+      <c r="A319" s="15"/>
+      <c r="B319" s="16"/>
+      <c r="C319" s="16"/>
+      <c r="D319" s="16"/>
+      <c r="E319" s="17" t="s">
         <v>718</v>
       </c>
-      <c r="E319" s="23" t="s">
+      <c r="F319" s="18" t="s">
         <v>719</v>
       </c>
-      <c r="F319" s="24" t="s">
+    </row>
+    <row r="320" customHeight="1" ht="15.0">
+      <c r="A320" s="19" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="320" customHeight="1" ht="15.0">
-      <c r="A320" s="11"/>
-      <c r="B320" s="12"/>
-      <c r="C320" s="12"/>
-      <c r="D320" s="12"/>
-      <c r="E320" s="25" t="s">
+      <c r="B320" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="C320" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="D320" s="22" t="s">
         <v>721</v>
       </c>
-      <c r="F320" s="26" t="s">
+      <c r="E320" s="23" t="s">
         <v>722</v>
+      </c>
+      <c r="F320" s="24" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="321" customHeight="1" ht="15.0">
@@ -8328,10 +8480,10 @@
       <c r="C321" s="12"/>
       <c r="D321" s="12"/>
       <c r="E321" s="25" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F321" s="26" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="322" customHeight="1" ht="15.0">
@@ -8340,10 +8492,10 @@
       <c r="C322" s="12"/>
       <c r="D322" s="12"/>
       <c r="E322" s="25" t="s">
-        <v>543</v>
+        <v>726</v>
       </c>
       <c r="F322" s="26" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="323" customHeight="1" ht="15.0">
@@ -8352,10 +8504,10 @@
       <c r="C323" s="12"/>
       <c r="D323" s="12"/>
       <c r="E323" s="25" t="s">
-        <v>726</v>
+        <v>546</v>
       </c>
       <c r="F323" s="26" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="324" customHeight="1" ht="15.0">
@@ -8364,10 +8516,10 @@
       <c r="C324" s="12"/>
       <c r="D324" s="12"/>
       <c r="E324" s="25" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F324" s="26" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="325" customHeight="1" ht="15.0">
@@ -8376,10 +8528,10 @@
       <c r="C325" s="12"/>
       <c r="D325" s="12"/>
       <c r="E325" s="25" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F325" s="26" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="326" customHeight="1" ht="15.0">
@@ -8388,10 +8540,10 @@
       <c r="C326" s="12"/>
       <c r="D326" s="12"/>
       <c r="E326" s="25" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F326" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="327" customHeight="1" ht="15.0">
@@ -8400,10 +8552,10 @@
       <c r="C327" s="12"/>
       <c r="D327" s="12"/>
       <c r="E327" s="25" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F327" s="26" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="328" customHeight="1" ht="15.0">
@@ -8412,10 +8564,10 @@
       <c r="C328" s="12"/>
       <c r="D328" s="12"/>
       <c r="E328" s="25" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F328" s="26" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="329" customHeight="1" ht="15.0">
@@ -8424,10 +8576,10 @@
       <c r="C329" s="12"/>
       <c r="D329" s="12"/>
       <c r="E329" s="25" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F329" s="26" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="330" customHeight="1" ht="15.0">
@@ -8436,10 +8588,10 @@
       <c r="C330" s="12"/>
       <c r="D330" s="12"/>
       <c r="E330" s="25" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F330" s="26" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="331" customHeight="1" ht="15.0">
@@ -8448,10 +8600,10 @@
       <c r="C331" s="12"/>
       <c r="D331" s="12"/>
       <c r="E331" s="25" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F331" s="26" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="332" customHeight="1" ht="15.0">
@@ -8460,10 +8612,10 @@
       <c r="C332" s="12"/>
       <c r="D332" s="12"/>
       <c r="E332" s="25" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F332" s="26" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="333" customHeight="1" ht="15.0">
@@ -8472,10 +8624,10 @@
       <c r="C333" s="12"/>
       <c r="D333" s="12"/>
       <c r="E333" s="25" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F333" s="26" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="334" customHeight="1" ht="15.0">
@@ -8484,10 +8636,10 @@
       <c r="C334" s="12"/>
       <c r="D334" s="12"/>
       <c r="E334" s="25" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F334" s="26" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="335" customHeight="1" ht="15.0">
@@ -8496,10 +8648,10 @@
       <c r="C335" s="12"/>
       <c r="D335" s="12"/>
       <c r="E335" s="25" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F335" s="26" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="336" customHeight="1" ht="15.0">
@@ -8508,10 +8660,10 @@
       <c r="C336" s="12"/>
       <c r="D336" s="12"/>
       <c r="E336" s="25" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F336" s="26" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="337" customHeight="1" ht="15.0">
@@ -8520,10 +8672,10 @@
       <c r="C337" s="12"/>
       <c r="D337" s="12"/>
       <c r="E337" s="25" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F337" s="26" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="338" customHeight="1" ht="15.0">
@@ -8532,10 +8684,10 @@
       <c r="C338" s="12"/>
       <c r="D338" s="12"/>
       <c r="E338" s="25" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F338" s="26" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="339" customHeight="1" ht="15.0">
@@ -8544,10 +8696,10 @@
       <c r="C339" s="12"/>
       <c r="D339" s="12"/>
       <c r="E339" s="25" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F339" s="26" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="340" customHeight="1" ht="15.0">
@@ -8556,10 +8708,10 @@
       <c r="C340" s="12"/>
       <c r="D340" s="12"/>
       <c r="E340" s="25" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F340" s="26" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="341" customHeight="1" ht="15.0">
@@ -8568,10 +8720,10 @@
       <c r="C341" s="12"/>
       <c r="D341" s="12"/>
       <c r="E341" s="25" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F341" s="26" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="342" customHeight="1" ht="15.0">
@@ -8580,10 +8732,10 @@
       <c r="C342" s="12"/>
       <c r="D342" s="12"/>
       <c r="E342" s="25" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F342" s="26" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="343" customHeight="1" ht="15.0">
@@ -8592,10 +8744,10 @@
       <c r="C343" s="12"/>
       <c r="D343" s="12"/>
       <c r="E343" s="25" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F343" s="26" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="344" customHeight="1" ht="15.0">
@@ -8604,10 +8756,10 @@
       <c r="C344" s="12"/>
       <c r="D344" s="12"/>
       <c r="E344" s="25" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F344" s="26" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="345" customHeight="1" ht="15.0">
@@ -8616,10 +8768,10 @@
       <c r="C345" s="12"/>
       <c r="D345" s="12"/>
       <c r="E345" s="25" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F345" s="26" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="346" customHeight="1" ht="15.0">
@@ -8628,54 +8780,54 @@
       <c r="C346" s="12"/>
       <c r="D346" s="12"/>
       <c r="E346" s="25" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F346" s="26" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="347" customHeight="1" ht="15.0">
-      <c r="A347" s="15"/>
-      <c r="B347" s="16"/>
-      <c r="C347" s="16"/>
-      <c r="D347" s="16"/>
-      <c r="E347" s="27" t="s">
-        <v>774</v>
-      </c>
-      <c r="F347" s="28" t="s">
+      <c r="A347" s="11"/>
+      <c r="B347" s="12"/>
+      <c r="C347" s="12"/>
+      <c r="D347" s="12"/>
+      <c r="E347" s="25" t="s">
         <v>775</v>
       </c>
+      <c r="F347" s="26" t="s">
+        <v>776</v>
+      </c>
     </row>
     <row r="348" customHeight="1" ht="15.0">
-      <c r="A348" s="5" t="s">
-        <v>776</v>
-      </c>
-      <c r="B348" s="6" t="s">
+      <c r="A348" s="15"/>
+      <c r="B348" s="16"/>
+      <c r="C348" s="16"/>
+      <c r="D348" s="16"/>
+      <c r="E348" s="27" t="s">
         <v>777</v>
       </c>
-      <c r="C348" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="D348" s="8" t="s">
+      <c r="F348" s="28" t="s">
         <v>778</v>
       </c>
-      <c r="E348" s="9" t="s">
+    </row>
+    <row r="349" customHeight="1" ht="15.0">
+      <c r="A349" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="F348" s="10" t="s">
+      <c r="B349" s="6" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="349" customHeight="1" ht="15.0">
-      <c r="A349" s="11"/>
-      <c r="B349" s="12"/>
-      <c r="C349" s="12"/>
-      <c r="D349" s="12"/>
-      <c r="E349" s="13" t="s">
+      <c r="C349" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="D349" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="F349" s="14" t="s">
+      <c r="E349" s="9" t="s">
         <v>782</v>
+      </c>
+      <c r="F349" s="10" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="350" customHeight="1" ht="15.0">
@@ -8684,10 +8836,10 @@
       <c r="C350" s="12"/>
       <c r="D350" s="12"/>
       <c r="E350" s="13" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F350" s="14" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="351" customHeight="1" ht="15.0">
@@ -8696,34 +8848,34 @@
       <c r="C351" s="12"/>
       <c r="D351" s="12"/>
       <c r="E351" s="13" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F351" s="14" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="352" customHeight="1" ht="22.0">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="352" customHeight="1" ht="15.0">
       <c r="A352" s="11"/>
       <c r="B352" s="12"/>
       <c r="C352" s="12"/>
       <c r="D352" s="12"/>
       <c r="E352" s="13" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F352" s="14" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="353" customHeight="1" ht="78.0">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="353" customHeight="1" ht="22.0">
       <c r="A353" s="11"/>
       <c r="B353" s="12"/>
       <c r="C353" s="12"/>
       <c r="D353" s="12"/>
       <c r="E353" s="13" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="F353" s="14" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="354" customHeight="1" ht="78.0">
@@ -8732,54 +8884,54 @@
       <c r="C354" s="12"/>
       <c r="D354" s="12"/>
       <c r="E354" s="13" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F354" s="14" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="355" customHeight="1" ht="177.0">
-      <c r="A355" s="15"/>
-      <c r="B355" s="16"/>
-      <c r="C355" s="16"/>
-      <c r="D355" s="16"/>
-      <c r="E355" s="17" t="s">
         <v>793</v>
       </c>
-      <c r="F355" s="35" t="s">
+    </row>
+    <row r="355" customHeight="1" ht="78.0">
+      <c r="A355" s="11"/>
+      <c r="B355" s="12"/>
+      <c r="C355" s="12"/>
+      <c r="D355" s="12"/>
+      <c r="E355" s="13" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="356" customHeight="1" ht="15.0">
-      <c r="A356" s="19" t="s">
+      <c r="F355" s="14" t="s">
         <v>795</v>
       </c>
-      <c r="B356" s="20" t="s">
+    </row>
+    <row r="356" customHeight="1" ht="177.0">
+      <c r="A356" s="15"/>
+      <c r="B356" s="16"/>
+      <c r="C356" s="16"/>
+      <c r="D356" s="16"/>
+      <c r="E356" s="17" t="s">
         <v>796</v>
       </c>
-      <c r="C356" s="21" t="s">
-        <v>541</v>
-      </c>
-      <c r="D356" s="22" t="s">
+      <c r="F356" s="35" t="s">
         <v>797</v>
       </c>
-      <c r="E356" s="23" t="s">
+    </row>
+    <row r="357" customHeight="1" ht="15.0">
+      <c r="A357" s="19" t="s">
         <v>798</v>
       </c>
-      <c r="F356" s="24" t="s">
+      <c r="B357" s="20" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="357" customHeight="1" ht="15.0">
-      <c r="A357" s="11"/>
-      <c r="B357" s="12"/>
-      <c r="C357" s="12"/>
-      <c r="D357" s="12"/>
-      <c r="E357" s="25" t="s">
+      <c r="C357" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="D357" s="22" t="s">
         <v>800</v>
       </c>
-      <c r="F357" s="26" t="s">
+      <c r="E357" s="23" t="s">
         <v>801</v>
+      </c>
+      <c r="F357" s="24" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="358" customHeight="1" ht="15.0">
@@ -8788,10 +8940,10 @@
       <c r="C358" s="12"/>
       <c r="D358" s="12"/>
       <c r="E358" s="25" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F358" s="26" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="359" customHeight="1" ht="15.0">
@@ -8800,10 +8952,10 @@
       <c r="C359" s="12"/>
       <c r="D359" s="12"/>
       <c r="E359" s="25" t="s">
-        <v>762</v>
+        <v>805</v>
       </c>
       <c r="F359" s="26" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="360" customHeight="1" ht="15.0">
@@ -8812,10 +8964,10 @@
       <c r="C360" s="12"/>
       <c r="D360" s="12"/>
       <c r="E360" s="25" t="s">
-        <v>805</v>
+        <v>765</v>
       </c>
       <c r="F360" s="26" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="361" customHeight="1" ht="15.0">
@@ -8824,10 +8976,10 @@
       <c r="C361" s="12"/>
       <c r="D361" s="12"/>
       <c r="E361" s="25" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="F361" s="26" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="362" customHeight="1" ht="15.0">
@@ -8836,10 +8988,10 @@
       <c r="C362" s="12"/>
       <c r="D362" s="12"/>
       <c r="E362" s="25" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F362" s="26" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="363" customHeight="1" ht="15.0">
@@ -8848,10 +9000,10 @@
       <c r="C363" s="12"/>
       <c r="D363" s="12"/>
       <c r="E363" s="25" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="F363" s="26" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="364" customHeight="1" ht="15.0">
@@ -8860,10 +9012,10 @@
       <c r="C364" s="12"/>
       <c r="D364" s="12"/>
       <c r="E364" s="25" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="F364" s="26" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="365" customHeight="1" ht="15.0">
@@ -8872,34 +9024,34 @@
       <c r="C365" s="12"/>
       <c r="D365" s="12"/>
       <c r="E365" s="25" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F365" s="26" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="366" customHeight="1" ht="88.0">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="366" customHeight="1" ht="15.0">
       <c r="A366" s="11"/>
       <c r="B366" s="12"/>
       <c r="C366" s="12"/>
       <c r="D366" s="12"/>
       <c r="E366" s="25" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F366" s="26" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="367" customHeight="1" ht="42.0">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="367" customHeight="1" ht="88.0">
       <c r="A367" s="11"/>
       <c r="B367" s="12"/>
       <c r="C367" s="12"/>
       <c r="D367" s="12"/>
       <c r="E367" s="25" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F367" s="26" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="368" customHeight="1" ht="42.0">
@@ -8908,22 +9060,22 @@
       <c r="C368" s="12"/>
       <c r="D368" s="12"/>
       <c r="E368" s="25" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F368" s="26" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="369" customHeight="1" ht="15.0">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="369" customHeight="1" ht="42.0">
       <c r="A369" s="11"/>
       <c r="B369" s="12"/>
       <c r="C369" s="12"/>
       <c r="D369" s="12"/>
       <c r="E369" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F369" s="26" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="370" customHeight="1" ht="15.0">
@@ -8932,78 +9084,78 @@
       <c r="C370" s="12"/>
       <c r="D370" s="12"/>
       <c r="E370" s="25" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F370" s="26" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="371" customHeight="1" ht="53.0">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="371" customHeight="1" ht="15.0">
       <c r="A371" s="11"/>
       <c r="B371" s="12"/>
       <c r="C371" s="12"/>
       <c r="D371" s="12"/>
       <c r="E371" s="25" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F371" s="26" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="372" customHeight="1" ht="105.0">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="372" customHeight="1" ht="53.0">
       <c r="A372" s="11"/>
       <c r="B372" s="12"/>
       <c r="C372" s="12"/>
       <c r="D372" s="12"/>
       <c r="E372" s="25" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F372" s="26" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="373" customHeight="1" ht="15.0">
-      <c r="A373" s="15"/>
-      <c r="B373" s="16"/>
-      <c r="C373" s="16"/>
-      <c r="D373" s="16"/>
-      <c r="E373" s="27" t="s">
         <v>831</v>
       </c>
-      <c r="F373" s="28" t="s">
+    </row>
+    <row r="373" customHeight="1" ht="105.0">
+      <c r="A373" s="11"/>
+      <c r="B373" s="12"/>
+      <c r="C373" s="12"/>
+      <c r="D373" s="12"/>
+      <c r="E373" s="25" t="s">
         <v>832</v>
       </c>
+      <c r="F373" s="26" t="s">
+        <v>833</v>
+      </c>
     </row>
     <row r="374" customHeight="1" ht="15.0">
-      <c r="A374" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="B374" s="36" t="s">
+      <c r="A374" s="15"/>
+      <c r="B374" s="16"/>
+      <c r="C374" s="16"/>
+      <c r="D374" s="16"/>
+      <c r="E374" s="27" t="s">
         <v>834</v>
       </c>
-      <c r="C374" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="D374" s="8" t="s">
+      <c r="F374" s="28" t="s">
         <v>835</v>
       </c>
-      <c r="E374" s="9" t="s">
+    </row>
+    <row r="375" customHeight="1" ht="15.0">
+      <c r="A375" s="5" t="s">
         <v>836</v>
       </c>
-      <c r="F374" s="10" t="s">
+      <c r="B375" s="36" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="375" customHeight="1" ht="15.0">
-      <c r="A375" s="11"/>
-      <c r="B375" s="38"/>
-      <c r="C375" s="39"/>
-      <c r="D375" s="12"/>
-      <c r="E375" s="13" t="s">
+      <c r="C375" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="D375" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="F375" s="14" t="s">
+      <c r="E375" s="9" t="s">
         <v>839</v>
+      </c>
+      <c r="F375" s="10" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="376" customHeight="1" ht="15.0">
@@ -9012,10 +9164,10 @@
       <c r="C376" s="39"/>
       <c r="D376" s="12"/>
       <c r="E376" s="13" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F376" s="14" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="377" customHeight="1" ht="15.0">
@@ -9024,10 +9176,10 @@
       <c r="C377" s="39"/>
       <c r="D377" s="12"/>
       <c r="E377" s="13" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F377" s="14" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="378" customHeight="1" ht="15.0">
@@ -9036,10 +9188,10 @@
       <c r="C378" s="39"/>
       <c r="D378" s="12"/>
       <c r="E378" s="13" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F378" s="14" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="379" customHeight="1" ht="15.0">
@@ -9048,10 +9200,10 @@
       <c r="C379" s="39"/>
       <c r="D379" s="12"/>
       <c r="E379" s="13" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F379" s="14" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="380" customHeight="1" ht="15.0">
@@ -9060,10 +9212,10 @@
       <c r="C380" s="39"/>
       <c r="D380" s="12"/>
       <c r="E380" s="13" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F380" s="14" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="381" customHeight="1" ht="15.0">
@@ -9072,10 +9224,10 @@
       <c r="C381" s="39"/>
       <c r="D381" s="12"/>
       <c r="E381" s="13" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F381" s="14" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="382" customHeight="1" ht="15.0">
@@ -9084,10 +9236,10 @@
       <c r="C382" s="39"/>
       <c r="D382" s="12"/>
       <c r="E382" s="13" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F382" s="14" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="383" customHeight="1" ht="15.0">
@@ -9096,10 +9248,10 @@
       <c r="C383" s="39"/>
       <c r="D383" s="12"/>
       <c r="E383" s="13" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F383" s="14" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="384" customHeight="1" ht="15.0">
@@ -9108,10 +9260,10 @@
       <c r="C384" s="39"/>
       <c r="D384" s="12"/>
       <c r="E384" s="13" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F384" s="14" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="385" customHeight="1" ht="15.0">
@@ -9120,10 +9272,10 @@
       <c r="C385" s="39"/>
       <c r="D385" s="12"/>
       <c r="E385" s="13" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F385" s="14" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="386" customHeight="1" ht="15.0">
@@ -9132,10 +9284,10 @@
       <c r="C386" s="39"/>
       <c r="D386" s="12"/>
       <c r="E386" s="13" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F386" s="14" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="387" customHeight="1" ht="15.0">
@@ -9144,10 +9296,10 @@
       <c r="C387" s="39"/>
       <c r="D387" s="12"/>
       <c r="E387" s="13" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F387" s="14" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="388" customHeight="1" ht="15.0">
@@ -9156,10 +9308,10 @@
       <c r="C388" s="39"/>
       <c r="D388" s="12"/>
       <c r="E388" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F388" s="14" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="389" customHeight="1" ht="15.0">
@@ -9168,10 +9320,10 @@
       <c r="C389" s="39"/>
       <c r="D389" s="12"/>
       <c r="E389" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="F389" s="14" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="390" customHeight="1" ht="15.0">
@@ -9180,10 +9332,10 @@
       <c r="C390" s="39"/>
       <c r="D390" s="12"/>
       <c r="E390" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F390" s="14" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="391" customHeight="1" ht="15.0">
@@ -9192,10 +9344,10 @@
       <c r="C391" s="39"/>
       <c r="D391" s="12"/>
       <c r="E391" s="13" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="F391" s="14" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="392" customHeight="1" ht="15.0">
@@ -9204,10 +9356,10 @@
       <c r="C392" s="39"/>
       <c r="D392" s="12"/>
       <c r="E392" s="13" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F392" s="14" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="393" customHeight="1" ht="15.0">
@@ -9216,10 +9368,10 @@
       <c r="C393" s="39"/>
       <c r="D393" s="12"/>
       <c r="E393" s="13" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F393" s="14" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="394" customHeight="1" ht="15.0">
@@ -9227,53 +9379,54 @@
       <c r="B394" s="38"/>
       <c r="C394" s="39"/>
       <c r="D394" s="12"/>
-      <c r="E394" s="40" t="s">
-        <v>876</v>
-      </c>
-      <c r="F394" s="41" t="s">
+      <c r="E394" s="13" t="s">
         <v>877</v>
       </c>
+      <c r="F394" s="14" t="s">
+        <v>878</v>
+      </c>
     </row>
     <row r="395" customHeight="1" ht="15.0">
-      <c r="A395" s="15"/>
-      <c r="B395" s="42"/>
+      <c r="A395" s="11"/>
+      <c r="B395" s="38"/>
       <c r="C395" s="39"/>
-      <c r="D395" s="16"/>
-      <c r="E395" s="43" t="s">
-        <v>878</v>
-      </c>
-      <c r="F395" s="44" t="s">
+      <c r="D395" s="12"/>
+      <c r="E395" s="40" t="s">
         <v>879</v>
       </c>
-      <c r="G395" s="45"/>
+      <c r="F395" s="41" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="396" customHeight="1" ht="15.0">
-      <c r="A396" s="46" t="s">
-        <v>880</v>
-      </c>
-      <c r="B396" s="47" t="s">
+      <c r="A396" s="15"/>
+      <c r="B396" s="42"/>
+      <c r="C396" s="39"/>
+      <c r="D396" s="16"/>
+      <c r="E396" s="43" t="s">
         <v>881</v>
       </c>
-      <c r="C396" s="48"/>
-      <c r="D396" s="49" t="s">
+      <c r="F396" s="44" t="s">
         <v>882</v>
       </c>
-      <c r="E396" s="50" t="s">
+      <c r="G396" s="45"/>
+    </row>
+    <row r="397" customHeight="1" ht="15.0">
+      <c r="A397" s="46" t="s">
         <v>883</v>
       </c>
-      <c r="F396" s="51" t="s">
+      <c r="B397" s="47" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="397" customHeight="1" ht="15.0">
-      <c r="B397" s="39"/>
-      <c r="C397" s="39"/>
-      <c r="D397" s="52"/>
-      <c r="E397" s="25" t="s">
+      <c r="C397" s="48"/>
+      <c r="D397" s="49" t="s">
         <v>885</v>
       </c>
-      <c r="F397" s="26" t="s">
+      <c r="E397" s="50" t="s">
         <v>886</v>
+      </c>
+      <c r="F397" s="51" t="s">
+        <v>887</v>
       </c>
     </row>
     <row r="398" customHeight="1" ht="15.0">
@@ -9281,10 +9434,10 @@
       <c r="C398" s="39"/>
       <c r="D398" s="52"/>
       <c r="E398" s="25" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="F398" s="26" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="399" customHeight="1" ht="15.0">
@@ -9292,32 +9445,32 @@
       <c r="C399" s="39"/>
       <c r="D399" s="52"/>
       <c r="E399" s="25" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F399" s="26" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="400" customHeight="1" ht="19.0">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="400" customHeight="1" ht="15.0">
       <c r="B400" s="39"/>
       <c r="C400" s="39"/>
       <c r="D400" s="52"/>
       <c r="E400" s="25" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="F400" s="26" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="401" customHeight="1" ht="15.0">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="401" customHeight="1" ht="19.0">
       <c r="B401" s="39"/>
       <c r="C401" s="39"/>
       <c r="D401" s="52"/>
       <c r="E401" s="25" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F401" s="26" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="402" customHeight="1" ht="15.0">
@@ -9325,10 +9478,10 @@
       <c r="C402" s="39"/>
       <c r="D402" s="52"/>
       <c r="E402" s="25" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="F402" s="26" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="403" customHeight="1" ht="15.0">
@@ -9336,90 +9489,88 @@
       <c r="C403" s="39"/>
       <c r="D403" s="52"/>
       <c r="E403" s="25" t="s">
-        <v>294</v>
+        <v>898</v>
       </c>
       <c r="F403" s="26" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="404" customHeight="1" ht="15.0">
       <c r="B404" s="39"/>
       <c r="C404" s="39"/>
-      <c r="D404" s="53"/>
-      <c r="E404" s="54" t="s">
-        <v>292</v>
-      </c>
-      <c r="F404" s="55" t="s">
-        <v>898</v>
+      <c r="D404" s="52"/>
+      <c r="E404" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="F404" s="26" t="s">
+        <v>900</v>
       </c>
     </row>
     <row r="405" customHeight="1" ht="15.0">
       <c r="B405" s="39"/>
       <c r="C405" s="39"/>
-      <c r="D405" s="56" t="s">
-        <v>899</v>
-      </c>
+      <c r="D405" s="53"/>
       <c r="E405" s="54" t="s">
-        <v>668</v>
+        <v>295</v>
       </c>
       <c r="F405" s="55" t="s">
-        <v>900</v>
-      </c>
-      <c r="G405" s="45"/>
+        <v>901</v>
+      </c>
     </row>
     <row r="406" customHeight="1" ht="15.0">
       <c r="B406" s="39"/>
       <c r="C406" s="39"/>
-      <c r="D406" s="52"/>
+      <c r="D406" s="56" t="s">
+        <v>902</v>
+      </c>
       <c r="E406" s="54" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F406" s="55" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="G406" s="45"/>
     </row>
-    <row r="407" customHeight="1" ht="24.0">
-      <c r="A407" s="57"/>
-      <c r="B407" s="58"/>
+    <row r="407" customHeight="1" ht="15.0">
+      <c r="B407" s="39"/>
       <c r="C407" s="39"/>
-      <c r="D407" s="53"/>
+      <c r="D407" s="52"/>
       <c r="E407" s="54" t="s">
-        <v>902</v>
+        <v>673</v>
       </c>
       <c r="F407" s="55" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="G407" s="45"/>
     </row>
     <row r="408" customHeight="1" ht="24.0">
-      <c r="A408" s="59">
+      <c r="A408" s="57"/>
+      <c r="B408" s="58"/>
+      <c r="C408" s="39"/>
+      <c r="D408" s="53"/>
+      <c r="E408" s="54" t="s">
+        <v>905</v>
+      </c>
+      <c r="F408" s="55" t="s">
+        <v>906</v>
+      </c>
+      <c r="G408" s="45"/>
+    </row>
+    <row r="409" customHeight="1" ht="24.0">
+      <c r="A409" s="59">
         <v>35.0</v>
       </c>
-      <c r="B408" s="37" t="s">
-        <v>904</v>
-      </c>
-      <c r="C408" s="60"/>
-      <c r="D408" s="61" t="s">
-        <v>905</v>
-      </c>
-      <c r="E408" s="62" t="s">
-        <v>906</v>
-      </c>
-      <c r="F408" s="63"/>
-      <c r="G408" s="45"/>
-    </row>
-    <row r="409" customHeight="1" ht="24.0">
-      <c r="A409" s="64"/>
-      <c r="B409" s="60"/>
+      <c r="B409" s="37" t="s">
+        <v>907</v>
+      </c>
       <c r="C409" s="60"/>
-      <c r="D409" s="65"/>
-      <c r="E409" s="66" t="s">
-        <v>907</v>
-      </c>
-      <c r="F409" s="67" t="s">
+      <c r="D409" s="61" t="s">
         <v>908</v>
       </c>
+      <c r="E409" s="62" t="s">
+        <v>909</v>
+      </c>
+      <c r="F409" s="63"/>
       <c r="G409" s="45"/>
     </row>
     <row r="410" customHeight="1" ht="24.0">
@@ -9428,10 +9579,10 @@
       <c r="C410" s="60"/>
       <c r="D410" s="65"/>
       <c r="E410" s="66" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="F410" s="67" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="G410" s="45"/>
     </row>
@@ -9441,10 +9592,10 @@
       <c r="C411" s="60"/>
       <c r="D411" s="65"/>
       <c r="E411" s="66" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="F411" s="67" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="G411" s="45"/>
     </row>
@@ -9454,10 +9605,10 @@
       <c r="C412" s="60"/>
       <c r="D412" s="65"/>
       <c r="E412" s="66" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="F412" s="67" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="G412" s="45"/>
     </row>
@@ -9467,10 +9618,10 @@
       <c r="C413" s="60"/>
       <c r="D413" s="65"/>
       <c r="E413" s="66" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F413" s="67" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="G413" s="45"/>
     </row>
@@ -9480,10 +9631,10 @@
       <c r="C414" s="60"/>
       <c r="D414" s="65"/>
       <c r="E414" s="66" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F414" s="67" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="G414" s="45"/>
     </row>
@@ -9493,10 +9644,10 @@
       <c r="C415" s="60"/>
       <c r="D415" s="65"/>
       <c r="E415" s="66" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F415" s="67" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="G415" s="45"/>
     </row>
@@ -9505,47 +9656,49 @@
       <c r="B416" s="60"/>
       <c r="C416" s="60"/>
       <c r="D416" s="65"/>
-      <c r="E416" s="68" t="s">
-        <v>921</v>
-      </c>
-      <c r="F416" s="69" t="s">
+      <c r="E416" s="66" t="s">
         <v>922</v>
       </c>
+      <c r="F416" s="67" t="s">
+        <v>923</v>
+      </c>
       <c r="G416" s="45"/>
     </row>
-    <row r="417" customHeight="1" ht="36.0">
+    <row r="417" customHeight="1" ht="24.0">
       <c r="A417" s="64"/>
       <c r="B417" s="60"/>
       <c r="C417" s="60"/>
       <c r="D417" s="65"/>
       <c r="E417" s="68" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F417" s="69" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="G417" s="45"/>
     </row>
-    <row r="418" customHeight="1" ht="15.0">
-      <c r="B418" s="39"/>
-      <c r="C418" s="39"/>
-      <c r="D418" s="52"/>
-      <c r="E418" s="70" t="s">
-        <v>925</v>
-      </c>
-      <c r="F418" s="14" t="s">
+    <row r="418" customHeight="1" ht="36.0">
+      <c r="A418" s="64"/>
+      <c r="B418" s="60"/>
+      <c r="C418" s="60"/>
+      <c r="D418" s="65"/>
+      <c r="E418" s="68" t="s">
         <v>926</v>
       </c>
+      <c r="F418" s="69" t="s">
+        <v>927</v>
+      </c>
+      <c r="G418" s="45"/>
     </row>
     <row r="419" customHeight="1" ht="15.0">
       <c r="B419" s="39"/>
       <c r="C419" s="39"/>
       <c r="D419" s="52"/>
       <c r="E419" s="70" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F419" s="14" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="420" customHeight="1" ht="15.0">
@@ -9553,10 +9706,10 @@
       <c r="C420" s="39"/>
       <c r="D420" s="52"/>
       <c r="E420" s="70" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F420" s="14" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="421" customHeight="1" ht="15.0">
@@ -9564,76 +9717,74 @@
       <c r="C421" s="39"/>
       <c r="D421" s="52"/>
       <c r="E421" s="70" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F421" s="14" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="422" customHeight="1" ht="15.0">
-      <c r="A422" s="54"/>
-      <c r="B422" s="55"/>
-      <c r="C422" s="54"/>
-      <c r="D422" s="71"/>
-      <c r="E422" s="52"/>
-      <c r="F422" s="45"/>
-      <c r="G422" s="45"/>
+      <c r="B422" s="39"/>
+      <c r="C422" s="39"/>
+      <c r="D422" s="52"/>
+      <c r="E422" s="70" t="s">
+        <v>934</v>
+      </c>
+      <c r="F422" s="14" t="s">
+        <v>935</v>
+      </c>
     </row>
     <row r="423" customHeight="1" ht="15.0">
-      <c r="A423" s="72">
+      <c r="A423" s="54"/>
+      <c r="B423" s="55"/>
+      <c r="C423" s="54"/>
+      <c r="D423" s="71"/>
+      <c r="E423" s="52"/>
+      <c r="F423" s="45"/>
+      <c r="G423" s="45"/>
+    </row>
+    <row r="424" customHeight="1" ht="15.0">
+      <c r="A424" s="72">
         <v>36.0</v>
       </c>
-      <c r="B423" s="73">
+      <c r="B424" s="73">
         <v>46107.0</v>
       </c>
-      <c r="C423" s="72" t="s">
-        <v>933</v>
-      </c>
-      <c r="D423" s="72"/>
-      <c r="E423" s="43" t="s">
-        <v>934</v>
-      </c>
-      <c r="F423" s="44" t="s">
-        <v>935</v>
-      </c>
-      <c r="G423" s="45"/>
-    </row>
-    <row r="424" customHeight="1" ht="15.0">
-      <c r="A424" s="52"/>
-      <c r="B424" s="52"/>
-      <c r="C424" s="52"/>
-      <c r="D424" s="52"/>
+      <c r="C424" s="72" t="s">
+        <v>936</v>
+      </c>
+      <c r="D424" s="72"/>
       <c r="E424" s="43" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F424" s="44" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="G424" s="45"/>
     </row>
-    <row r="425" customHeight="1" ht="31.0">
+    <row r="425" customHeight="1" ht="15.0">
       <c r="A425" s="52"/>
       <c r="B425" s="52"/>
       <c r="C425" s="52"/>
       <c r="D425" s="52"/>
       <c r="E425" s="43" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F425" s="44" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="G425" s="45"/>
     </row>
-    <row r="426" customHeight="1" ht="15.0">
+    <row r="426" customHeight="1" ht="31.0">
       <c r="A426" s="52"/>
       <c r="B426" s="52"/>
       <c r="C426" s="52"/>
       <c r="D426" s="52"/>
       <c r="E426" s="43" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F426" s="44" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G426" s="45"/>
     </row>
@@ -9643,10 +9794,10 @@
       <c r="C427" s="52"/>
       <c r="D427" s="52"/>
       <c r="E427" s="43" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F427" s="44" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="G427" s="45"/>
     </row>
@@ -9656,10 +9807,10 @@
       <c r="C428" s="52"/>
       <c r="D428" s="52"/>
       <c r="E428" s="43" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F428" s="44" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G428" s="45"/>
     </row>
@@ -9669,10 +9820,10 @@
       <c r="C429" s="52"/>
       <c r="D429" s="52"/>
       <c r="E429" s="43" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F429" s="44" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="G429" s="45"/>
     </row>
@@ -9682,10 +9833,10 @@
       <c r="C430" s="52"/>
       <c r="D430" s="52"/>
       <c r="E430" s="43" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F430" s="44" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="G430" s="45"/>
     </row>
@@ -9695,10 +9846,10 @@
       <c r="C431" s="52"/>
       <c r="D431" s="52"/>
       <c r="E431" s="43" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F431" s="44" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="G431" s="45"/>
     </row>
@@ -9708,10 +9859,10 @@
       <c r="C432" s="52"/>
       <c r="D432" s="52"/>
       <c r="E432" s="43" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F432" s="44" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="G432" s="45"/>
     </row>
@@ -9721,11 +9872,12 @@
       <c r="C433" s="52"/>
       <c r="D433" s="52"/>
       <c r="E433" s="43" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F433" s="44" t="s">
-        <v>955</v>
-      </c>
+        <v>956</v>
+      </c>
+      <c r="G433" s="45"/>
     </row>
     <row r="434" customHeight="1" ht="15.0">
       <c r="A434" s="52"/>
@@ -9733,10 +9885,10 @@
       <c r="C434" s="52"/>
       <c r="D434" s="52"/>
       <c r="E434" s="43" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F434" s="44" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="435" customHeight="1" ht="15.0">
@@ -9745,10 +9897,10 @@
       <c r="C435" s="52"/>
       <c r="D435" s="52"/>
       <c r="E435" s="43" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F435" s="44" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="436" customHeight="1" ht="15.0">
@@ -9757,52 +9909,52 @@
       <c r="C436" s="52"/>
       <c r="D436" s="52"/>
       <c r="E436" s="43" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F436" s="44" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="437" customHeight="1" ht="15.0">
-      <c r="A437" s="53"/>
+      <c r="A437" s="52"/>
       <c r="B437" s="52"/>
       <c r="C437" s="52"/>
       <c r="D437" s="52"/>
       <c r="E437" s="43" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F437" s="44" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="438" customHeight="1" ht="15.0">
-      <c r="A438" s="74">
+      <c r="A438" s="53"/>
+      <c r="B438" s="52"/>
+      <c r="C438" s="52"/>
+      <c r="D438" s="52"/>
+      <c r="E438" s="43" t="s">
+        <v>965</v>
+      </c>
+      <c r="F438" s="44" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="439" customHeight="1" ht="15.0">
+      <c r="A439" s="74">
         <v>37.0</v>
       </c>
-      <c r="B438" s="75">
+      <c r="B439" s="75">
         <v>46108</v>
       </c>
-      <c r="C438" s="76" t="s">
-        <v>330</v>
-      </c>
-      <c r="D438" s="72"/>
-      <c r="E438" s="77" t="s">
-        <v>459</v>
-      </c>
-      <c r="F438" s="25" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="439" customHeight="1" ht="15.0">
-      <c r="A439" s="78"/>
-      <c r="B439" s="79"/>
-      <c r="C439" s="80"/>
-      <c r="D439" s="81"/>
+      <c r="C439" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="D439" s="72"/>
       <c r="E439" s="77" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F439" s="25" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="440" customHeight="1" ht="15.0">
@@ -9811,10 +9963,10 @@
       <c r="C440" s="80"/>
       <c r="D440" s="81"/>
       <c r="E440" s="77" t="s">
-        <v>966</v>
+        <v>464</v>
       </c>
       <c r="F440" s="25" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="441" customHeight="1" ht="15.0">
@@ -9823,10 +9975,10 @@
       <c r="C441" s="80"/>
       <c r="D441" s="81"/>
       <c r="E441" s="77" t="s">
-        <v>410</v>
+        <v>969</v>
       </c>
       <c r="F441" s="25" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="442" customHeight="1" ht="15.0">
@@ -9835,10 +9987,10 @@
       <c r="C442" s="80"/>
       <c r="D442" s="81"/>
       <c r="E442" s="77" t="s">
-        <v>969</v>
+        <v>413</v>
       </c>
       <c r="F442" s="25" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="443" customHeight="1" ht="15.0">
@@ -9847,10 +9999,10 @@
       <c r="C443" s="80"/>
       <c r="D443" s="81"/>
       <c r="E443" s="77" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F443" s="25" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="444" customHeight="1" ht="15.0">
@@ -9859,10 +10011,10 @@
       <c r="C444" s="80"/>
       <c r="D444" s="81"/>
       <c r="E444" s="77" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F444" s="25" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="445" customHeight="1" ht="15.0">
@@ -9871,10 +10023,10 @@
       <c r="C445" s="80"/>
       <c r="D445" s="81"/>
       <c r="E445" s="77" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F445" s="25" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="446" customHeight="1" ht="15.0">
@@ -9883,12 +10035,11 @@
       <c r="C446" s="80"/>
       <c r="D446" s="81"/>
       <c r="E446" s="77" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F446" s="25" t="s">
-        <v>978</v>
-      </c>
-      <c r="G446" s="82"/>
+        <v>979</v>
+      </c>
     </row>
     <row r="447" customHeight="1" ht="15.0">
       <c r="A447" s="78"/>
@@ -9896,11 +10047,12 @@
       <c r="C447" s="80"/>
       <c r="D447" s="81"/>
       <c r="E447" s="77" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F447" s="25" t="s">
-        <v>980</v>
-      </c>
+        <v>981</v>
+      </c>
+      <c r="G447" s="82"/>
     </row>
     <row r="448" customHeight="1" ht="15.0">
       <c r="A448" s="78"/>
@@ -9908,10 +10060,10 @@
       <c r="C448" s="80"/>
       <c r="D448" s="81"/>
       <c r="E448" s="77" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F448" s="25" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="449" customHeight="1" ht="15.0">
@@ -9920,10 +10072,10 @@
       <c r="C449" s="80"/>
       <c r="D449" s="81"/>
       <c r="E449" s="77" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F449" s="25" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="450" customHeight="1" ht="15.0">
@@ -9932,10 +10084,10 @@
       <c r="C450" s="80"/>
       <c r="D450" s="81"/>
       <c r="E450" s="77" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F450" s="25" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="451" customHeight="1" ht="15.0">
@@ -9944,10 +10096,10 @@
       <c r="C451" s="80"/>
       <c r="D451" s="81"/>
       <c r="E451" s="77" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F451" s="25" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="452" customHeight="1" ht="15.0">
@@ -9956,10 +10108,10 @@
       <c r="C452" s="80"/>
       <c r="D452" s="81"/>
       <c r="E452" s="77" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F452" s="25" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="453" customHeight="1" ht="15.0">
@@ -9968,10 +10120,10 @@
       <c r="C453" s="80"/>
       <c r="D453" s="81"/>
       <c r="E453" s="77" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F453" s="25" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="454" customHeight="1" ht="15.0">
@@ -9980,10 +10132,10 @@
       <c r="C454" s="80"/>
       <c r="D454" s="81"/>
       <c r="E454" s="77" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F454" s="25" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="455" customHeight="1" ht="15.0">
@@ -9992,10 +10144,10 @@
       <c r="C455" s="80"/>
       <c r="D455" s="81"/>
       <c r="E455" s="77" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F455" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="456" customHeight="1" ht="15.0">
@@ -10004,10 +10156,10 @@
       <c r="C456" s="80"/>
       <c r="D456" s="81"/>
       <c r="E456" s="77" t="s">
-        <v>433</v>
+        <v>998</v>
       </c>
       <c r="F456" s="25" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="457" customHeight="1" ht="15.0">
@@ -10016,10 +10168,10 @@
       <c r="C457" s="80"/>
       <c r="D457" s="81"/>
       <c r="E457" s="77" t="s">
-        <v>998</v>
+        <v>436</v>
       </c>
       <c r="F457" s="25" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="458" customHeight="1" ht="15.0">
@@ -10028,10 +10180,10 @@
       <c r="C458" s="80"/>
       <c r="D458" s="81"/>
       <c r="E458" s="77" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F458" s="25" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="459" customHeight="1" ht="15.0">
@@ -10040,10 +10192,10 @@
       <c r="C459" s="80"/>
       <c r="D459" s="81"/>
       <c r="E459" s="77" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F459" s="25" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="460" customHeight="1" ht="15.0">
@@ -10052,131 +10204,127 @@
       <c r="C460" s="80"/>
       <c r="D460" s="81"/>
       <c r="E460" s="77" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F460" s="25" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="461" customHeight="1" ht="30.0">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="461" customHeight="1" ht="15.0">
       <c r="A461" s="78"/>
       <c r="B461" s="79"/>
       <c r="C461" s="80"/>
       <c r="D461" s="81"/>
       <c r="E461" s="77" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F461" s="25" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="462" customHeight="1" ht="77.0">
-      <c r="A462" s="74">
-        <v>38.0</v>
-      </c>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="462" customHeight="1" ht="30.0">
+      <c r="A462" s="78"/>
       <c r="B462" s="79"/>
-      <c r="C462" s="83" t="s">
+      <c r="C462" s="80"/>
+      <c r="D462" s="81"/>
+      <c r="E462" s="77" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F462" s="25" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="463" customHeight="1" ht="77.0">
+      <c r="A463" s="78"/>
+      <c r="B463" s="79"/>
+      <c r="C463" s="83" t="s">
         <v>73</v>
       </c>
-      <c r="D462" s="84"/>
-      <c r="E462" s="77" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F462" s="25" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="463" customHeight="1" ht="117.0">
-      <c r="A463" s="85"/>
-      <c r="B463" s="79"/>
-      <c r="C463" s="81"/>
       <c r="D463" s="84"/>
       <c r="E463" s="77" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F463" s="25" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="464" customHeight="1" ht="150.0">
-      <c r="A464" s="85"/>
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="464" customHeight="1" ht="117.0">
+      <c r="A464" s="78"/>
       <c r="B464" s="79"/>
       <c r="C464" s="81"/>
       <c r="D464" s="84"/>
       <c r="E464" s="77" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F464" s="25" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="465" customHeight="1" ht="40.0">
-      <c r="A465" s="85"/>
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="465" customHeight="1" ht="150.0">
+      <c r="A465" s="78"/>
       <c r="B465" s="79"/>
       <c r="C465" s="81"/>
       <c r="D465" s="84"/>
       <c r="E465" s="77" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F465" s="25" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="466" customHeight="1" ht="15.0">
-      <c r="A466" s="85"/>
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="466" customHeight="1" ht="40.0">
+      <c r="A466" s="78"/>
       <c r="B466" s="79"/>
       <c r="C466" s="81"/>
       <c r="D466" s="84"/>
       <c r="E466" s="77" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F466" s="25" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="467" customHeight="1" ht="15.0">
-      <c r="A467" s="85"/>
+      <c r="A467" s="78"/>
       <c r="B467" s="79"/>
       <c r="C467" s="81"/>
       <c r="D467" s="84"/>
       <c r="E467" s="77" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F467" s="25" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="468" customHeight="1" ht="15.0">
-      <c r="A468" s="85"/>
+      <c r="A468" s="78"/>
       <c r="B468" s="79"/>
-      <c r="C468" s="86"/>
-      <c r="D468" s="87"/>
+      <c r="C468" s="81"/>
+      <c r="D468" s="84"/>
       <c r="E468" s="77" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F468" s="25" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="469" customHeight="1" ht="64.0">
-      <c r="A469" s="85"/>
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="469" customHeight="1" ht="15.0">
+      <c r="A469" s="78"/>
       <c r="B469" s="79"/>
-      <c r="C469" s="79"/>
-      <c r="D469" s="88"/>
+      <c r="C469" s="85"/>
+      <c r="D469" s="86"/>
       <c r="E469" s="77" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F469" s="25" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="470" customHeight="1" ht="53.0">
-      <c r="A470" s="85"/>
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="470" customHeight="1" ht="64.0">
+      <c r="A470" s="78"/>
       <c r="B470" s="79"/>
-      <c r="C470" s="89"/>
-      <c r="D470" s="90" t="s">
-        <v>1024</v>
-      </c>
+      <c r="C470" s="79"/>
+      <c r="D470" s="87"/>
       <c r="E470" s="77" t="s">
         <v>1025</v>
       </c>
@@ -10185,330 +10333,488 @@
       </c>
     </row>
     <row r="471" customHeight="1" ht="53.0">
-      <c r="A471" s="85"/>
+      <c r="A471" s="78"/>
       <c r="B471" s="79"/>
-      <c r="C471" s="89"/>
-      <c r="D471" s="91"/>
+      <c r="C471" s="88"/>
+      <c r="D471" s="89" t="s">
+        <v>1027</v>
+      </c>
       <c r="E471" s="77" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F471" s="25" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="472" customHeight="1" ht="63.0">
-      <c r="A472" s="85"/>
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="472" customHeight="1" ht="53.0">
+      <c r="A472" s="78"/>
       <c r="B472" s="79"/>
-      <c r="C472" s="89"/>
-      <c r="D472" s="91"/>
+      <c r="C472" s="88"/>
+      <c r="D472" s="90"/>
       <c r="E472" s="77" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F472" s="25" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="473" customHeight="1" ht="53.0">
-      <c r="A473" s="85"/>
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="473" customHeight="1" ht="63.0">
+      <c r="A473" s="78"/>
       <c r="B473" s="79"/>
-      <c r="C473" s="89"/>
-      <c r="D473" s="91"/>
+      <c r="C473" s="88"/>
+      <c r="D473" s="90"/>
       <c r="E473" s="77" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F473" s="25" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="474" customHeight="1" ht="60.0">
-      <c r="A474" s="85"/>
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="474" customHeight="1" ht="53.0">
+      <c r="A474" s="78"/>
       <c r="B474" s="79"/>
-      <c r="C474" s="89"/>
-      <c r="D474" s="91"/>
+      <c r="C474" s="88"/>
+      <c r="D474" s="90"/>
       <c r="E474" s="77" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F474" s="25" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="475" customHeight="1" ht="94.0">
-      <c r="A475" s="85"/>
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="475" customHeight="1" ht="60.0">
+      <c r="A475" s="78"/>
       <c r="B475" s="79"/>
-      <c r="C475" s="89"/>
-      <c r="D475" s="91"/>
+      <c r="C475" s="88"/>
+      <c r="D475" s="90"/>
       <c r="E475" s="77" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F475" s="25" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="476" customHeight="1" ht="24.0">
-      <c r="A476" s="85"/>
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="476" customHeight="1" ht="94.0">
+      <c r="A476" s="78"/>
       <c r="B476" s="79"/>
-      <c r="C476" s="89"/>
-      <c r="D476" s="91"/>
+      <c r="C476" s="88"/>
+      <c r="D476" s="90"/>
       <c r="E476" s="77" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F476" s="25" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="477" customHeight="1" ht="38.0">
-      <c r="A477" s="85"/>
-      <c r="B477" s="92"/>
-      <c r="C477" s="89"/>
-      <c r="D477" s="91"/>
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="477" customHeight="1" ht="24.0">
+      <c r="A477" s="78"/>
+      <c r="B477" s="79"/>
+      <c r="C477" s="88"/>
+      <c r="D477" s="90"/>
       <c r="E477" s="77" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F477" s="25" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="478" customHeight="1" ht="113.0">
-      <c r="A478" s="85"/>
-      <c r="B478" s="77"/>
-      <c r="C478" s="25"/>
-      <c r="D478" s="25"/>
-      <c r="E478" s="25" t="s">
         <v>1041</v>
       </c>
+    </row>
+    <row r="478" customHeight="1" ht="38.0">
+      <c r="A478" s="91"/>
+      <c r="B478" s="92"/>
+      <c r="C478" s="88"/>
+      <c r="D478" s="90"/>
+      <c r="E478" s="77" t="s">
+        <v>1042</v>
+      </c>
       <c r="F478" s="25" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="479" customHeight="1" ht="24.0">
-      <c r="A479" s="85"/>
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="479" customHeight="1" ht="113.0">
+      <c r="A479" s="93">
+        <v>38.0</v>
+      </c>
       <c r="B479" s="77"/>
       <c r="C479" s="25"/>
       <c r="D479" s="25"/>
       <c r="E479" s="25" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F479" s="25" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="480" customHeight="1" ht="40.0">
-      <c r="A480" s="85"/>
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="480" customHeight="1" ht="24.0">
+      <c r="A480" s="94"/>
       <c r="B480" s="77"/>
       <c r="C480" s="25"/>
       <c r="D480" s="25"/>
       <c r="E480" s="25" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F480" s="25" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="481" customHeight="1" ht="28.0">
-      <c r="A481" s="85"/>
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="481" customHeight="1" ht="40.0">
+      <c r="A481" s="94"/>
       <c r="B481" s="77"/>
       <c r="C481" s="25"/>
       <c r="D481" s="25"/>
       <c r="E481" s="25" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F481" s="25" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="482" customHeight="1" ht="68.0">
-      <c r="A482" s="85"/>
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="482" customHeight="1" ht="28.0">
+      <c r="A482" s="94"/>
       <c r="B482" s="77"/>
       <c r="C482" s="25"/>
       <c r="D482" s="25"/>
       <c r="E482" s="25" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F482" s="25" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="483" customHeight="1" ht="15.0">
-      <c r="A483" s="85"/>
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="483" customHeight="1" ht="68.0">
+      <c r="A483" s="94"/>
       <c r="B483" s="77"/>
       <c r="C483" s="25"/>
       <c r="D483" s="25"/>
       <c r="E483" s="25" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F483" s="25" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="484" customHeight="1" ht="15.0">
-      <c r="A484" s="85"/>
+      <c r="A484" s="94"/>
       <c r="B484" s="77"/>
       <c r="C484" s="25"/>
       <c r="D484" s="25"/>
-      <c r="E484" s="25"/>
-      <c r="F484" s="25"/>
-    </row>
-    <row r="485" customHeight="1" ht="15.0">
-      <c r="A485" s="85"/>
-      <c r="B485" s="77"/>
-      <c r="C485" s="25"/>
+      <c r="E484" s="25" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F484" s="25" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="485" customHeight="1" ht="40.0">
+      <c r="A485" s="94"/>
+      <c r="B485" s="95">
+        <v>46109</v>
+      </c>
+      <c r="C485" s="76" t="s">
+        <v>1056</v>
+      </c>
       <c r="D485" s="25"/>
-      <c r="E485" s="25"/>
-      <c r="F485" s="25"/>
+      <c r="E485" s="25" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F485" s="25" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="486" customHeight="1" ht="29.0">
+      <c r="A486" s="94"/>
+      <c r="B486" s="94"/>
+      <c r="C486" s="80"/>
+      <c r="D486" s="25"/>
+      <c r="E486" s="25" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F486" s="25" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="487" customHeight="1" ht="15.0">
+      <c r="A487" s="94"/>
+      <c r="B487" s="94"/>
+      <c r="C487" s="80"/>
+      <c r="D487" s="25"/>
+      <c r="E487" s="25" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F487" s="25" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="488" customHeight="1" ht="15.0">
+      <c r="A488" s="94"/>
+      <c r="B488" s="94"/>
+      <c r="C488" s="80"/>
+      <c r="D488" s="25"/>
+      <c r="E488" s="25" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F488" s="25" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="489" customHeight="1" ht="15.0">
+      <c r="A489" s="94"/>
+      <c r="B489" s="94"/>
+      <c r="C489" s="80"/>
+      <c r="D489" s="25"/>
+      <c r="E489" s="25" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F489" s="25" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="490" customHeight="1" ht="15.0">
+      <c r="A490" s="94"/>
+      <c r="B490" s="94"/>
+      <c r="C490" s="80"/>
+      <c r="D490" s="25"/>
+      <c r="E490" s="25" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F490" s="25" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="491" customHeight="1" ht="151.0">
+      <c r="A491" s="94"/>
+      <c r="B491" s="94"/>
+      <c r="C491" s="80"/>
+      <c r="D491" s="25"/>
+      <c r="E491" s="25" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F491" s="25" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="492" customHeight="1" ht="84.0">
+      <c r="A492" s="94"/>
+      <c r="B492" s="94"/>
+      <c r="C492" s="80"/>
+      <c r="D492" s="25"/>
+      <c r="E492" s="25" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F492" s="25" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="493" customHeight="1" ht="15.0">
+      <c r="A493" s="94"/>
+      <c r="B493" s="94"/>
+      <c r="C493" s="80"/>
+      <c r="D493" s="25"/>
+      <c r="E493" s="25"/>
+      <c r="F493" s="25"/>
+    </row>
+    <row r="494" customHeight="1" ht="15.0">
+      <c r="A494" s="94"/>
+      <c r="B494" s="94"/>
+      <c r="C494" s="80"/>
+      <c r="D494" s="25"/>
+      <c r="E494" s="25"/>
+      <c r="F494" s="25"/>
+    </row>
+    <row r="495" customHeight="1" ht="15.0">
+      <c r="A495" s="94"/>
+      <c r="B495" s="94"/>
+      <c r="C495" s="80"/>
+      <c r="D495" s="25"/>
+      <c r="E495" s="25"/>
+      <c r="F495" s="25"/>
+    </row>
+    <row r="496" customHeight="1" ht="15.0">
+      <c r="A496" s="94"/>
+      <c r="B496" s="94"/>
+      <c r="C496" s="80"/>
+      <c r="D496" s="25"/>
+      <c r="E496" s="25"/>
+      <c r="F496" s="25"/>
+    </row>
+    <row r="497" customHeight="1" ht="15.0">
+      <c r="A497" s="96"/>
+      <c r="B497" s="96"/>
+      <c r="C497" s="97"/>
+      <c r="D497" s="25"/>
+      <c r="E497" s="25"/>
+      <c r="F497" s="25"/>
+    </row>
+    <row r="498" customHeight="1" ht="15.0">
+      <c r="A498" s="77"/>
+      <c r="B498" s="77"/>
+      <c r="C498" s="25"/>
+      <c r="D498" s="25"/>
+      <c r="E498" s="25"/>
+      <c r="F498" s="25"/>
+    </row>
+    <row r="499" customHeight="1" ht="15.0">
+      <c r="A499" s="77"/>
+      <c r="B499" s="77"/>
+      <c r="C499" s="25"/>
+      <c r="D499" s="25"/>
+      <c r="E499" s="25"/>
+      <c r="F499" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="149">
+  <mergeCells count="151">
+    <mergeCell ref="A32:A57"/>
     <mergeCell ref="C71:C82"/>
-    <mergeCell ref="D126:D129"/>
-    <mergeCell ref="A27:A31"/>
     <mergeCell ref="A16:A26"/>
-    <mergeCell ref="D112:D124"/>
-    <mergeCell ref="A32:A57"/>
+    <mergeCell ref="D113:D125"/>
+    <mergeCell ref="C83:C112"/>
     <mergeCell ref="B62:B70"/>
-    <mergeCell ref="C83:C111"/>
     <mergeCell ref="B58:B61"/>
     <mergeCell ref="A3:A15"/>
+    <mergeCell ref="A27:A31"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D127:D130"/>
+    <mergeCell ref="A62:A70"/>
+    <mergeCell ref="B16:B26"/>
+    <mergeCell ref="C113:C125"/>
+    <mergeCell ref="C127:C130"/>
     <mergeCell ref="D71:D82"/>
-    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="B3:B15"/>
+    <mergeCell ref="D83:D112"/>
+    <mergeCell ref="B27:B31"/>
     <mergeCell ref="B32:B57"/>
-    <mergeCell ref="B3:B15"/>
-    <mergeCell ref="D83:D111"/>
-    <mergeCell ref="C112:C124"/>
-    <mergeCell ref="A62:A70"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="B16:B26"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="D62:D70"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="C32:C57"/>
     <mergeCell ref="D58:D61"/>
     <mergeCell ref="A71:A82"/>
-    <mergeCell ref="A83:A111"/>
-    <mergeCell ref="B112:B124"/>
+    <mergeCell ref="B127:B130"/>
     <mergeCell ref="C27:C31"/>
+    <mergeCell ref="C32:C57"/>
     <mergeCell ref="C16:C26"/>
     <mergeCell ref="C3:C15"/>
+    <mergeCell ref="B113:B125"/>
+    <mergeCell ref="D62:D70"/>
+    <mergeCell ref="A83:A112"/>
     <mergeCell ref="C62:C70"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="B71:B82"/>
+    <mergeCell ref="B83:B112"/>
+    <mergeCell ref="D16:D26"/>
+    <mergeCell ref="D3:D15"/>
+    <mergeCell ref="A113:A125"/>
     <mergeCell ref="D27:D31"/>
-    <mergeCell ref="D3:D15"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="D16:D26"/>
-    <mergeCell ref="B71:B82"/>
-    <mergeCell ref="B83:B111"/>
-    <mergeCell ref="A112:A124"/>
-    <mergeCell ref="A126:A129"/>
     <mergeCell ref="D32:D57"/>
-    <mergeCell ref="C216:C224"/>
-    <mergeCell ref="D243:D250"/>
-    <mergeCell ref="A141:A147"/>
-    <mergeCell ref="A133:A140"/>
-    <mergeCell ref="A130:A132"/>
-    <mergeCell ref="A148:A153"/>
-    <mergeCell ref="D251:D253"/>
-    <mergeCell ref="D254:D264"/>
-    <mergeCell ref="D230:D242"/>
-    <mergeCell ref="D225:D229"/>
-    <mergeCell ref="A154:A167"/>
-    <mergeCell ref="B168:B173"/>
-    <mergeCell ref="B174:B187"/>
-    <mergeCell ref="B188:B215"/>
-    <mergeCell ref="D216:D224"/>
-    <mergeCell ref="A168:A173"/>
-    <mergeCell ref="A174:A187"/>
-    <mergeCell ref="A188:A215"/>
-    <mergeCell ref="B130:B132"/>
-    <mergeCell ref="B154:B167"/>
-    <mergeCell ref="B141:B147"/>
-    <mergeCell ref="B148:B153"/>
-    <mergeCell ref="B133:B140"/>
-    <mergeCell ref="C251:C253"/>
-    <mergeCell ref="C254:C264"/>
-    <mergeCell ref="C225:C229"/>
-    <mergeCell ref="C230:C242"/>
-    <mergeCell ref="C243:C250"/>
-    <mergeCell ref="C148:C153"/>
-    <mergeCell ref="B225:B229"/>
-    <mergeCell ref="B230:B242"/>
-    <mergeCell ref="B243:B250"/>
-    <mergeCell ref="A216:A224"/>
-    <mergeCell ref="D188:D215"/>
-    <mergeCell ref="D174:D187"/>
-    <mergeCell ref="C133:C140"/>
-    <mergeCell ref="C141:C147"/>
-    <mergeCell ref="C130:C132"/>
-    <mergeCell ref="B251:B253"/>
-    <mergeCell ref="B254:B264"/>
-    <mergeCell ref="C154:C167"/>
-    <mergeCell ref="D168:D173"/>
-    <mergeCell ref="D148:D153"/>
-    <mergeCell ref="C168:C173"/>
-    <mergeCell ref="D133:D140"/>
-    <mergeCell ref="D130:D132"/>
-    <mergeCell ref="C174:C187"/>
-    <mergeCell ref="C188:C215"/>
-    <mergeCell ref="B216:B224"/>
-    <mergeCell ref="A243:A250"/>
-    <mergeCell ref="A230:A242"/>
-    <mergeCell ref="A225:A229"/>
-    <mergeCell ref="D141:D147"/>
-    <mergeCell ref="D154:D167"/>
-    <mergeCell ref="A254:A264"/>
-    <mergeCell ref="A251:A253"/>
-    <mergeCell ref="B319:B347"/>
-    <mergeCell ref="C348:C355"/>
-    <mergeCell ref="D374:D395"/>
-    <mergeCell ref="D356:D373"/>
-    <mergeCell ref="B306:B318"/>
-    <mergeCell ref="A284:A305"/>
-    <mergeCell ref="A265:A270"/>
-    <mergeCell ref="A271:A283"/>
-    <mergeCell ref="B265:B270"/>
-    <mergeCell ref="B284:B305"/>
-    <mergeCell ref="A319:A347"/>
-    <mergeCell ref="C374:C421"/>
-    <mergeCell ref="D348:D355"/>
-    <mergeCell ref="A306:A318"/>
-    <mergeCell ref="B271:B283"/>
-    <mergeCell ref="C356:C373"/>
-    <mergeCell ref="C271:C283"/>
-    <mergeCell ref="C265:C270"/>
-    <mergeCell ref="B356:B373"/>
-    <mergeCell ref="D319:D347"/>
-    <mergeCell ref="C284:C305"/>
-    <mergeCell ref="D306:D318"/>
-    <mergeCell ref="A348:A355"/>
-    <mergeCell ref="B374:B395"/>
-    <mergeCell ref="A374:A395"/>
-    <mergeCell ref="A356:A373"/>
-    <mergeCell ref="D265:D270"/>
-    <mergeCell ref="D271:D283"/>
-    <mergeCell ref="C306:C318"/>
-    <mergeCell ref="D284:D305"/>
-    <mergeCell ref="B348:B355"/>
-    <mergeCell ref="C319:C347"/>
-    <mergeCell ref="A396:A407"/>
-    <mergeCell ref="E265:E270"/>
-    <mergeCell ref="C462:C468"/>
-    <mergeCell ref="A408:A421"/>
-    <mergeCell ref="C469:C477"/>
-    <mergeCell ref="B438:B477"/>
-    <mergeCell ref="B423:B437"/>
-    <mergeCell ref="A423:A437"/>
-    <mergeCell ref="D470:D477"/>
-    <mergeCell ref="B396:B407"/>
-    <mergeCell ref="A438:A461"/>
-    <mergeCell ref="B408:B421"/>
-    <mergeCell ref="A462:A485"/>
-    <mergeCell ref="D423:D437"/>
-    <mergeCell ref="D438:D468"/>
-    <mergeCell ref="D405:D407"/>
-    <mergeCell ref="D408:D421"/>
-    <mergeCell ref="D396:D404"/>
-    <mergeCell ref="C423:C437"/>
-    <mergeCell ref="C438:C461"/>
+    <mergeCell ref="A127:A130"/>
+    <mergeCell ref="B175:B188"/>
+    <mergeCell ref="A134:A141"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A142:A148"/>
+    <mergeCell ref="A149:A154"/>
+    <mergeCell ref="D231:D243"/>
+    <mergeCell ref="A155:A168"/>
+    <mergeCell ref="B169:B174"/>
+    <mergeCell ref="D244:D251"/>
+    <mergeCell ref="D252:D254"/>
+    <mergeCell ref="D255:D265"/>
+    <mergeCell ref="B189:B216"/>
+    <mergeCell ref="C217:C225"/>
+    <mergeCell ref="D226:D230"/>
+    <mergeCell ref="D217:D225"/>
+    <mergeCell ref="C231:C243"/>
+    <mergeCell ref="A169:A174"/>
+    <mergeCell ref="B155:B168"/>
+    <mergeCell ref="A175:A188"/>
+    <mergeCell ref="A189:A216"/>
+    <mergeCell ref="C244:C251"/>
+    <mergeCell ref="B149:B154"/>
+    <mergeCell ref="C252:C254"/>
+    <mergeCell ref="C255:C265"/>
+    <mergeCell ref="B142:B148"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B134:B141"/>
+    <mergeCell ref="C226:C230"/>
+    <mergeCell ref="D169:D174"/>
+    <mergeCell ref="C155:C168"/>
+    <mergeCell ref="C149:C154"/>
+    <mergeCell ref="C142:C148"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="C134:C141"/>
+    <mergeCell ref="B226:B230"/>
+    <mergeCell ref="A217:A225"/>
+    <mergeCell ref="D189:D216"/>
+    <mergeCell ref="D175:D188"/>
+    <mergeCell ref="B252:B254"/>
+    <mergeCell ref="B255:B265"/>
+    <mergeCell ref="B244:B251"/>
+    <mergeCell ref="B231:B243"/>
+    <mergeCell ref="C169:C174"/>
+    <mergeCell ref="B217:B225"/>
+    <mergeCell ref="A226:A230"/>
+    <mergeCell ref="A231:A243"/>
+    <mergeCell ref="A255:A265"/>
+    <mergeCell ref="A252:A254"/>
+    <mergeCell ref="A244:A251"/>
+    <mergeCell ref="D134:D141"/>
+    <mergeCell ref="C175:C188"/>
+    <mergeCell ref="C189:C216"/>
+    <mergeCell ref="D131:D133"/>
+    <mergeCell ref="D155:D168"/>
+    <mergeCell ref="D142:D148"/>
+    <mergeCell ref="D149:D154"/>
+    <mergeCell ref="D357:D374"/>
+    <mergeCell ref="D375:D396"/>
+    <mergeCell ref="B320:B348"/>
+    <mergeCell ref="C349:C356"/>
+    <mergeCell ref="A266:A271"/>
+    <mergeCell ref="A272:A284"/>
+    <mergeCell ref="B307:B319"/>
+    <mergeCell ref="A285:A306"/>
+    <mergeCell ref="C357:C374"/>
+    <mergeCell ref="B285:B306"/>
+    <mergeCell ref="A320:A348"/>
+    <mergeCell ref="A307:A319"/>
+    <mergeCell ref="B266:B271"/>
+    <mergeCell ref="D349:D356"/>
+    <mergeCell ref="C375:C422"/>
+    <mergeCell ref="B272:B284"/>
+    <mergeCell ref="B375:B396"/>
+    <mergeCell ref="D307:D319"/>
+    <mergeCell ref="C285:C306"/>
+    <mergeCell ref="B357:B374"/>
+    <mergeCell ref="C266:C271"/>
+    <mergeCell ref="A349:A356"/>
+    <mergeCell ref="C272:C284"/>
+    <mergeCell ref="D320:D348"/>
+    <mergeCell ref="D266:D271"/>
+    <mergeCell ref="C320:C348"/>
+    <mergeCell ref="D272:D284"/>
+    <mergeCell ref="B349:B356"/>
+    <mergeCell ref="D285:D306"/>
+    <mergeCell ref="C307:C319"/>
+    <mergeCell ref="A357:A374"/>
+    <mergeCell ref="A375:A396"/>
+    <mergeCell ref="B424:B438"/>
+    <mergeCell ref="C470:C478"/>
+    <mergeCell ref="E266:E271"/>
+    <mergeCell ref="C463:C469"/>
+    <mergeCell ref="A409:A422"/>
+    <mergeCell ref="A397:A408"/>
+    <mergeCell ref="B439:B478"/>
+    <mergeCell ref="B397:B408"/>
+    <mergeCell ref="B409:B422"/>
+    <mergeCell ref="A424:A438"/>
+    <mergeCell ref="C485:C497"/>
+    <mergeCell ref="D471:D478"/>
+    <mergeCell ref="A439:A478"/>
+    <mergeCell ref="A479:A497"/>
+    <mergeCell ref="B485:B497"/>
+    <mergeCell ref="D439:D469"/>
+    <mergeCell ref="D424:D438"/>
+    <mergeCell ref="C424:C438"/>
+    <mergeCell ref="D406:D408"/>
+    <mergeCell ref="C439:C462"/>
+    <mergeCell ref="D397:D405"/>
+    <mergeCell ref="D409:D422"/>
   </mergeCells>
-  <conditionalFormatting sqref="F255:F255">
+  <conditionalFormatting sqref="F256:F256">
     <cfRule priority="1" type="colorScale">
       <colorScale>
         <cfvo type="min"/>
@@ -10519,7 +10825,7 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F407" r:id="rId1"/>
+    <hyperlink ref="F408" r:id="rId1"/>
   </hyperlinks>
   <extLst/>
 </worksheet>

--- a/Files/Tracker Update.xlsx
+++ b/Files/Tracker Update.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="1168">
   <si>
     <t>TRACKER</t>
   </si>
@@ -810,13 +810,14 @@
     <t>Enum</t>
   </si>
   <si>
-    <t>named constants, used when variable can only be one of few values</t>
+    <t>store predefined values inside enum and access those with enum properties</t>
   </si>
   <si>
     <t>Aliases</t>
   </si>
   <si>
-    <t>type keyword gives a custom name to any type for reuse</t>
+    <t>type keyword gives a custom name to any type for reuse  -&gt; type studentNameAlias =string;
+studentname:studentNameAlias="raj";</t>
   </si>
   <si>
     <t>Interfaces</t>
@@ -834,7 +835,14 @@
     <t>TS Functions</t>
   </si>
   <si>
-    <t>can type params and return value, supports optional and default params</t>
+    <t>simple function function getValue():number{}
+void return type : return nothing
+optional parameter:  function setValue(firstVal:number,secondval?:number){return firstVal*secondVal}
+Default parameter: function setValue(firstVal:number,secondVal=40),
+Rest Parameter: function :setValue(firstVal:number,...otherValues:number[]),
+named Parameter:  function namedFunc(
+    { name: firstinput, age: secondinput }: { name: string; age: number }
+) {return firstInput}</t>
   </si>
   <si>
     <t>Type Cast</t>
@@ -1702,7 +1710,7 @@
     <t>File System</t>
   </si>
   <si>
-    <t>readFile reads file, writeFile writes, appendFile adds to end, readdirSync reads folder, existsSync checks if file exists</t>
+    <t>readFile reads file, writeFile writes, appendFile adds to end, readdirSync reads folder, existsSync checks if file or folder exists or not</t>
   </si>
   <si>
     <t>Path Module</t>
@@ -1714,19 +1722,39 @@
     <t>Streams</t>
   </si>
   <si>
-    <t>used to read or write data in chunks, readStream reads, writeStream writes, pipe connects them, unpipe disconnects</t>
+    <t>used to read or write data in chunks, readStream reads, writeStream writes, pipe connects them - used to emit chunks immediately whenever receives, unpipe disconnects</t>
   </si>
   <si>
     <t>Process Object</t>
   </si>
   <si>
-    <t>process.env gets environment variables, cwd gets current directory, pid gets process ID, memoryUsage returns memory info</t>
+    <t>process.env gets environment variables, cwd gets current directory, pid gets process ID, memoryUsage returns memory info, process.emitWarning -&gt; return warning, process.arch -&gt; return archietecture like x32,x64, process.platform -&gt; return win 32, or win 64</t>
   </si>
   <si>
     <t>Http Server</t>
   </si>
   <si>
-    <t>http.createServer sets up a server, server.listen starts it on a port</t>
+    <t>http.createServer sets up a server, server.listen starts it on a port
+http server is built on top of TCP
+https is the secure version (uses TLS)
+http gives extra features like methods, headers, status codes, routing style, etc.</t>
+  </si>
+  <si>
+    <t>HTTP/2 Server</t>
+  </si>
+  <si>
+    <t>Most efficient and fast compared to http
+multiplexing concept used in this which means -&gt; many request + response at the same time in one connection
+http open many tcp connections but http/2 1 connection to every flows
+http repsonse text based but it uses binary internally</t>
+  </si>
+  <si>
+    <t>UDP/Datagram</t>
+  </si>
+  <si>
+    <t>send data in small packets lightweight and faster than TCP.
+you can send data fast as you can but it will reaches or not is doubted.
+and no real connection even happened</t>
   </si>
   <si>
     <t>Readline Module</t>
@@ -2182,7 +2210,12 @@
     <t>Intersection Types</t>
   </si>
   <si>
-    <t>combines multiple types into one, all properties from each are required</t>
+    <t>combines multiple types into one, all properties from each are required
+interface identy{id,name}
+interface designation{department,noofassets}
+interface workDetails{assignedwork,assignedArea}
+type Employee =identity &amp; designation
+type workers = identity &amp; workersDetails</t>
   </si>
   <si>
     <t>Type Guards</t>
@@ -2191,12 +2224,6 @@
     <t>typeof, instanceof, in used to narrow type inside a condition block</t>
   </si>
   <si>
-    <t>Generic Constraints</t>
-  </si>
-  <si>
-    <t>extends keyword limits what types can be passed to a generic</t>
-  </si>
-  <si>
     <t>Generic Classes</t>
   </si>
   <si>
@@ -2209,6 +2236,47 @@
     <t>interface accepts a type parameter to stay reusable across types</t>
   </si>
   <si>
+    <t>Ambients</t>
+  </si>
+  <si>
+    <t>Tell typescript that something exists without actuall implementation 
+declare var $: any;   
+$("#button").click();   ----&gt; no error with above declar var$: any;</t>
+  </si>
+  <si>
+    <t>Decorators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decorators special declaration for adding extra behavior to class parameter properties.
+class decorator - @Sealed  using this we can't able to add anything inside class which sealed
+parameter decorator - @Required using this we can put rules to put that parameter 
+Decorator with parameters -&gt; @Role("admin) using this we can pass decorator with parameter for role access though
+Property decorator -&gt; class person{ @Readonly name:string="vasi"  } give properties controlled access through this </t>
+  </si>
+  <si>
+    <t>Namespaces</t>
+  </si>
+  <si>
+    <t>Namespaces grouping related codes together to avoid name conflicts 
+namespace Admin{class User}
+nameSpace Guest {class User}</t>
+  </si>
+  <si>
+    <t>Duck Typing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typescript checks the shape of the object and object names to implement it 
+interface user{name,age}  interface car{name,model,year}
+let userone={name:"..",age:".."} ---&gt; this one takes no error
+let carone ={name:"--",color:"---"}  ---&gt; here fails because in interface  mentioned model but here expecting color </t>
+  </si>
+  <si>
+    <t>Temlate Literals</t>
+  </si>
+  <si>
+    <t>Defined the variable + strings inside easily without + or , using backtics(`)</t>
+  </si>
+  <si>
     <t>TS Modules</t>
   </si>
   <si>
@@ -2416,19 +2484,47 @@
     <t>Query String</t>
   </si>
   <si>
-    <t>parse converts URL query string to object, stringify does reverse, escape encodes special chars</t>
+    <t>querystring.parse("") -&gt; parse converts URL query string to object,
+querystring.stringify("")-&gt; converts object to URL query string, does reverse, escape encodes special chars  - add %20 instead of spaces, unescape -&gt; remove the %20 and given with spaces,    URLSearchParams -&gt; using this create new urlsearch params and using this we can get, add, modify, delete params</t>
   </si>
   <si>
     <t>DNS</t>
   </si>
   <si>
-    <t>lookup resolves hostname to IP, reverseLookup IP to hostname, resolve gets DNS records</t>
+    <t>lookup  - used to figure out ip version and ip address of the domain, reverse -&gt; used to convert ip into domain like 8.8.8.8 -&gt;dns.google, resolve -  gets DNS records like (A - IP address, AAAA - IPV6 , CNAME- alias),  dns.resolveMax() -&gt; finding mail server, dns.resolveTxt()-&gt; get text related dns records</t>
+  </si>
+  <si>
+    <t>Net Model</t>
+  </si>
+  <si>
+    <t>used to create a TCP communication,
+connection between client and server,
+this a normal traditional concept
+server=net.createServer()=&gt;.....</t>
+  </si>
+  <si>
+    <t>TLS</t>
+  </si>
+  <si>
+    <t>TLS client and server connection related but in a secure way connection.
+Secure encrypted TCP connection.</t>
   </si>
   <si>
     <t>URL</t>
   </si>
   <si>
-    <t>hostname, port, pathname parsed from a URL string</t>
+    <r>
+      <t xml:space="preserve">myUrl.hostname -&gt; given the host name ex. </t>
+    </r>
+    <r>
+      <t>https://example.com</t>
+    </r>
+    <r>
+      <t xml:space="preserve"> returns example.com
+myUrl.port -&gt; return the current listening port
+myUrl.path -&gt; given the path after the example.com/  ex example.com/pathhere -&gt;return pathhere
+myUrl.serarchParams.append('city','london') -&gt;we can directly manually add this into patha also it returns like ---&gt; example.com/pathhere?city=london</t>
+    </r>
   </si>
   <si>
     <t>Worker Threads</t>
@@ -3383,6 +3479,243 @@
   </si>
   <si>
     <t>set.add(), set.has(), set.size(), set.delete(), set.clear(), set.foreach()</t>
+  </si>
+  <si>
+    <t>NodeRed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node Red </t>
+  </si>
+  <si>
+    <t>Node red is a debugging and testing tool with flow integration</t>
+  </si>
+  <si>
+    <t>Basic Nodes</t>
+  </si>
+  <si>
+    <t>Input Node (default timestamp)</t>
+  </si>
+  <si>
+    <t>holds the input which gonna input string or number anything as a draggable node</t>
+  </si>
+  <si>
+    <t>debugger node</t>
+  </si>
+  <si>
+    <t>holds the information of output or error whatever holds as a draggable node</t>
+  </si>
+  <si>
+    <t>link call</t>
+  </si>
+  <si>
+    <t>call another flow like a funciton through link in link out</t>
+  </si>
+  <si>
+    <t>link in node</t>
+  </si>
+  <si>
+    <t>used to receive the input data without connecting wires through from linkout node</t>
+  </si>
+  <si>
+    <t>link out node</t>
+  </si>
+  <si>
+    <t>used to send the data without connecting wires through to linkin node</t>
+  </si>
+  <si>
+    <t>status node</t>
+  </si>
+  <si>
+    <t>detect status changes of another node</t>
+  </si>
+  <si>
+    <t>comment node</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is used to add notes, labels like that </t>
+  </si>
+  <si>
+    <t>catch node</t>
+  </si>
+  <si>
+    <t>used to capture and handle erros thrown by other nodes</t>
+  </si>
+  <si>
+    <t>complete node</t>
+  </si>
+  <si>
+    <t>detect when another node has successfully finished its works</t>
+  </si>
+  <si>
+    <t>Function Nodes</t>
+  </si>
+  <si>
+    <t>function node</t>
+  </si>
+  <si>
+    <t>whole the function implementation along with draggable node</t>
+  </si>
+  <si>
+    <t xml:space="preserve">switch node </t>
+  </si>
+  <si>
+    <t>return a message to different outputs based on condition</t>
+  </si>
+  <si>
+    <t>change node</t>
+  </si>
+  <si>
+    <t>modify,set,move,rename or delete message properties</t>
+  </si>
+  <si>
+    <t>template node</t>
+  </si>
+  <si>
+    <t>generate formatted text,html,json or messages dynamically</t>
+  </si>
+  <si>
+    <t>delay node</t>
+  </si>
+  <si>
+    <t>pause or postpone a message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger node </t>
+  </si>
+  <si>
+    <t>used to send one message immediately and then send a message after specified delay</t>
+  </si>
+  <si>
+    <t>Exec node</t>
+  </si>
+  <si>
+    <t>used to run system/terminal/cli commands</t>
+  </si>
+  <si>
+    <t>Filter node</t>
+  </si>
+  <si>
+    <t xml:space="preserve">used to allow certain messages based on condition </t>
+  </si>
+  <si>
+    <t>Network Nodes</t>
+  </si>
+  <si>
+    <t>http in node</t>
+  </si>
+  <si>
+    <t>create an incoming http endpoint</t>
+  </si>
+  <si>
+    <t>http response node</t>
+  </si>
+  <si>
+    <t>request received and procedded</t>
+  </si>
+  <si>
+    <t>websocketin</t>
+  </si>
+  <si>
+    <t>incoming realtime messages</t>
+  </si>
+  <si>
+    <t>websocketout</t>
+  </si>
+  <si>
+    <t>send realtime messages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCP in, TCP Out </t>
+  </si>
+  <si>
+    <t>raw tcp data related receives and sends</t>
+  </si>
+  <si>
+    <t>UDP in, UDPout</t>
+  </si>
+  <si>
+    <t>UDP data receives and sends like datagram pockets little by little</t>
+  </si>
+  <si>
+    <t>Parser Nodes</t>
+  </si>
+  <si>
+    <t>JSON node</t>
+  </si>
+  <si>
+    <t>string to object, object to string</t>
+  </si>
+  <si>
+    <t>XML node</t>
+  </si>
+  <si>
+    <t>xml to object, object to xml</t>
+  </si>
+  <si>
+    <t>html node</t>
+  </si>
+  <si>
+    <t>extract element from html which msg.payload through using a css selectors</t>
+  </si>
+  <si>
+    <t>CSV node</t>
+  </si>
+  <si>
+    <t>convert csv to object, object to csv</t>
+  </si>
+  <si>
+    <t>yaml node</t>
+  </si>
+  <si>
+    <t>yaml to object, object to yaml</t>
+  </si>
+  <si>
+    <t>Sequence Nodes</t>
+  </si>
+  <si>
+    <t>splite node</t>
+  </si>
+  <si>
+    <t>used to splite into mulitple items seprate messages</t>
+  </si>
+  <si>
+    <t>join node</t>
+  </si>
+  <si>
+    <t>used to join mulitple incoming messages</t>
+  </si>
+  <si>
+    <t>sort node</t>
+  </si>
+  <si>
+    <t>for sorting purpose</t>
+  </si>
+  <si>
+    <t>batch node</t>
+  </si>
+  <si>
+    <t>group multiple messages together into batches before sending them onward</t>
+  </si>
+  <si>
+    <t>Storage Nodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">write file </t>
+  </si>
+  <si>
+    <t>used to write file</t>
+  </si>
+  <si>
+    <t>read file</t>
+  </si>
+  <si>
+    <t>for readfile purpose</t>
+  </si>
+  <si>
+    <t>watch</t>
+  </si>
+  <si>
+    <t>monitor file folder changes</t>
   </si>
 </sst>
 </file>
@@ -3488,7 +3821,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -4056,13 +4389,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB0BDD8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="102">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -4303,25 +4645,13 @@
     <xf borderId="21" fillId="4" fontId="7" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="10" numFmtId="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="10" numFmtId="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf borderId="34" fillId="4" fontId="7" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="41" fillId="0" fontId="10" numFmtId="0" xfId="0">
+    <xf borderId="41" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="30" fillId="0" fontId="10" numFmtId="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="42" fillId="0" fontId="10" numFmtId="0" xfId="0">
+    <xf borderId="42" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="43" fillId="4" fontId="7" numFmtId="0" xfId="0">
@@ -4333,7 +4663,7 @@
     <xf borderId="29" fillId="4" fontId="7" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="0" fontId="10" numFmtId="0" xfId="0">
+    <xf borderId="29" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="44" fillId="6" fontId="9" numFmtId="0" xfId="0">
@@ -4345,13 +4675,37 @@
     <xf borderId="37" fillId="4" fontId="7" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="46" fillId="0" fontId="10" numFmtId="0" xfId="0">
+    <xf borderId="46" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="37" fillId="4" fontId="7" numFmtId="164" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="35" fillId="0" fontId="10" numFmtId="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="20" fillId="4" fontId="7" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="10" numFmtId="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="35" fillId="0" fontId="2" numFmtId="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="47" fillId="4" fontId="7" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="10" numFmtId="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="10" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="12" fillId="0" fontId="10" numFmtId="0" xfId="0">
@@ -4376,7 +4730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-  <dimension ref="A1:F492"/>
+  <dimension ref="A1:F538"/>
   <sheetFormatPr defaultRowHeight="15.0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.03"/>
@@ -5246,7 +5600,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" customHeight="1" ht="15.0">
+    <row r="68" customHeight="1" ht="68.0">
       <c r="A68" s="11"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -5434,7 +5788,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="83" customHeight="1" ht="15.0">
+    <row r="83" customHeight="1" ht="60.0">
       <c r="A83" s="19" t="s">
         <v>181</v>
       </c>
@@ -5790,7 +6144,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="112" customHeight="1" ht="15.0">
+    <row r="112" customHeight="1" ht="71.0">
       <c r="A112" s="15"/>
       <c r="B112" s="16"/>
       <c r="C112" s="16"/>
@@ -5894,7 +6248,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="120" customHeight="1" ht="15.0">
+    <row r="120" customHeight="1" ht="30.0">
       <c r="A120" s="11"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
@@ -5930,7 +6284,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="123" customHeight="1" ht="15.0">
+    <row r="123" customHeight="1" ht="175.0">
       <c r="A123" s="11"/>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
@@ -6538,7 +6892,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="169" customHeight="1" ht="15.0">
+    <row r="169" customHeight="1" ht="37.0">
       <c r="A169" s="5" t="s">
         <v>379</v>
       </c>
@@ -7242,7 +7596,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="225" customHeight="1" ht="114.0">
+    <row r="225" customHeight="1" ht="167.0">
       <c r="A225" s="15"/>
       <c r="B225" s="16"/>
       <c r="C225" s="16"/>
@@ -7310,7 +7664,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="230" customHeight="1" ht="15.0">
+    <row r="230" customHeight="1" ht="30.0">
       <c r="A230" s="15"/>
       <c r="B230" s="16"/>
       <c r="C230" s="16"/>
@@ -7566,7 +7920,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="250" customHeight="1" ht="43.0">
+    <row r="250" customHeight="1" ht="60.0">
       <c r="A250" s="11"/>
       <c r="B250" s="12"/>
       <c r="C250" s="12"/>
@@ -7578,107 +7932,107 @@
         <v>559</v>
       </c>
     </row>
-    <row r="251" customHeight="1" ht="55.0">
-      <c r="A251" s="15"/>
-      <c r="B251" s="16"/>
-      <c r="C251" s="16"/>
-      <c r="D251" s="16"/>
-      <c r="E251" s="17" t="s">
+    <row r="251" customHeight="1" ht="60.0">
+      <c r="A251" s="11"/>
+      <c r="B251" s="12"/>
+      <c r="C251" s="12"/>
+      <c r="D251" s="12"/>
+      <c r="E251" s="13" t="s">
         <v>560</v>
       </c>
-      <c r="F251" s="18" t="s">
+      <c r="F251" s="14" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="252" customHeight="1" ht="89.0">
-      <c r="A252" s="19" t="s">
+    <row r="252" customHeight="1" ht="43.0">
+      <c r="A252" s="11"/>
+      <c r="B252" s="12"/>
+      <c r="C252" s="12"/>
+      <c r="D252" s="12"/>
+      <c r="E252" s="13" t="s">
         <v>562</v>
       </c>
-      <c r="B252" s="20" t="s">
+      <c r="F252" s="14" t="s">
         <v>563</v>
       </c>
-      <c r="C252" s="21" t="s">
+    </row>
+    <row r="253" customHeight="1" ht="55.0">
+      <c r="A253" s="15"/>
+      <c r="B253" s="16"/>
+      <c r="C253" s="16"/>
+      <c r="D253" s="16"/>
+      <c r="E253" s="17" t="s">
         <v>564</v>
       </c>
-      <c r="D252" s="22" t="s">
+      <c r="F253" s="18" t="s">
         <v>565</v>
       </c>
-      <c r="E252" s="23" t="s">
+    </row>
+    <row r="254" customHeight="1" ht="89.0">
+      <c r="A254" s="19" t="s">
         <v>566</v>
       </c>
-      <c r="F252" s="24" t="s">
+      <c r="B254" s="20" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="253" customHeight="1" ht="52.0">
-      <c r="A253" s="11"/>
-      <c r="B253" s="12"/>
-      <c r="C253" s="12"/>
-      <c r="D253" s="12"/>
-      <c r="E253" s="25" t="s">
+      <c r="C254" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="F253" s="26" t="s">
+      <c r="D254" s="22" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="254" customHeight="1" ht="46.0">
-      <c r="A254" s="15"/>
-      <c r="B254" s="16"/>
-      <c r="C254" s="16"/>
-      <c r="D254" s="16"/>
-      <c r="E254" s="27" t="s">
+      <c r="E254" s="23" t="s">
         <v>570</v>
       </c>
-      <c r="F254" s="28" t="s">
+      <c r="F254" s="24" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="255" customHeight="1" ht="76.0">
-      <c r="A255" s="5" t="s">
+    <row r="255" customHeight="1" ht="52.0">
+      <c r="A255" s="11"/>
+      <c r="B255" s="12"/>
+      <c r="C255" s="12"/>
+      <c r="D255" s="12"/>
+      <c r="E255" s="25" t="s">
         <v>572</v>
       </c>
-      <c r="B255" s="6" t="s">
+      <c r="F255" s="26" t="s">
         <v>573</v>
       </c>
-      <c r="C255" s="7" t="s">
+    </row>
+    <row r="256" customHeight="1" ht="46.0">
+      <c r="A256" s="15"/>
+      <c r="B256" s="16"/>
+      <c r="C256" s="16"/>
+      <c r="D256" s="16"/>
+      <c r="E256" s="27" t="s">
         <v>574</v>
       </c>
-      <c r="D255" s="8" t="s">
+      <c r="F256" s="28" t="s">
         <v>575</v>
       </c>
-      <c r="E255" s="9" t="s">
+    </row>
+    <row r="257" customHeight="1" ht="76.0">
+      <c r="A257" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="F255" s="10" t="s">
+      <c r="B257" s="6" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="256" customHeight="1" ht="54.0">
-      <c r="A256" s="11"/>
-      <c r="B256" s="12"/>
-      <c r="C256" s="12"/>
-      <c r="D256" s="12"/>
-      <c r="E256" s="13" t="s">
+      <c r="C257" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="F256" s="14" t="s">
+      <c r="D257" s="8" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="257" customHeight="1" ht="54.0">
-      <c r="A257" s="11"/>
-      <c r="B257" s="12"/>
-      <c r="C257" s="12"/>
-      <c r="D257" s="12"/>
-      <c r="E257" s="13" t="s">
+      <c r="E257" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="F257" s="14" t="s">
+      <c r="F257" s="10" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="258" customHeight="1" ht="55.0">
+    <row r="258" customHeight="1" ht="54.0">
       <c r="A258" s="11"/>
       <c r="B258" s="12"/>
       <c r="C258" s="12"/>
@@ -7690,7 +8044,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="259" customHeight="1" ht="36.0">
+    <row r="259" customHeight="1" ht="54.0">
       <c r="A259" s="11"/>
       <c r="B259" s="12"/>
       <c r="C259" s="12"/>
@@ -7702,7 +8056,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="260" customHeight="1" ht="41.0">
+    <row r="260" customHeight="1" ht="55.0">
       <c r="A260" s="11"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12"/>
@@ -7714,7 +8068,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="261" customHeight="1" ht="31.0">
+    <row r="261" customHeight="1" ht="36.0">
       <c r="A261" s="11"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12"/>
@@ -7726,7 +8080,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="262" customHeight="1" ht="32.0">
+    <row r="262" customHeight="1" ht="41.0">
       <c r="A262" s="11"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12"/>
@@ -7738,7 +8092,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="263" customHeight="1" ht="42.0">
+    <row r="263" customHeight="1" ht="31.0">
       <c r="A263" s="11"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
@@ -7750,7 +8104,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="264" customHeight="1" ht="39.0">
+    <row r="264" customHeight="1" ht="32.0">
       <c r="A264" s="11"/>
       <c r="B264" s="12"/>
       <c r="C264" s="12"/>
@@ -7762,59 +8116,59 @@
         <v>595</v>
       </c>
     </row>
-    <row r="265" customHeight="1" ht="49.0">
-      <c r="A265" s="15"/>
-      <c r="B265" s="16"/>
-      <c r="C265" s="16"/>
-      <c r="D265" s="16"/>
-      <c r="E265" s="17" t="s">
+    <row r="265" customHeight="1" ht="42.0">
+      <c r="A265" s="11"/>
+      <c r="B265" s="12"/>
+      <c r="C265" s="12"/>
+      <c r="D265" s="12"/>
+      <c r="E265" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="F265" s="18" t="s">
+      <c r="F265" s="14" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="266" customHeight="1" ht="15.0">
-      <c r="A266" s="19" t="s">
+    <row r="266" customHeight="1" ht="39.0">
+      <c r="A266" s="11"/>
+      <c r="B266" s="12"/>
+      <c r="C266" s="12"/>
+      <c r="D266" s="12"/>
+      <c r="E266" s="13" t="s">
         <v>598</v>
       </c>
-      <c r="B266" s="21" t="s">
+      <c r="F266" s="14" t="s">
         <v>599</v>
       </c>
-      <c r="C266" s="21" t="s">
+    </row>
+    <row r="267" customHeight="1" ht="49.0">
+      <c r="A267" s="15"/>
+      <c r="B267" s="16"/>
+      <c r="C267" s="16"/>
+      <c r="D267" s="16"/>
+      <c r="E267" s="17" t="s">
         <v>600</v>
       </c>
-      <c r="D266" s="21" t="s">
+      <c r="F267" s="18" t="s">
         <v>601</v>
       </c>
-      <c r="E266" s="21" t="s">
+    </row>
+    <row r="268" customHeight="1" ht="15.0">
+      <c r="A268" s="19" t="s">
         <v>602</v>
       </c>
-      <c r="F266" s="24" t="s">
+      <c r="B268" s="21" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="267" customHeight="1" ht="15.0">
-      <c r="A267" s="11"/>
-      <c r="B267" s="12"/>
-      <c r="C267" s="12"/>
-      <c r="D267" s="12"/>
-      <c r="E267" s="12" t="s">
+      <c r="C268" s="21" t="s">
         <v>604</v>
       </c>
-      <c r="F267" s="26" t="s">
+      <c r="D268" s="21" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="268" customHeight="1" ht="15.0">
-      <c r="A268" s="11"/>
-      <c r="B268" s="12"/>
-      <c r="C268" s="12"/>
-      <c r="D268" s="12"/>
-      <c r="E268" s="12" t="s">
+      <c r="E268" s="21" t="s">
         <v>606</v>
       </c>
-      <c r="F268" s="26" t="s">
+      <c r="F268" s="24" t="s">
         <v>607</v>
       </c>
     </row>
@@ -7843,58 +8197,58 @@
       </c>
     </row>
     <row r="271" customHeight="1" ht="15.0">
-      <c r="A271" s="15"/>
-      <c r="B271" s="16"/>
-      <c r="C271" s="16"/>
-      <c r="D271" s="16"/>
-      <c r="E271" s="16" t="s">
+      <c r="A271" s="11"/>
+      <c r="B271" s="12"/>
+      <c r="C271" s="12"/>
+      <c r="D271" s="12"/>
+      <c r="E271" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="F271" s="28" t="s">
+      <c r="F271" s="26" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="272" customHeight="1" ht="15.0">
-      <c r="A272" s="5" t="s">
+      <c r="A272" s="11"/>
+      <c r="B272" s="12"/>
+      <c r="C272" s="12"/>
+      <c r="D272" s="12"/>
+      <c r="E272" s="12" t="s">
         <v>614</v>
       </c>
-      <c r="B272" s="6" t="s">
+      <c r="F272" s="26" t="s">
         <v>615</v>
       </c>
-      <c r="C272" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="D272" s="8" t="s">
+    </row>
+    <row r="273" customHeight="1" ht="15.0">
+      <c r="A273" s="15"/>
+      <c r="B273" s="16"/>
+      <c r="C273" s="16"/>
+      <c r="D273" s="16"/>
+      <c r="E273" s="16" t="s">
         <v>616</v>
       </c>
-      <c r="E272" s="9" t="s">
+      <c r="F273" s="28" t="s">
         <v>617</v>
       </c>
-      <c r="F272" s="10" t="s">
+    </row>
+    <row r="274" customHeight="1" ht="15.0">
+      <c r="A274" s="5" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="273" customHeight="1" ht="15.0">
-      <c r="A273" s="11"/>
-      <c r="B273" s="12"/>
-      <c r="C273" s="12"/>
-      <c r="D273" s="12"/>
-      <c r="E273" s="13" t="s">
+      <c r="B274" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="F273" s="14" t="s">
+      <c r="C274" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="D274" s="8" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="274" customHeight="1" ht="15.0">
-      <c r="A274" s="11"/>
-      <c r="B274" s="12"/>
-      <c r="C274" s="12"/>
-      <c r="D274" s="12"/>
-      <c r="E274" s="13" t="s">
+      <c r="E274" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="F274" s="14" t="s">
+      <c r="F274" s="10" t="s">
         <v>622</v>
       </c>
     </row>
@@ -8007,58 +8361,58 @@
       </c>
     </row>
     <row r="284" customHeight="1" ht="15.0">
-      <c r="A284" s="15"/>
-      <c r="B284" s="16"/>
-      <c r="C284" s="16"/>
-      <c r="D284" s="16"/>
-      <c r="E284" s="17" t="s">
+      <c r="A284" s="11"/>
+      <c r="B284" s="12"/>
+      <c r="C284" s="12"/>
+      <c r="D284" s="12"/>
+      <c r="E284" s="13" t="s">
         <v>641</v>
       </c>
-      <c r="F284" s="18" t="s">
+      <c r="F284" s="14" t="s">
         <v>642</v>
       </c>
     </row>
     <row r="285" customHeight="1" ht="15.0">
-      <c r="A285" s="19" t="s">
+      <c r="A285" s="11"/>
+      <c r="B285" s="12"/>
+      <c r="C285" s="12"/>
+      <c r="D285" s="12"/>
+      <c r="E285" s="13" t="s">
         <v>643</v>
       </c>
-      <c r="B285" s="20" t="s">
+      <c r="F285" s="14" t="s">
         <v>644</v>
       </c>
-      <c r="C285" s="21" t="s">
+    </row>
+    <row r="286" customHeight="1" ht="15.0">
+      <c r="A286" s="15"/>
+      <c r="B286" s="16"/>
+      <c r="C286" s="16"/>
+      <c r="D286" s="16"/>
+      <c r="E286" s="17" t="s">
         <v>645</v>
       </c>
-      <c r="D285" s="22" t="s">
+      <c r="F286" s="18" t="s">
         <v>646</v>
       </c>
-      <c r="E285" s="23" t="s">
+    </row>
+    <row r="287" customHeight="1" ht="15.0">
+      <c r="A287" s="19" t="s">
         <v>647</v>
       </c>
-      <c r="F285" s="24" t="s">
+      <c r="B287" s="20" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="286" customHeight="1" ht="15.0">
-      <c r="A286" s="11"/>
-      <c r="B286" s="12"/>
-      <c r="C286" s="12"/>
-      <c r="D286" s="12"/>
-      <c r="E286" s="25" t="s">
+      <c r="C287" s="21" t="s">
         <v>649</v>
       </c>
-      <c r="F286" s="26" t="s">
+      <c r="D287" s="22" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="287" customHeight="1" ht="15.0">
-      <c r="A287" s="11"/>
-      <c r="B287" s="12"/>
-      <c r="C287" s="12"/>
-      <c r="D287" s="12"/>
-      <c r="E287" s="25" t="s">
+      <c r="E287" s="23" t="s">
         <v>651</v>
       </c>
-      <c r="F287" s="26" t="s">
+      <c r="F287" s="24" t="s">
         <v>652</v>
       </c>
     </row>
@@ -8279,58 +8633,58 @@
       </c>
     </row>
     <row r="306" customHeight="1" ht="15.0">
-      <c r="A306" s="15"/>
-      <c r="B306" s="16"/>
-      <c r="C306" s="16"/>
-      <c r="D306" s="16"/>
-      <c r="E306" s="27" t="s">
+      <c r="A306" s="11"/>
+      <c r="B306" s="12"/>
+      <c r="C306" s="12"/>
+      <c r="D306" s="12"/>
+      <c r="E306" s="25" t="s">
         <v>689</v>
       </c>
-      <c r="F306" s="28" t="s">
+      <c r="F306" s="26" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="307" customHeight="1" ht="15.0">
-      <c r="A307" s="5" t="s">
+      <c r="A307" s="11"/>
+      <c r="B307" s="12"/>
+      <c r="C307" s="12"/>
+      <c r="D307" s="12"/>
+      <c r="E307" s="25" t="s">
         <v>691</v>
       </c>
-      <c r="B307" s="6" t="s">
+      <c r="F307" s="26" t="s">
         <v>692</v>
       </c>
-      <c r="C307" s="7" t="s">
+    </row>
+    <row r="308" customHeight="1" ht="15.0">
+      <c r="A308" s="15"/>
+      <c r="B308" s="16"/>
+      <c r="C308" s="16"/>
+      <c r="D308" s="16"/>
+      <c r="E308" s="27" t="s">
+        <v>693</v>
+      </c>
+      <c r="F308" s="28" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="309" customHeight="1" ht="15.0">
+      <c r="A309" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="C309" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="D307" s="8" t="s">
-        <v>693</v>
-      </c>
-      <c r="E307" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="F307" s="10" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="308" customHeight="1" ht="15.0">
-      <c r="A308" s="11"/>
-      <c r="B308" s="12"/>
-      <c r="C308" s="12"/>
-      <c r="D308" s="12"/>
-      <c r="E308" s="13" t="s">
-        <v>696</v>
-      </c>
-      <c r="F308" s="14" t="s">
+      <c r="D309" s="8" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="309" customHeight="1" ht="15.0">
-      <c r="A309" s="11"/>
-      <c r="B309" s="12"/>
-      <c r="C309" s="12"/>
-      <c r="D309" s="12"/>
-      <c r="E309" s="13" t="s">
+      <c r="E309" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="F309" s="14" t="s">
+      <c r="F309" s="10" t="s">
         <v>699</v>
       </c>
     </row>
@@ -8406,7 +8760,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="316" customHeight="1" ht="15.0">
+    <row r="316" customHeight="1" ht="91.0">
       <c r="A316" s="11"/>
       <c r="B316" s="12"/>
       <c r="C316" s="12"/>
@@ -8435,127 +8789,123 @@
       <c r="B318" s="12"/>
       <c r="C318" s="12"/>
       <c r="D318" s="12"/>
-      <c r="E318" s="13" t="s">
+      <c r="E318" s="13"/>
+      <c r="F318" s="14"/>
+    </row>
+    <row r="319" customHeight="1" ht="15.0">
+      <c r="A319" s="11"/>
+      <c r="B319" s="12"/>
+      <c r="C319" s="12"/>
+      <c r="D319" s="12"/>
+      <c r="E319" s="13" t="s">
         <v>716</v>
       </c>
-      <c r="F318" s="14" t="s">
+      <c r="F319" s="14" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="319" customHeight="1" ht="15.0">
-      <c r="A319" s="15"/>
-      <c r="B319" s="16"/>
-      <c r="C319" s="16"/>
-      <c r="D319" s="16"/>
-      <c r="E319" s="17" t="s">
+    <row r="320" customHeight="1" ht="15.0">
+      <c r="A320" s="11"/>
+      <c r="B320" s="12"/>
+      <c r="C320" s="12"/>
+      <c r="D320" s="12"/>
+      <c r="E320" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="F319" s="18" t="s">
+      <c r="F320" s="14" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="320" customHeight="1" ht="15.0">
-      <c r="A320" s="19" t="s">
-        <v>720</v>
-      </c>
-      <c r="B320" s="20" t="s">
-        <v>507</v>
-      </c>
-      <c r="C320" s="21" t="s">
-        <v>544</v>
-      </c>
-      <c r="D320" s="22" t="s">
-        <v>721</v>
-      </c>
-      <c r="E320" s="23" t="s">
-        <v>722</v>
-      </c>
-      <c r="F320" s="24" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="321" customHeight="1" ht="15.0">
+    <row r="321" customHeight="1" ht="49.0">
       <c r="A321" s="11"/>
       <c r="B321" s="12"/>
       <c r="C321" s="12"/>
       <c r="D321" s="12"/>
-      <c r="E321" s="25" t="s">
-        <v>724</v>
-      </c>
-      <c r="F321" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="322" customHeight="1" ht="15.0">
+      <c r="E321" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="F321" s="14" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="322" customHeight="1" ht="127.0">
       <c r="A322" s="11"/>
       <c r="B322" s="12"/>
       <c r="C322" s="12"/>
       <c r="D322" s="12"/>
-      <c r="E322" s="25" t="s">
-        <v>726</v>
-      </c>
-      <c r="F322" s="26" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="323" customHeight="1" ht="15.0">
+      <c r="E322" s="13" t="s">
+        <v>722</v>
+      </c>
+      <c r="F322" s="14" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="323" customHeight="1" ht="127.0">
       <c r="A323" s="11"/>
       <c r="B323" s="12"/>
       <c r="C323" s="12"/>
       <c r="D323" s="12"/>
-      <c r="E323" s="25" t="s">
-        <v>546</v>
-      </c>
-      <c r="F323" s="26" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="324" customHeight="1" ht="15.0">
+      <c r="E323" s="13" t="s">
+        <v>724</v>
+      </c>
+      <c r="F323" s="14" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="324" customHeight="1" ht="91.0">
       <c r="A324" s="11"/>
       <c r="B324" s="12"/>
       <c r="C324" s="12"/>
       <c r="D324" s="12"/>
-      <c r="E324" s="25" t="s">
-        <v>729</v>
-      </c>
-      <c r="F324" s="26" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="325" customHeight="1" ht="15.0">
+      <c r="E324" s="13" t="s">
+        <v>726</v>
+      </c>
+      <c r="F324" s="14" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="325" customHeight="1" ht="84.0">
       <c r="A325" s="11"/>
       <c r="B325" s="12"/>
       <c r="C325" s="12"/>
       <c r="D325" s="12"/>
-      <c r="E325" s="25" t="s">
+      <c r="E325" s="13" t="s">
+        <v>728</v>
+      </c>
+      <c r="F325" s="14" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="326" customHeight="1" ht="15.0">
+      <c r="A326" s="15"/>
+      <c r="B326" s="16"/>
+      <c r="C326" s="16"/>
+      <c r="D326" s="16"/>
+      <c r="E326" s="17" t="s">
+        <v>730</v>
+      </c>
+      <c r="F326" s="18" t="s">
         <v>731</v>
       </c>
-      <c r="F325" s="26" t="s">
+    </row>
+    <row r="327" customHeight="1" ht="15.0">
+      <c r="A327" s="19" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="326" customHeight="1" ht="15.0">
-      <c r="A326" s="11"/>
-      <c r="B326" s="12"/>
-      <c r="C326" s="12"/>
-      <c r="D326" s="12"/>
-      <c r="E326" s="25" t="s">
+      <c r="B327" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="C327" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="D327" s="22" t="s">
         <v>733</v>
       </c>
-      <c r="F326" s="26" t="s">
+      <c r="E327" s="23" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="327" customHeight="1" ht="15.0">
-      <c r="A327" s="11"/>
-      <c r="B327" s="12"/>
-      <c r="C327" s="12"/>
-      <c r="D327" s="12"/>
-      <c r="E327" s="25" t="s">
+      <c r="F327" s="24" t="s">
         <v>735</v>
-      </c>
-      <c r="F327" s="26" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="328" customHeight="1" ht="15.0">
@@ -8564,10 +8914,10 @@
       <c r="C328" s="12"/>
       <c r="D328" s="12"/>
       <c r="E328" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="F328" s="26" t="s">
         <v>737</v>
-      </c>
-      <c r="F328" s="26" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="329" customHeight="1" ht="15.0">
@@ -8576,10 +8926,10 @@
       <c r="C329" s="12"/>
       <c r="D329" s="12"/>
       <c r="E329" s="25" t="s">
+        <v>738</v>
+      </c>
+      <c r="F329" s="26" t="s">
         <v>739</v>
-      </c>
-      <c r="F329" s="26" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="330" customHeight="1" ht="15.0">
@@ -8588,10 +8938,10 @@
       <c r="C330" s="12"/>
       <c r="D330" s="12"/>
       <c r="E330" s="25" t="s">
-        <v>741</v>
+        <v>546</v>
       </c>
       <c r="F330" s="26" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="331" customHeight="1" ht="15.0">
@@ -8600,10 +8950,10 @@
       <c r="C331" s="12"/>
       <c r="D331" s="12"/>
       <c r="E331" s="25" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="F331" s="26" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="332" customHeight="1" ht="15.0">
@@ -8612,10 +8962,10 @@
       <c r="C332" s="12"/>
       <c r="D332" s="12"/>
       <c r="E332" s="25" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="F332" s="26" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="333" customHeight="1" ht="15.0">
@@ -8624,10 +8974,10 @@
       <c r="C333" s="12"/>
       <c r="D333" s="12"/>
       <c r="E333" s="25" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F333" s="26" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="334" customHeight="1" ht="15.0">
@@ -8636,10 +8986,10 @@
       <c r="C334" s="12"/>
       <c r="D334" s="12"/>
       <c r="E334" s="25" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="F334" s="26" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="335" customHeight="1" ht="15.0">
@@ -8648,10 +8998,10 @@
       <c r="C335" s="12"/>
       <c r="D335" s="12"/>
       <c r="E335" s="25" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="F335" s="26" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="336" customHeight="1" ht="15.0">
@@ -8660,10 +9010,10 @@
       <c r="C336" s="12"/>
       <c r="D336" s="12"/>
       <c r="E336" s="25" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F336" s="26" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="337" customHeight="1" ht="15.0">
@@ -8672,10 +9022,10 @@
       <c r="C337" s="12"/>
       <c r="D337" s="12"/>
       <c r="E337" s="25" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="F337" s="26" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="338" customHeight="1" ht="15.0">
@@ -8684,10 +9034,10 @@
       <c r="C338" s="12"/>
       <c r="D338" s="12"/>
       <c r="E338" s="25" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="F338" s="26" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="339" customHeight="1" ht="15.0">
@@ -8696,10 +9046,10 @@
       <c r="C339" s="12"/>
       <c r="D339" s="12"/>
       <c r="E339" s="25" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="F339" s="26" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="340" customHeight="1" ht="15.0">
@@ -8708,10 +9058,10 @@
       <c r="C340" s="12"/>
       <c r="D340" s="12"/>
       <c r="E340" s="25" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="F340" s="26" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="341" customHeight="1" ht="15.0">
@@ -8720,10 +9070,10 @@
       <c r="C341" s="12"/>
       <c r="D341" s="12"/>
       <c r="E341" s="25" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="F341" s="26" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="342" customHeight="1" ht="15.0">
@@ -8732,10 +9082,10 @@
       <c r="C342" s="12"/>
       <c r="D342" s="12"/>
       <c r="E342" s="25" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="F342" s="26" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="343" customHeight="1" ht="15.0">
@@ -8744,10 +9094,10 @@
       <c r="C343" s="12"/>
       <c r="D343" s="12"/>
       <c r="E343" s="25" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="F343" s="26" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="344" customHeight="1" ht="15.0">
@@ -8756,10 +9106,10 @@
       <c r="C344" s="12"/>
       <c r="D344" s="12"/>
       <c r="E344" s="25" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F344" s="26" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="345" customHeight="1" ht="15.0">
@@ -8768,10 +9118,10 @@
       <c r="C345" s="12"/>
       <c r="D345" s="12"/>
       <c r="E345" s="25" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="F345" s="26" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="346" customHeight="1" ht="15.0">
@@ -8780,10 +9130,10 @@
       <c r="C346" s="12"/>
       <c r="D346" s="12"/>
       <c r="E346" s="25" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="F346" s="26" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="347" customHeight="1" ht="15.0">
@@ -8792,42 +9142,34 @@
       <c r="C347" s="12"/>
       <c r="D347" s="12"/>
       <c r="E347" s="25" t="s">
+        <v>773</v>
+      </c>
+      <c r="F347" s="26" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="348" customHeight="1" ht="15.0">
+      <c r="A348" s="11"/>
+      <c r="B348" s="12"/>
+      <c r="C348" s="12"/>
+      <c r="D348" s="12"/>
+      <c r="E348" s="25" t="s">
         <v>775</v>
       </c>
-      <c r="F347" s="26" t="s">
+      <c r="F348" s="26" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="348" customHeight="1" ht="15.0">
-      <c r="A348" s="15"/>
-      <c r="B348" s="16"/>
-      <c r="C348" s="16"/>
-      <c r="D348" s="16"/>
-      <c r="E348" s="27" t="s">
+    <row r="349" customHeight="1" ht="15.0">
+      <c r="A349" s="11"/>
+      <c r="B349" s="12"/>
+      <c r="C349" s="12"/>
+      <c r="D349" s="12"/>
+      <c r="E349" s="25" t="s">
         <v>777</v>
       </c>
-      <c r="F348" s="28" t="s">
+      <c r="F349" s="26" t="s">
         <v>778</v>
-      </c>
-    </row>
-    <row r="349" customHeight="1" ht="15.0">
-      <c r="A349" s="5" t="s">
-        <v>779</v>
-      </c>
-      <c r="B349" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="C349" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="D349" s="8" t="s">
-        <v>781</v>
-      </c>
-      <c r="E349" s="9" t="s">
-        <v>782</v>
-      </c>
-      <c r="F349" s="10" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="350" customHeight="1" ht="15.0">
@@ -8835,11 +9177,11 @@
       <c r="B350" s="12"/>
       <c r="C350" s="12"/>
       <c r="D350" s="12"/>
-      <c r="E350" s="13" t="s">
-        <v>784</v>
-      </c>
-      <c r="F350" s="14" t="s">
-        <v>785</v>
+      <c r="E350" s="25" t="s">
+        <v>779</v>
+      </c>
+      <c r="F350" s="26" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="351" customHeight="1" ht="15.0">
@@ -8847,11 +9189,11 @@
       <c r="B351" s="12"/>
       <c r="C351" s="12"/>
       <c r="D351" s="12"/>
-      <c r="E351" s="13" t="s">
-        <v>786</v>
-      </c>
-      <c r="F351" s="14" t="s">
-        <v>787</v>
+      <c r="E351" s="25" t="s">
+        <v>781</v>
+      </c>
+      <c r="F351" s="26" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="352" customHeight="1" ht="15.0">
@@ -8859,223 +9201,231 @@
       <c r="B352" s="12"/>
       <c r="C352" s="12"/>
       <c r="D352" s="12"/>
-      <c r="E352" s="13" t="s">
-        <v>788</v>
-      </c>
-      <c r="F352" s="14" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="353" customHeight="1" ht="22.0">
+      <c r="E352" s="25" t="s">
+        <v>783</v>
+      </c>
+      <c r="F352" s="26" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="353" customHeight="1" ht="15.0">
       <c r="A353" s="11"/>
       <c r="B353" s="12"/>
       <c r="C353" s="12"/>
       <c r="D353" s="12"/>
-      <c r="E353" s="13" t="s">
-        <v>790</v>
-      </c>
-      <c r="F353" s="14" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="354" customHeight="1" ht="78.0">
+      <c r="E353" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="F353" s="26" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="354" customHeight="1" ht="15.0">
       <c r="A354" s="11"/>
       <c r="B354" s="12"/>
       <c r="C354" s="12"/>
       <c r="D354" s="12"/>
-      <c r="E354" s="13" t="s">
+      <c r="E354" s="25" t="s">
+        <v>787</v>
+      </c>
+      <c r="F354" s="26" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="355" customHeight="1" ht="15.0">
+      <c r="A355" s="15"/>
+      <c r="B355" s="16"/>
+      <c r="C355" s="16"/>
+      <c r="D355" s="16"/>
+      <c r="E355" s="27" t="s">
+        <v>789</v>
+      </c>
+      <c r="F355" s="28" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="356" customHeight="1" ht="72.0">
+      <c r="A356" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="B356" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="F354" s="14" t="s">
+      <c r="C356" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="D356" s="8" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="355" customHeight="1" ht="78.0">
-      <c r="A355" s="11"/>
-      <c r="B355" s="12"/>
-      <c r="C355" s="12"/>
-      <c r="D355" s="12"/>
-      <c r="E355" s="13" t="s">
+      <c r="E356" s="9" t="s">
         <v>794</v>
       </c>
-      <c r="F355" s="14" t="s">
+      <c r="F356" s="10" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="356" customHeight="1" ht="177.0">
-      <c r="A356" s="15"/>
-      <c r="B356" s="16"/>
-      <c r="C356" s="16"/>
-      <c r="D356" s="16"/>
-      <c r="E356" s="17" t="s">
+    <row r="357" customHeight="1" ht="72.0">
+      <c r="A357" s="11"/>
+      <c r="B357" s="12"/>
+      <c r="C357" s="12"/>
+      <c r="D357" s="12"/>
+      <c r="E357" s="13" t="s">
         <v>796</v>
       </c>
-      <c r="F356" s="35" t="s">
+      <c r="F357" s="14" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="357" customHeight="1" ht="15.0">
-      <c r="A357" s="19" t="s">
-        <v>798</v>
-      </c>
-      <c r="B357" s="20" t="s">
-        <v>799</v>
-      </c>
-      <c r="C357" s="21" t="s">
-        <v>544</v>
-      </c>
-      <c r="D357" s="22" t="s">
-        <v>800</v>
-      </c>
-      <c r="E357" s="23" t="s">
-        <v>801</v>
-      </c>
-      <c r="F357" s="24" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="358" customHeight="1" ht="15.0">
+    <row r="358" customHeight="1" ht="72.0">
       <c r="A358" s="11"/>
       <c r="B358" s="12"/>
       <c r="C358" s="12"/>
       <c r="D358" s="12"/>
-      <c r="E358" s="25" t="s">
-        <v>803</v>
-      </c>
-      <c r="F358" s="26" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="359" customHeight="1" ht="15.0">
+      <c r="E358" s="13" t="s">
+        <v>798</v>
+      </c>
+      <c r="F358" s="14" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="359" customHeight="1" ht="72.0">
       <c r="A359" s="11"/>
       <c r="B359" s="12"/>
       <c r="C359" s="12"/>
       <c r="D359" s="12"/>
-      <c r="E359" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="F359" s="26" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="360" customHeight="1" ht="15.0">
+      <c r="E359" s="13" t="s">
+        <v>800</v>
+      </c>
+      <c r="F359" s="14" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="360" customHeight="1" ht="72.0">
       <c r="A360" s="11"/>
       <c r="B360" s="12"/>
       <c r="C360" s="12"/>
       <c r="D360" s="12"/>
-      <c r="E360" s="25" t="s">
-        <v>765</v>
-      </c>
-      <c r="F360" s="26" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="361" customHeight="1" ht="15.0">
+      <c r="E360" s="13" t="s">
+        <v>802</v>
+      </c>
+      <c r="F360" s="14" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="361" customHeight="1" ht="72.0">
       <c r="A361" s="11"/>
       <c r="B361" s="12"/>
       <c r="C361" s="12"/>
       <c r="D361" s="12"/>
-      <c r="E361" s="25" t="s">
-        <v>808</v>
-      </c>
-      <c r="F361" s="26" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="362" customHeight="1" ht="15.0">
+      <c r="E361" s="13" t="s">
+        <v>804</v>
+      </c>
+      <c r="F361" s="14" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="362" customHeight="1" ht="72.0">
       <c r="A362" s="11"/>
       <c r="B362" s="12"/>
       <c r="C362" s="12"/>
       <c r="D362" s="12"/>
-      <c r="E362" s="25" t="s">
-        <v>810</v>
-      </c>
-      <c r="F362" s="26" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="363" customHeight="1" ht="15.0">
+      <c r="E362" s="13" t="s">
+        <v>806</v>
+      </c>
+      <c r="F362" s="14" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="363" customHeight="1" ht="72.0">
       <c r="A363" s="11"/>
       <c r="B363" s="12"/>
       <c r="C363" s="12"/>
       <c r="D363" s="12"/>
-      <c r="E363" s="25" t="s">
-        <v>812</v>
-      </c>
-      <c r="F363" s="26" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="364" customHeight="1" ht="15.0">
+      <c r="E363" s="13" t="s">
+        <v>808</v>
+      </c>
+      <c r="F363" s="14" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="364" customHeight="1" ht="72.0">
       <c r="A364" s="11"/>
       <c r="B364" s="12"/>
       <c r="C364" s="12"/>
       <c r="D364" s="12"/>
-      <c r="E364" s="25" t="s">
+      <c r="E364" s="13" t="s">
+        <v>810</v>
+      </c>
+      <c r="F364" s="14" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="365" customHeight="1" ht="72.0">
+      <c r="A365" s="15"/>
+      <c r="B365" s="16"/>
+      <c r="C365" s="16"/>
+      <c r="D365" s="16"/>
+      <c r="E365" s="17" t="s">
+        <v>812</v>
+      </c>
+      <c r="F365" s="35" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="366" customHeight="1" ht="15.0">
+      <c r="A366" s="19" t="s">
         <v>814</v>
       </c>
-      <c r="F364" s="26" t="s">
+      <c r="B366" s="20" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="365" customHeight="1" ht="15.0">
-      <c r="A365" s="11"/>
-      <c r="B365" s="12"/>
-      <c r="C365" s="12"/>
-      <c r="D365" s="12"/>
-      <c r="E365" s="25" t="s">
+      <c r="C366" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="D366" s="22" t="s">
         <v>816</v>
       </c>
-      <c r="F365" s="26" t="s">
+      <c r="E366" s="23" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="366" customHeight="1" ht="15.0">
-      <c r="A366" s="11"/>
-      <c r="B366" s="12"/>
-      <c r="C366" s="12"/>
-      <c r="D366" s="12"/>
-      <c r="E366" s="25" t="s">
+      <c r="F366" s="24" t="s">
         <v>818</v>
       </c>
-      <c r="F366" s="26" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="367" customHeight="1" ht="88.0">
+    </row>
+    <row r="367" customHeight="1" ht="15.0">
       <c r="A367" s="11"/>
       <c r="B367" s="12"/>
       <c r="C367" s="12"/>
       <c r="D367" s="12"/>
       <c r="E367" s="25" t="s">
+        <v>819</v>
+      </c>
+      <c r="F367" s="26" t="s">
         <v>820</v>
       </c>
-      <c r="F367" s="26" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="368" customHeight="1" ht="42.0">
+    </row>
+    <row r="368" customHeight="1" ht="15.0">
       <c r="A368" s="11"/>
       <c r="B368" s="12"/>
       <c r="C368" s="12"/>
       <c r="D368" s="12"/>
       <c r="E368" s="25" t="s">
+        <v>821</v>
+      </c>
+      <c r="F368" s="26" t="s">
         <v>822</v>
       </c>
-      <c r="F368" s="26" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="369" customHeight="1" ht="42.0">
+    </row>
+    <row r="369" customHeight="1" ht="15.0">
       <c r="A369" s="11"/>
       <c r="B369" s="12"/>
       <c r="C369" s="12"/>
       <c r="D369" s="12"/>
       <c r="E369" s="25" t="s">
-        <v>824</v>
+        <v>777</v>
       </c>
       <c r="F369" s="26" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="370" customHeight="1" ht="15.0">
@@ -9084,10 +9434,10 @@
       <c r="C370" s="12"/>
       <c r="D370" s="12"/>
       <c r="E370" s="25" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="F370" s="26" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="371" customHeight="1" ht="15.0">
@@ -9096,174 +9446,174 @@
       <c r="C371" s="12"/>
       <c r="D371" s="12"/>
       <c r="E371" s="25" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="F371" s="26" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="372" customHeight="1" ht="53.0">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="372" customHeight="1" ht="15.0">
       <c r="A372" s="11"/>
       <c r="B372" s="12"/>
       <c r="C372" s="12"/>
       <c r="D372" s="12"/>
       <c r="E372" s="25" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="F372" s="26" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="373" customHeight="1" ht="105.0">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="373" customHeight="1" ht="15.0">
       <c r="A373" s="11"/>
       <c r="B373" s="12"/>
       <c r="C373" s="12"/>
       <c r="D373" s="12"/>
       <c r="E373" s="25" t="s">
+        <v>830</v>
+      </c>
+      <c r="F373" s="26" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="374" customHeight="1" ht="15.0">
+      <c r="A374" s="11"/>
+      <c r="B374" s="12"/>
+      <c r="C374" s="12"/>
+      <c r="D374" s="12"/>
+      <c r="E374" s="25" t="s">
         <v>832</v>
       </c>
-      <c r="F373" s="26" t="s">
+      <c r="F374" s="26" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="374" customHeight="1" ht="15.0">
-      <c r="A374" s="15"/>
-      <c r="B374" s="16"/>
-      <c r="C374" s="16"/>
-      <c r="D374" s="16"/>
-      <c r="E374" s="27" t="s">
+    <row r="375" customHeight="1" ht="15.0">
+      <c r="A375" s="11"/>
+      <c r="B375" s="12"/>
+      <c r="C375" s="12"/>
+      <c r="D375" s="12"/>
+      <c r="E375" s="25" t="s">
         <v>834</v>
       </c>
-      <c r="F374" s="28" t="s">
+      <c r="F375" s="26" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="375" customHeight="1" ht="15.0">
-      <c r="A375" s="5" t="s">
+    <row r="376" customHeight="1" ht="88.0">
+      <c r="A376" s="11"/>
+      <c r="B376" s="12"/>
+      <c r="C376" s="12"/>
+      <c r="D376" s="12"/>
+      <c r="E376" s="25" t="s">
         <v>836</v>
       </c>
-      <c r="B375" s="36" t="s">
+      <c r="F376" s="26" t="s">
         <v>837</v>
       </c>
-      <c r="C375" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="D375" s="8" t="s">
+    </row>
+    <row r="377" customHeight="1" ht="42.0">
+      <c r="A377" s="11"/>
+      <c r="B377" s="12"/>
+      <c r="C377" s="12"/>
+      <c r="D377" s="12"/>
+      <c r="E377" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="E375" s="9" t="s">
+      <c r="F377" s="26" t="s">
         <v>839</v>
       </c>
-      <c r="F375" s="10" t="s">
+    </row>
+    <row r="378" customHeight="1" ht="42.0">
+      <c r="A378" s="11"/>
+      <c r="B378" s="12"/>
+      <c r="C378" s="12"/>
+      <c r="D378" s="12"/>
+      <c r="E378" s="25" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="376" customHeight="1" ht="15.0">
-      <c r="A376" s="11"/>
-      <c r="B376" s="38"/>
-      <c r="C376" s="39"/>
-      <c r="D376" s="12"/>
-      <c r="E376" s="13" t="s">
+      <c r="F378" s="26" t="s">
         <v>841</v>
-      </c>
-      <c r="F376" s="14" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="377" customHeight="1" ht="15.0">
-      <c r="A377" s="11"/>
-      <c r="B377" s="38"/>
-      <c r="C377" s="39"/>
-      <c r="D377" s="12"/>
-      <c r="E377" s="13" t="s">
-        <v>843</v>
-      </c>
-      <c r="F377" s="14" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="378" customHeight="1" ht="15.0">
-      <c r="A378" s="11"/>
-      <c r="B378" s="38"/>
-      <c r="C378" s="39"/>
-      <c r="D378" s="12"/>
-      <c r="E378" s="13" t="s">
-        <v>845</v>
-      </c>
-      <c r="F378" s="14" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="379" customHeight="1" ht="15.0">
       <c r="A379" s="11"/>
-      <c r="B379" s="38"/>
-      <c r="C379" s="39"/>
+      <c r="B379" s="12"/>
+      <c r="C379" s="12"/>
       <c r="D379" s="12"/>
-      <c r="E379" s="13" t="s">
-        <v>847</v>
-      </c>
-      <c r="F379" s="14" t="s">
-        <v>848</v>
+      <c r="E379" s="25" t="s">
+        <v>842</v>
+      </c>
+      <c r="F379" s="26" t="s">
+        <v>843</v>
       </c>
     </row>
     <row r="380" customHeight="1" ht="15.0">
       <c r="A380" s="11"/>
-      <c r="B380" s="38"/>
-      <c r="C380" s="39"/>
+      <c r="B380" s="12"/>
+      <c r="C380" s="12"/>
       <c r="D380" s="12"/>
-      <c r="E380" s="13" t="s">
+      <c r="E380" s="25" t="s">
+        <v>844</v>
+      </c>
+      <c r="F380" s="26" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="381" customHeight="1" ht="53.0">
+      <c r="A381" s="11"/>
+      <c r="B381" s="12"/>
+      <c r="C381" s="12"/>
+      <c r="D381" s="12"/>
+      <c r="E381" s="25" t="s">
+        <v>846</v>
+      </c>
+      <c r="F381" s="26" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="382" customHeight="1" ht="105.0">
+      <c r="A382" s="11"/>
+      <c r="B382" s="12"/>
+      <c r="C382" s="12"/>
+      <c r="D382" s="12"/>
+      <c r="E382" s="25" t="s">
+        <v>848</v>
+      </c>
+      <c r="F382" s="26" t="s">
         <v>849</v>
       </c>
-      <c r="F380" s="14" t="s">
+    </row>
+    <row r="383" customHeight="1" ht="15.0">
+      <c r="A383" s="15"/>
+      <c r="B383" s="16"/>
+      <c r="C383" s="16"/>
+      <c r="D383" s="16"/>
+      <c r="E383" s="27" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="381" customHeight="1" ht="15.0">
-      <c r="A381" s="11"/>
-      <c r="B381" s="38"/>
-      <c r="C381" s="39"/>
-      <c r="D381" s="12"/>
-      <c r="E381" s="13" t="s">
+      <c r="F383" s="28" t="s">
         <v>851</v>
       </c>
-      <c r="F381" s="14" t="s">
+    </row>
+    <row r="384" customHeight="1" ht="15.0">
+      <c r="A384" s="5" t="s">
         <v>852</v>
       </c>
-    </row>
-    <row r="382" customHeight="1" ht="15.0">
-      <c r="A382" s="11"/>
-      <c r="B382" s="38"/>
-      <c r="C382" s="39"/>
-      <c r="D382" s="12"/>
-      <c r="E382" s="13" t="s">
+      <c r="B384" s="36" t="s">
         <v>853</v>
       </c>
-      <c r="F382" s="14" t="s">
+      <c r="C384" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="D384" s="8" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="383" customHeight="1" ht="15.0">
-      <c r="A383" s="11"/>
-      <c r="B383" s="38"/>
-      <c r="C383" s="39"/>
-      <c r="D383" s="12"/>
-      <c r="E383" s="13" t="s">
+      <c r="E384" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="F383" s="14" t="s">
+      <c r="F384" s="10" t="s">
         <v>856</v>
-      </c>
-    </row>
-    <row r="384" customHeight="1" ht="15.0">
-      <c r="A384" s="11"/>
-      <c r="B384" s="38"/>
-      <c r="C384" s="39"/>
-      <c r="D384" s="12"/>
-      <c r="E384" s="13" t="s">
-        <v>857</v>
-      </c>
-      <c r="F384" s="14" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="385" customHeight="1" ht="15.0">
@@ -9272,10 +9622,10 @@
       <c r="C385" s="39"/>
       <c r="D385" s="12"/>
       <c r="E385" s="13" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="F385" s="14" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="386" customHeight="1" ht="15.0">
@@ -9284,10 +9634,10 @@
       <c r="C386" s="39"/>
       <c r="D386" s="12"/>
       <c r="E386" s="13" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="F386" s="14" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="387" customHeight="1" ht="15.0">
@@ -9296,10 +9646,10 @@
       <c r="C387" s="39"/>
       <c r="D387" s="12"/>
       <c r="E387" s="13" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="F387" s="14" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="388" customHeight="1" ht="15.0">
@@ -9308,10 +9658,10 @@
       <c r="C388" s="39"/>
       <c r="D388" s="12"/>
       <c r="E388" s="13" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="F388" s="14" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="389" customHeight="1" ht="15.0">
@@ -9320,10 +9670,10 @@
       <c r="C389" s="39"/>
       <c r="D389" s="12"/>
       <c r="E389" s="13" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="F389" s="14" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="390" customHeight="1" ht="15.0">
@@ -9332,10 +9682,10 @@
       <c r="C390" s="39"/>
       <c r="D390" s="12"/>
       <c r="E390" s="13" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F390" s="14" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="391" customHeight="1" ht="15.0">
@@ -9344,10 +9694,10 @@
       <c r="C391" s="39"/>
       <c r="D391" s="12"/>
       <c r="E391" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="F391" s="14" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="392" customHeight="1" ht="15.0">
@@ -9356,10 +9706,10 @@
       <c r="C392" s="39"/>
       <c r="D392" s="12"/>
       <c r="E392" s="13" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="F392" s="14" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="393" customHeight="1" ht="15.0">
@@ -9368,10 +9718,10 @@
       <c r="C393" s="39"/>
       <c r="D393" s="12"/>
       <c r="E393" s="13" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="F393" s="14" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="394" customHeight="1" ht="15.0">
@@ -9380,10 +9730,10 @@
       <c r="C394" s="39"/>
       <c r="D394" s="12"/>
       <c r="E394" s="13" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="F394" s="14" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="395" customHeight="1" ht="15.0">
@@ -9391,491 +9741,482 @@
       <c r="B395" s="38"/>
       <c r="C395" s="39"/>
       <c r="D395" s="12"/>
-      <c r="E395" s="40" t="s">
+      <c r="E395" s="13" t="s">
+        <v>877</v>
+      </c>
+      <c r="F395" s="14" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="396" customHeight="1" ht="15.0">
+      <c r="A396" s="11"/>
+      <c r="B396" s="38"/>
+      <c r="C396" s="39"/>
+      <c r="D396" s="12"/>
+      <c r="E396" s="13" t="s">
         <v>879</v>
       </c>
-      <c r="F395" s="41" t="s">
+      <c r="F396" s="14" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="396" customHeight="1" ht="15.0">
-      <c r="A396" s="15"/>
-      <c r="B396" s="42"/>
-      <c r="C396" s="39"/>
-      <c r="D396" s="16"/>
-      <c r="E396" s="43" t="s">
+    <row r="397" customHeight="1" ht="15.0">
+      <c r="A397" s="11"/>
+      <c r="B397" s="38"/>
+      <c r="C397" s="39"/>
+      <c r="D397" s="12"/>
+      <c r="E397" s="13" t="s">
         <v>881</v>
       </c>
-      <c r="F396" s="44" t="s">
+      <c r="F397" s="14" t="s">
         <v>882</v>
       </c>
-      <c r="G396" s="45"/>
-    </row>
-    <row r="397" customHeight="1" ht="15.0">
-      <c r="A397" s="46" t="s">
+    </row>
+    <row r="398" customHeight="1" ht="15.0">
+      <c r="A398" s="11"/>
+      <c r="B398" s="38"/>
+      <c r="C398" s="39"/>
+      <c r="D398" s="12"/>
+      <c r="E398" s="13" t="s">
         <v>883</v>
       </c>
-      <c r="B397" s="47" t="s">
+      <c r="F398" s="14" t="s">
         <v>884</v>
       </c>
-      <c r="C397" s="48"/>
-      <c r="D397" s="49" t="s">
+    </row>
+    <row r="399" customHeight="1" ht="15.0">
+      <c r="A399" s="11"/>
+      <c r="B399" s="38"/>
+      <c r="C399" s="39"/>
+      <c r="D399" s="12"/>
+      <c r="E399" s="13" t="s">
         <v>885</v>
       </c>
-      <c r="E397" s="50" t="s">
+      <c r="F399" s="14" t="s">
         <v>886</v>
       </c>
-      <c r="F397" s="51" t="s">
+    </row>
+    <row r="400" customHeight="1" ht="15.0">
+      <c r="A400" s="11"/>
+      <c r="B400" s="38"/>
+      <c r="C400" s="39"/>
+      <c r="D400" s="12"/>
+      <c r="E400" s="13" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="398" customHeight="1" ht="15.0">
-      <c r="B398" s="39"/>
-      <c r="C398" s="39"/>
-      <c r="D398" s="52"/>
-      <c r="E398" s="25" t="s">
+      <c r="F400" s="14" t="s">
         <v>888</v>
       </c>
-      <c r="F398" s="26" t="s">
+    </row>
+    <row r="401" customHeight="1" ht="15.0">
+      <c r="A401" s="11"/>
+      <c r="B401" s="38"/>
+      <c r="C401" s="39"/>
+      <c r="D401" s="12"/>
+      <c r="E401" s="13" t="s">
         <v>889</v>
       </c>
-    </row>
-    <row r="399" customHeight="1" ht="15.0">
-      <c r="B399" s="39"/>
-      <c r="C399" s="39"/>
-      <c r="D399" s="52"/>
-      <c r="E399" s="25" t="s">
+      <c r="F401" s="14" t="s">
         <v>890</v>
       </c>
-      <c r="F399" s="26" t="s">
+    </row>
+    <row r="402" customHeight="1" ht="15.0">
+      <c r="A402" s="11"/>
+      <c r="B402" s="38"/>
+      <c r="C402" s="39"/>
+      <c r="D402" s="12"/>
+      <c r="E402" s="13" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="400" customHeight="1" ht="15.0">
-      <c r="B400" s="39"/>
-      <c r="C400" s="39"/>
-      <c r="D400" s="52"/>
-      <c r="E400" s="25" t="s">
+      <c r="F402" s="14" t="s">
         <v>892</v>
       </c>
-      <c r="F400" s="26" t="s">
+    </row>
+    <row r="403" customHeight="1" ht="15.0">
+      <c r="A403" s="11"/>
+      <c r="B403" s="38"/>
+      <c r="C403" s="39"/>
+      <c r="D403" s="12"/>
+      <c r="E403" s="13" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="401" customHeight="1" ht="19.0">
-      <c r="B401" s="39"/>
-      <c r="C401" s="39"/>
-      <c r="D401" s="52"/>
-      <c r="E401" s="25" t="s">
+      <c r="F403" s="14" t="s">
         <v>894</v>
       </c>
-      <c r="F401" s="26" t="s">
+    </row>
+    <row r="404" customHeight="1" ht="15.0">
+      <c r="A404" s="11"/>
+      <c r="B404" s="38"/>
+      <c r="C404" s="39"/>
+      <c r="D404" s="12"/>
+      <c r="E404" s="40" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="402" customHeight="1" ht="15.0">
-      <c r="B402" s="39"/>
-      <c r="C402" s="39"/>
-      <c r="D402" s="52"/>
-      <c r="E402" s="25" t="s">
+      <c r="F404" s="41" t="s">
         <v>896</v>
       </c>
-      <c r="F402" s="26" t="s">
+    </row>
+    <row r="405" customHeight="1" ht="15.0">
+      <c r="A405" s="15"/>
+      <c r="B405" s="42"/>
+      <c r="C405" s="39"/>
+      <c r="D405" s="16"/>
+      <c r="E405" s="43" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="403" customHeight="1" ht="15.0">
-      <c r="B403" s="39"/>
-      <c r="C403" s="39"/>
-      <c r="D403" s="52"/>
-      <c r="E403" s="25" t="s">
+      <c r="F405" s="44" t="s">
         <v>898</v>
       </c>
-      <c r="F403" s="26" t="s">
+      <c r="G405" s="45"/>
+    </row>
+    <row r="406" customHeight="1" ht="15.0">
+      <c r="A406" s="46" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="404" customHeight="1" ht="15.0">
-      <c r="B404" s="39"/>
-      <c r="C404" s="39"/>
-      <c r="D404" s="52"/>
-      <c r="E404" s="25" t="s">
-        <v>297</v>
-      </c>
-      <c r="F404" s="26" t="s">
+      <c r="B406" s="47" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="405" customHeight="1" ht="15.0">
-      <c r="B405" s="39"/>
-      <c r="C405" s="39"/>
-      <c r="D405" s="53"/>
-      <c r="E405" s="54" t="s">
-        <v>295</v>
-      </c>
-      <c r="F405" s="55" t="s">
+      <c r="C406" s="48"/>
+      <c r="D406" s="49" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="406" customHeight="1" ht="15.0">
-      <c r="B406" s="39"/>
-      <c r="C406" s="39"/>
-      <c r="D406" s="56" t="s">
+      <c r="E406" s="50" t="s">
         <v>902</v>
       </c>
-      <c r="E406" s="54" t="s">
-        <v>671</v>
-      </c>
-      <c r="F406" s="55" t="s">
+      <c r="F406" s="51" t="s">
         <v>903</v>
       </c>
-      <c r="G406" s="45"/>
     </row>
     <row r="407" customHeight="1" ht="15.0">
       <c r="B407" s="39"/>
       <c r="C407" s="39"/>
       <c r="D407" s="52"/>
-      <c r="E407" s="54" t="s">
-        <v>673</v>
-      </c>
-      <c r="F407" s="55" t="s">
+      <c r="E407" s="25" t="s">
         <v>904</v>
       </c>
-      <c r="G407" s="45"/>
-    </row>
-    <row r="408" customHeight="1" ht="24.0">
-      <c r="A408" s="57"/>
-      <c r="B408" s="58"/>
+      <c r="F407" s="26" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="408" customHeight="1" ht="15.0">
+      <c r="B408" s="39"/>
       <c r="C408" s="39"/>
-      <c r="D408" s="53"/>
-      <c r="E408" s="54" t="s">
-        <v>905</v>
-      </c>
-      <c r="F408" s="55" t="s">
+      <c r="D408" s="52"/>
+      <c r="E408" s="25" t="s">
         <v>906</v>
       </c>
-      <c r="G408" s="45"/>
-    </row>
-    <row r="409" customHeight="1" ht="24.0">
-      <c r="A409" s="59">
+      <c r="F408" s="26" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="409" customHeight="1" ht="15.0">
+      <c r="B409" s="39"/>
+      <c r="C409" s="39"/>
+      <c r="D409" s="52"/>
+      <c r="E409" s="25" t="s">
+        <v>908</v>
+      </c>
+      <c r="F409" s="26" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="410" customHeight="1" ht="19.0">
+      <c r="B410" s="39"/>
+      <c r="C410" s="39"/>
+      <c r="D410" s="52"/>
+      <c r="E410" s="25" t="s">
+        <v>910</v>
+      </c>
+      <c r="F410" s="26" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="411" customHeight="1" ht="15.0">
+      <c r="B411" s="39"/>
+      <c r="C411" s="39"/>
+      <c r="D411" s="52"/>
+      <c r="E411" s="25" t="s">
+        <v>912</v>
+      </c>
+      <c r="F411" s="26" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="412" customHeight="1" ht="15.0">
+      <c r="B412" s="39"/>
+      <c r="C412" s="39"/>
+      <c r="D412" s="52"/>
+      <c r="E412" s="25" t="s">
+        <v>914</v>
+      </c>
+      <c r="F412" s="26" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="413" customHeight="1" ht="15.0">
+      <c r="B413" s="39"/>
+      <c r="C413" s="39"/>
+      <c r="D413" s="52"/>
+      <c r="E413" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="F413" s="26" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="414" customHeight="1" ht="15.0">
+      <c r="B414" s="39"/>
+      <c r="C414" s="39"/>
+      <c r="D414" s="53"/>
+      <c r="E414" s="54" t="s">
+        <v>295</v>
+      </c>
+      <c r="F414" s="55" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="415" customHeight="1" ht="15.0">
+      <c r="B415" s="39"/>
+      <c r="C415" s="39"/>
+      <c r="D415" s="56" t="s">
+        <v>918</v>
+      </c>
+      <c r="E415" s="54" t="s">
+        <v>675</v>
+      </c>
+      <c r="F415" s="55" t="s">
+        <v>919</v>
+      </c>
+      <c r="G415" s="45"/>
+    </row>
+    <row r="416" customHeight="1" ht="15.0">
+      <c r="B416" s="39"/>
+      <c r="C416" s="39"/>
+      <c r="D416" s="52"/>
+      <c r="E416" s="54" t="s">
+        <v>677</v>
+      </c>
+      <c r="F416" s="55" t="s">
+        <v>920</v>
+      </c>
+      <c r="G416" s="45"/>
+    </row>
+    <row r="417" customHeight="1" ht="24.0">
+      <c r="A417" s="57"/>
+      <c r="B417" s="58"/>
+      <c r="C417" s="39"/>
+      <c r="D417" s="53"/>
+      <c r="E417" s="54" t="s">
+        <v>921</v>
+      </c>
+      <c r="F417" s="55" t="s">
+        <v>922</v>
+      </c>
+      <c r="G417" s="45"/>
+    </row>
+    <row r="418" customHeight="1" ht="24.0">
+      <c r="A418" s="59">
         <v>35.0</v>
       </c>
-      <c r="B409" s="37" t="s">
-        <v>907</v>
-      </c>
-      <c r="C409" s="60"/>
-      <c r="D409" s="61" t="s">
-        <v>908</v>
-      </c>
-      <c r="E409" s="62" t="s">
-        <v>909</v>
-      </c>
-      <c r="F409" s="63"/>
-      <c r="G409" s="45"/>
-    </row>
-    <row r="410" customHeight="1" ht="24.0">
-      <c r="A410" s="64"/>
-      <c r="B410" s="60"/>
-      <c r="C410" s="60"/>
-      <c r="D410" s="65"/>
-      <c r="E410" s="66" t="s">
-        <v>910</v>
-      </c>
-      <c r="F410" s="67" t="s">
-        <v>911</v>
-      </c>
-      <c r="G410" s="45"/>
-    </row>
-    <row r="411" customHeight="1" ht="24.0">
-      <c r="A411" s="64"/>
-      <c r="B411" s="60"/>
-      <c r="C411" s="60"/>
-      <c r="D411" s="65"/>
-      <c r="E411" s="66" t="s">
-        <v>912</v>
-      </c>
-      <c r="F411" s="67" t="s">
-        <v>913</v>
-      </c>
-      <c r="G411" s="45"/>
-    </row>
-    <row r="412" customHeight="1" ht="24.0">
-      <c r="A412" s="64"/>
-      <c r="B412" s="60"/>
-      <c r="C412" s="60"/>
-      <c r="D412" s="65"/>
-      <c r="E412" s="66" t="s">
-        <v>914</v>
-      </c>
-      <c r="F412" s="67" t="s">
-        <v>915</v>
-      </c>
-      <c r="G412" s="45"/>
-    </row>
-    <row r="413" customHeight="1" ht="24.0">
-      <c r="A413" s="64"/>
-      <c r="B413" s="60"/>
-      <c r="C413" s="60"/>
-      <c r="D413" s="65"/>
-      <c r="E413" s="66" t="s">
-        <v>916</v>
-      </c>
-      <c r="F413" s="67" t="s">
-        <v>917</v>
-      </c>
-      <c r="G413" s="45"/>
-    </row>
-    <row r="414" customHeight="1" ht="24.0">
-      <c r="A414" s="64"/>
-      <c r="B414" s="60"/>
-      <c r="C414" s="60"/>
-      <c r="D414" s="65"/>
-      <c r="E414" s="66" t="s">
-        <v>918</v>
-      </c>
-      <c r="F414" s="67" t="s">
-        <v>919</v>
-      </c>
-      <c r="G414" s="45"/>
-    </row>
-    <row r="415" customHeight="1" ht="24.0">
-      <c r="A415" s="64"/>
-      <c r="B415" s="60"/>
-      <c r="C415" s="60"/>
-      <c r="D415" s="65"/>
-      <c r="E415" s="66" t="s">
-        <v>920</v>
-      </c>
-      <c r="F415" s="67" t="s">
-        <v>921</v>
-      </c>
-      <c r="G415" s="45"/>
-    </row>
-    <row r="416" customHeight="1" ht="24.0">
-      <c r="A416" s="64"/>
-      <c r="B416" s="60"/>
-      <c r="C416" s="60"/>
-      <c r="D416" s="65"/>
-      <c r="E416" s="66" t="s">
-        <v>922</v>
-      </c>
-      <c r="F416" s="67" t="s">
+      <c r="B418" s="37" t="s">
         <v>923</v>
       </c>
-      <c r="G416" s="45"/>
-    </row>
-    <row r="417" customHeight="1" ht="24.0">
-      <c r="A417" s="64"/>
-      <c r="B417" s="60"/>
-      <c r="C417" s="60"/>
-      <c r="D417" s="65"/>
-      <c r="E417" s="68" t="s">
+      <c r="C418" s="60"/>
+      <c r="D418" s="61" t="s">
         <v>924</v>
       </c>
-      <c r="F417" s="69" t="s">
+      <c r="E418" s="62" t="s">
         <v>925</v>
       </c>
-      <c r="G417" s="45"/>
-    </row>
-    <row r="418" customHeight="1" ht="36.0">
-      <c r="A418" s="64"/>
-      <c r="B418" s="60"/>
-      <c r="C418" s="60"/>
-      <c r="D418" s="65"/>
-      <c r="E418" s="68" t="s">
+      <c r="F418" s="63"/>
+      <c r="G418" s="45"/>
+    </row>
+    <row r="419" customHeight="1" ht="24.0">
+      <c r="A419" s="64"/>
+      <c r="B419" s="60"/>
+      <c r="C419" s="60"/>
+      <c r="D419" s="65"/>
+      <c r="E419" s="66" t="s">
         <v>926</v>
       </c>
-      <c r="F418" s="69" t="s">
+      <c r="F419" s="67" t="s">
         <v>927</v>
       </c>
-      <c r="G418" s="45"/>
-    </row>
-    <row r="419" customHeight="1" ht="15.0">
-      <c r="B419" s="39"/>
-      <c r="C419" s="39"/>
-      <c r="D419" s="52"/>
-      <c r="E419" s="70" t="s">
+      <c r="G419" s="45"/>
+    </row>
+    <row r="420" customHeight="1" ht="24.0">
+      <c r="A420" s="64"/>
+      <c r="B420" s="60"/>
+      <c r="C420" s="60"/>
+      <c r="D420" s="65"/>
+      <c r="E420" s="66" t="s">
         <v>928</v>
       </c>
-      <c r="F419" s="14" t="s">
+      <c r="F420" s="67" t="s">
         <v>929</v>
       </c>
-    </row>
-    <row r="420" customHeight="1" ht="15.0">
-      <c r="B420" s="39"/>
-      <c r="C420" s="39"/>
-      <c r="D420" s="52"/>
-      <c r="E420" s="70" t="s">
+      <c r="G420" s="45"/>
+    </row>
+    <row r="421" customHeight="1" ht="24.0">
+      <c r="A421" s="64"/>
+      <c r="B421" s="60"/>
+      <c r="C421" s="60"/>
+      <c r="D421" s="65"/>
+      <c r="E421" s="66" t="s">
         <v>930</v>
       </c>
-      <c r="F420" s="14" t="s">
+      <c r="F421" s="67" t="s">
         <v>931</v>
       </c>
-    </row>
-    <row r="421" customHeight="1" ht="15.0">
-      <c r="B421" s="39"/>
-      <c r="C421" s="39"/>
-      <c r="D421" s="52"/>
-      <c r="E421" s="70" t="s">
+      <c r="G421" s="45"/>
+    </row>
+    <row r="422" customHeight="1" ht="24.0">
+      <c r="A422" s="64"/>
+      <c r="B422" s="60"/>
+      <c r="C422" s="60"/>
+      <c r="D422" s="65"/>
+      <c r="E422" s="66" t="s">
         <v>932</v>
       </c>
-      <c r="F421" s="14" t="s">
+      <c r="F422" s="67" t="s">
         <v>933</v>
       </c>
-    </row>
-    <row r="422" customHeight="1" ht="15.0">
-      <c r="B422" s="39"/>
-      <c r="C422" s="39"/>
-      <c r="D422" s="52"/>
-      <c r="E422" s="70" t="s">
+      <c r="G422" s="45"/>
+    </row>
+    <row r="423" customHeight="1" ht="24.0">
+      <c r="A423" s="64"/>
+      <c r="B423" s="60"/>
+      <c r="C423" s="60"/>
+      <c r="D423" s="65"/>
+      <c r="E423" s="66" t="s">
         <v>934</v>
       </c>
-      <c r="F422" s="14" t="s">
+      <c r="F423" s="67" t="s">
         <v>935</v>
       </c>
-    </row>
-    <row r="423" customHeight="1" ht="15.0">
-      <c r="A423" s="54"/>
-      <c r="B423" s="55"/>
-      <c r="C423" s="54"/>
-      <c r="D423" s="71"/>
-      <c r="E423" s="52"/>
-      <c r="F423" s="45"/>
       <c r="G423" s="45"/>
     </row>
-    <row r="424" customHeight="1" ht="15.0">
-      <c r="A424" s="72">
+    <row r="424" customHeight="1" ht="24.0">
+      <c r="A424" s="64"/>
+      <c r="B424" s="60"/>
+      <c r="C424" s="60"/>
+      <c r="D424" s="65"/>
+      <c r="E424" s="66" t="s">
+        <v>936</v>
+      </c>
+      <c r="F424" s="67" t="s">
+        <v>937</v>
+      </c>
+      <c r="G424" s="45"/>
+    </row>
+    <row r="425" customHeight="1" ht="24.0">
+      <c r="A425" s="64"/>
+      <c r="B425" s="60"/>
+      <c r="C425" s="60"/>
+      <c r="D425" s="65"/>
+      <c r="E425" s="66" t="s">
+        <v>938</v>
+      </c>
+      <c r="F425" s="67" t="s">
+        <v>939</v>
+      </c>
+      <c r="G425" s="45"/>
+    </row>
+    <row r="426" customHeight="1" ht="24.0">
+      <c r="A426" s="64"/>
+      <c r="B426" s="60"/>
+      <c r="C426" s="60"/>
+      <c r="D426" s="65"/>
+      <c r="E426" s="68" t="s">
+        <v>940</v>
+      </c>
+      <c r="F426" s="69" t="s">
+        <v>941</v>
+      </c>
+      <c r="G426" s="45"/>
+    </row>
+    <row r="427" customHeight="1" ht="36.0">
+      <c r="A427" s="64"/>
+      <c r="B427" s="60"/>
+      <c r="C427" s="60"/>
+      <c r="D427" s="65"/>
+      <c r="E427" s="68" t="s">
+        <v>942</v>
+      </c>
+      <c r="F427" s="69" t="s">
+        <v>943</v>
+      </c>
+      <c r="G427" s="45"/>
+    </row>
+    <row r="428" customHeight="1" ht="15.0">
+      <c r="B428" s="39"/>
+      <c r="C428" s="39"/>
+      <c r="D428" s="52"/>
+      <c r="E428" s="70" t="s">
+        <v>944</v>
+      </c>
+      <c r="F428" s="14" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="429" customHeight="1" ht="15.0">
+      <c r="B429" s="39"/>
+      <c r="C429" s="39"/>
+      <c r="D429" s="52"/>
+      <c r="E429" s="70" t="s">
+        <v>946</v>
+      </c>
+      <c r="F429" s="14" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="430" customHeight="1" ht="15.0">
+      <c r="B430" s="39"/>
+      <c r="C430" s="39"/>
+      <c r="D430" s="52"/>
+      <c r="E430" s="70" t="s">
+        <v>948</v>
+      </c>
+      <c r="F430" s="14" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="431" customHeight="1" ht="15.0">
+      <c r="B431" s="39"/>
+      <c r="C431" s="39"/>
+      <c r="D431" s="52"/>
+      <c r="E431" s="70" t="s">
+        <v>950</v>
+      </c>
+      <c r="F431" s="14" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="432" customHeight="1" ht="15.0">
+      <c r="A432" s="54"/>
+      <c r="B432" s="55"/>
+      <c r="C432" s="54"/>
+      <c r="D432" s="71"/>
+      <c r="E432" s="52"/>
+      <c r="F432" s="45"/>
+      <c r="G432" s="45"/>
+    </row>
+    <row r="433" customHeight="1" ht="15.0">
+      <c r="A433" s="72">
         <v>36.0</v>
       </c>
-      <c r="B424" s="73">
+      <c r="B433" s="73">
         <v>46107.0</v>
       </c>
-      <c r="C424" s="72" t="s">
-        <v>936</v>
-      </c>
-      <c r="D424" s="72"/>
-      <c r="E424" s="43" t="s">
-        <v>937</v>
-      </c>
-      <c r="F424" s="44" t="s">
-        <v>938</v>
-      </c>
-      <c r="G424" s="45"/>
-    </row>
-    <row r="425" customHeight="1" ht="15.0">
-      <c r="A425" s="52"/>
-      <c r="B425" s="52"/>
-      <c r="C425" s="52"/>
-      <c r="D425" s="52"/>
-      <c r="E425" s="43" t="s">
-        <v>939</v>
-      </c>
-      <c r="F425" s="44" t="s">
-        <v>940</v>
-      </c>
-      <c r="G425" s="45"/>
-    </row>
-    <row r="426" customHeight="1" ht="31.0">
-      <c r="A426" s="52"/>
-      <c r="B426" s="52"/>
-      <c r="C426" s="52"/>
-      <c r="D426" s="52"/>
-      <c r="E426" s="43" t="s">
-        <v>941</v>
-      </c>
-      <c r="F426" s="44" t="s">
-        <v>942</v>
-      </c>
-      <c r="G426" s="45"/>
-    </row>
-    <row r="427" customHeight="1" ht="15.0">
-      <c r="A427" s="52"/>
-      <c r="B427" s="52"/>
-      <c r="C427" s="52"/>
-      <c r="D427" s="52"/>
-      <c r="E427" s="43" t="s">
-        <v>943</v>
-      </c>
-      <c r="F427" s="44" t="s">
-        <v>944</v>
-      </c>
-      <c r="G427" s="45"/>
-    </row>
-    <row r="428" customHeight="1" ht="15.0">
-      <c r="A428" s="52"/>
-      <c r="B428" s="52"/>
-      <c r="C428" s="52"/>
-      <c r="D428" s="52"/>
-      <c r="E428" s="43" t="s">
-        <v>945</v>
-      </c>
-      <c r="F428" s="44" t="s">
-        <v>946</v>
-      </c>
-      <c r="G428" s="45"/>
-    </row>
-    <row r="429" customHeight="1" ht="15.0">
-      <c r="A429" s="52"/>
-      <c r="B429" s="52"/>
-      <c r="C429" s="52"/>
-      <c r="D429" s="52"/>
-      <c r="E429" s="43" t="s">
-        <v>947</v>
-      </c>
-      <c r="F429" s="44" t="s">
-        <v>948</v>
-      </c>
-      <c r="G429" s="45"/>
-    </row>
-    <row r="430" customHeight="1" ht="15.0">
-      <c r="A430" s="52"/>
-      <c r="B430" s="52"/>
-      <c r="C430" s="52"/>
-      <c r="D430" s="52"/>
-      <c r="E430" s="43" t="s">
-        <v>949</v>
-      </c>
-      <c r="F430" s="44" t="s">
-        <v>950</v>
-      </c>
-      <c r="G430" s="45"/>
-    </row>
-    <row r="431" customHeight="1" ht="15.0">
-      <c r="A431" s="52"/>
-      <c r="B431" s="52"/>
-      <c r="C431" s="52"/>
-      <c r="D431" s="52"/>
-      <c r="E431" s="43" t="s">
-        <v>951</v>
-      </c>
-      <c r="F431" s="44" t="s">
+      <c r="C433" s="72" t="s">
         <v>952</v>
       </c>
-      <c r="G431" s="45"/>
-    </row>
-    <row r="432" customHeight="1" ht="15.0">
-      <c r="A432" s="52"/>
-      <c r="B432" s="52"/>
-      <c r="C432" s="52"/>
-      <c r="D432" s="52"/>
-      <c r="E432" s="43" t="s">
+      <c r="D433" s="72"/>
+      <c r="E433" s="43" t="s">
         <v>953</v>
       </c>
-      <c r="F432" s="44" t="s">
+      <c r="F433" s="44" t="s">
         <v>954</v>
-      </c>
-      <c r="G432" s="45"/>
-    </row>
-    <row r="433" customHeight="1" ht="15.0">
-      <c r="A433" s="52"/>
-      <c r="B433" s="52"/>
-      <c r="C433" s="52"/>
-      <c r="D433" s="52"/>
-      <c r="E433" s="43" t="s">
-        <v>955</v>
-      </c>
-      <c r="F433" s="44" t="s">
-        <v>956</v>
       </c>
       <c r="G433" s="45"/>
     </row>
@@ -9885,23 +10226,25 @@
       <c r="C434" s="52"/>
       <c r="D434" s="52"/>
       <c r="E434" s="43" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F434" s="44" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="435" customHeight="1" ht="15.0">
+        <v>956</v>
+      </c>
+      <c r="G434" s="45"/>
+    </row>
+    <row r="435" customHeight="1" ht="31.0">
       <c r="A435" s="52"/>
       <c r="B435" s="52"/>
       <c r="C435" s="52"/>
       <c r="D435" s="52"/>
       <c r="E435" s="43" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="F435" s="44" t="s">
-        <v>960</v>
-      </c>
+        <v>958</v>
+      </c>
+      <c r="G435" s="45"/>
     </row>
     <row r="436" customHeight="1" ht="15.0">
       <c r="A436" s="52"/>
@@ -9909,11 +10252,12 @@
       <c r="C436" s="52"/>
       <c r="D436" s="52"/>
       <c r="E436" s="43" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="F436" s="44" t="s">
-        <v>962</v>
-      </c>
+        <v>960</v>
+      </c>
+      <c r="G436" s="45"/>
     </row>
     <row r="437" customHeight="1" ht="15.0">
       <c r="A437" s="52"/>
@@ -9921,146 +10265,151 @@
       <c r="C437" s="52"/>
       <c r="D437" s="52"/>
       <c r="E437" s="43" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F437" s="44" t="s">
-        <v>964</v>
-      </c>
+        <v>962</v>
+      </c>
+      <c r="G437" s="45"/>
     </row>
     <row r="438" customHeight="1" ht="15.0">
-      <c r="A438" s="53"/>
+      <c r="A438" s="52"/>
       <c r="B438" s="52"/>
       <c r="C438" s="52"/>
       <c r="D438" s="52"/>
       <c r="E438" s="43" t="s">
+        <v>963</v>
+      </c>
+      <c r="F438" s="44" t="s">
+        <v>964</v>
+      </c>
+      <c r="G438" s="45"/>
+    </row>
+    <row r="439" customHeight="1" ht="15.0">
+      <c r="A439" s="52"/>
+      <c r="B439" s="52"/>
+      <c r="C439" s="52"/>
+      <c r="D439" s="52"/>
+      <c r="E439" s="43" t="s">
         <v>965</v>
       </c>
-      <c r="F438" s="44" t="s">
+      <c r="F439" s="44" t="s">
         <v>966</v>
       </c>
-    </row>
-    <row r="439" customHeight="1" ht="15.0">
-      <c r="A439" s="74">
+      <c r="G439" s="45"/>
+    </row>
+    <row r="440" customHeight="1" ht="15.0">
+      <c r="A440" s="52"/>
+      <c r="B440" s="52"/>
+      <c r="C440" s="52"/>
+      <c r="D440" s="52"/>
+      <c r="E440" s="43" t="s">
+        <v>967</v>
+      </c>
+      <c r="F440" s="44" t="s">
+        <v>968</v>
+      </c>
+      <c r="G440" s="45"/>
+    </row>
+    <row r="441" customHeight="1" ht="15.0">
+      <c r="A441" s="52"/>
+      <c r="B441" s="52"/>
+      <c r="C441" s="52"/>
+      <c r="D441" s="52"/>
+      <c r="E441" s="43" t="s">
+        <v>969</v>
+      </c>
+      <c r="F441" s="44" t="s">
+        <v>970</v>
+      </c>
+      <c r="G441" s="45"/>
+    </row>
+    <row r="442" customHeight="1" ht="15.0">
+      <c r="A442" s="52"/>
+      <c r="B442" s="52"/>
+      <c r="C442" s="52"/>
+      <c r="D442" s="52"/>
+      <c r="E442" s="43" t="s">
+        <v>971</v>
+      </c>
+      <c r="F442" s="44" t="s">
+        <v>972</v>
+      </c>
+      <c r="G442" s="45"/>
+    </row>
+    <row r="443" customHeight="1" ht="15.0">
+      <c r="A443" s="52"/>
+      <c r="B443" s="52"/>
+      <c r="C443" s="52"/>
+      <c r="D443" s="52"/>
+      <c r="E443" s="43" t="s">
+        <v>973</v>
+      </c>
+      <c r="F443" s="44" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="444" customHeight="1" ht="15.0">
+      <c r="A444" s="52"/>
+      <c r="B444" s="52"/>
+      <c r="C444" s="52"/>
+      <c r="D444" s="52"/>
+      <c r="E444" s="43" t="s">
+        <v>975</v>
+      </c>
+      <c r="F444" s="44" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="445" customHeight="1" ht="15.0">
+      <c r="A445" s="52"/>
+      <c r="B445" s="52"/>
+      <c r="C445" s="52"/>
+      <c r="D445" s="52"/>
+      <c r="E445" s="43" t="s">
+        <v>977</v>
+      </c>
+      <c r="F445" s="44" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="446" customHeight="1" ht="15.0">
+      <c r="A446" s="52"/>
+      <c r="B446" s="52"/>
+      <c r="C446" s="52"/>
+      <c r="D446" s="52"/>
+      <c r="E446" s="43" t="s">
+        <v>979</v>
+      </c>
+      <c r="F446" s="44" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="447" customHeight="1" ht="15.0">
+      <c r="A447" s="53"/>
+      <c r="B447" s="52"/>
+      <c r="C447" s="52"/>
+      <c r="D447" s="52"/>
+      <c r="E447" s="43" t="s">
+        <v>981</v>
+      </c>
+      <c r="F447" s="44" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="448" customHeight="1" ht="15.0">
+      <c r="A448" s="74">
         <v>37.0</v>
       </c>
-      <c r="B439" s="75">
-        <v>46108</v>
-      </c>
-      <c r="C439" s="76" t="s">
+      <c r="B448" s="75">
+        <v>46108.0</v>
+      </c>
+      <c r="C448" s="76" t="s">
         <v>333</v>
       </c>
-      <c r="D439" s="72"/>
-      <c r="E439" s="77" t="s">
+      <c r="D448" s="72"/>
+      <c r="E448" s="77" t="s">
         <v>462</v>
-      </c>
-      <c r="F439" s="25" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="440" customHeight="1" ht="15.0">
-      <c r="A440" s="78"/>
-      <c r="B440" s="79"/>
-      <c r="C440" s="80"/>
-      <c r="D440" s="81"/>
-      <c r="E440" s="77" t="s">
-        <v>464</v>
-      </c>
-      <c r="F440" s="25" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="441" customHeight="1" ht="15.0">
-      <c r="A441" s="78"/>
-      <c r="B441" s="79"/>
-      <c r="C441" s="80"/>
-      <c r="D441" s="81"/>
-      <c r="E441" s="77" t="s">
-        <v>969</v>
-      </c>
-      <c r="F441" s="25" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="442" customHeight="1" ht="15.0">
-      <c r="A442" s="78"/>
-      <c r="B442" s="79"/>
-      <c r="C442" s="80"/>
-      <c r="D442" s="81"/>
-      <c r="E442" s="77" t="s">
-        <v>413</v>
-      </c>
-      <c r="F442" s="25" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="443" customHeight="1" ht="15.0">
-      <c r="A443" s="78"/>
-      <c r="B443" s="79"/>
-      <c r="C443" s="80"/>
-      <c r="D443" s="81"/>
-      <c r="E443" s="77" t="s">
-        <v>972</v>
-      </c>
-      <c r="F443" s="25" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="444" customHeight="1" ht="15.0">
-      <c r="A444" s="78"/>
-      <c r="B444" s="79"/>
-      <c r="C444" s="80"/>
-      <c r="D444" s="81"/>
-      <c r="E444" s="77" t="s">
-        <v>974</v>
-      </c>
-      <c r="F444" s="25" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="445" customHeight="1" ht="15.0">
-      <c r="A445" s="78"/>
-      <c r="B445" s="79"/>
-      <c r="C445" s="80"/>
-      <c r="D445" s="81"/>
-      <c r="E445" s="77" t="s">
-        <v>976</v>
-      </c>
-      <c r="F445" s="25" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="446" customHeight="1" ht="15.0">
-      <c r="A446" s="78"/>
-      <c r="B446" s="79"/>
-      <c r="C446" s="80"/>
-      <c r="D446" s="81"/>
-      <c r="E446" s="77" t="s">
-        <v>978</v>
-      </c>
-      <c r="F446" s="25" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="447" customHeight="1" ht="15.0">
-      <c r="A447" s="78"/>
-      <c r="B447" s="79"/>
-      <c r="C447" s="80"/>
-      <c r="D447" s="81"/>
-      <c r="E447" s="77" t="s">
-        <v>980</v>
-      </c>
-      <c r="F447" s="25" t="s">
-        <v>981</v>
-      </c>
-      <c r="G447" s="82"/>
-    </row>
-    <row r="448" customHeight="1" ht="15.0">
-      <c r="A448" s="78"/>
-      <c r="B448" s="79"/>
-      <c r="C448" s="80"/>
-      <c r="D448" s="81"/>
-      <c r="E448" s="77" t="s">
-        <v>982</v>
       </c>
       <c r="F448" s="25" t="s">
         <v>983</v>
@@ -10069,752 +10418,1274 @@
     <row r="449" customHeight="1" ht="15.0">
       <c r="A449" s="78"/>
       <c r="B449" s="79"/>
-      <c r="C449" s="80"/>
-      <c r="D449" s="81"/>
+      <c r="C449" s="12"/>
+      <c r="D449" s="52"/>
       <c r="E449" s="77" t="s">
+        <v>464</v>
+      </c>
+      <c r="F449" s="25" t="s">
         <v>984</v>
-      </c>
-      <c r="F449" s="25" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="450" customHeight="1" ht="15.0">
       <c r="A450" s="78"/>
       <c r="B450" s="79"/>
-      <c r="C450" s="80"/>
-      <c r="D450" s="81"/>
+      <c r="C450" s="12"/>
+      <c r="D450" s="52"/>
       <c r="E450" s="77" t="s">
+        <v>985</v>
+      </c>
+      <c r="F450" s="25" t="s">
         <v>986</v>
-      </c>
-      <c r="F450" s="25" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="451" customHeight="1" ht="15.0">
       <c r="A451" s="78"/>
       <c r="B451" s="79"/>
-      <c r="C451" s="80"/>
-      <c r="D451" s="81"/>
+      <c r="C451" s="12"/>
+      <c r="D451" s="52"/>
       <c r="E451" s="77" t="s">
-        <v>988</v>
+        <v>413</v>
       </c>
       <c r="F451" s="25" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="452" customHeight="1" ht="15.0">
       <c r="A452" s="78"/>
       <c r="B452" s="79"/>
-      <c r="C452" s="80"/>
-      <c r="D452" s="81"/>
+      <c r="C452" s="12"/>
+      <c r="D452" s="52"/>
       <c r="E452" s="77" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F452" s="25" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="453" customHeight="1" ht="15.0">
       <c r="A453" s="78"/>
       <c r="B453" s="79"/>
-      <c r="C453" s="80"/>
-      <c r="D453" s="81"/>
+      <c r="C453" s="12"/>
+      <c r="D453" s="52"/>
       <c r="E453" s="77" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="F453" s="25" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="454" customHeight="1" ht="15.0">
       <c r="A454" s="78"/>
       <c r="B454" s="79"/>
-      <c r="C454" s="80"/>
-      <c r="D454" s="81"/>
+      <c r="C454" s="12"/>
+      <c r="D454" s="52"/>
       <c r="E454" s="77" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="F454" s="25" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="455" customHeight="1" ht="15.0">
       <c r="A455" s="78"/>
       <c r="B455" s="79"/>
-      <c r="C455" s="80"/>
-      <c r="D455" s="81"/>
+      <c r="C455" s="12"/>
+      <c r="D455" s="52"/>
       <c r="E455" s="77" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="F455" s="25" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="456" customHeight="1" ht="15.0">
       <c r="A456" s="78"/>
       <c r="B456" s="79"/>
-      <c r="C456" s="80"/>
-      <c r="D456" s="81"/>
+      <c r="C456" s="12"/>
+      <c r="D456" s="52"/>
       <c r="E456" s="77" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="F456" s="25" t="s">
-        <v>999</v>
-      </c>
+        <v>997</v>
+      </c>
+      <c r="G456" s="45"/>
     </row>
     <row r="457" customHeight="1" ht="15.0">
       <c r="A457" s="78"/>
       <c r="B457" s="79"/>
-      <c r="C457" s="80"/>
-      <c r="D457" s="81"/>
+      <c r="C457" s="12"/>
+      <c r="D457" s="52"/>
       <c r="E457" s="77" t="s">
-        <v>436</v>
+        <v>998</v>
       </c>
       <c r="F457" s="25" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="458" customHeight="1" ht="15.0">
       <c r="A458" s="78"/>
       <c r="B458" s="79"/>
-      <c r="C458" s="80"/>
-      <c r="D458" s="81"/>
+      <c r="C458" s="12"/>
+      <c r="D458" s="52"/>
       <c r="E458" s="77" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F458" s="25" t="s">
         <v>1001</v>
-      </c>
-      <c r="F458" s="25" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="459" customHeight="1" ht="15.0">
       <c r="A459" s="78"/>
       <c r="B459" s="79"/>
-      <c r="C459" s="80"/>
-      <c r="D459" s="81"/>
+      <c r="C459" s="12"/>
+      <c r="D459" s="52"/>
       <c r="E459" s="77" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F459" s="25" t="s">
         <v>1003</v>
-      </c>
-      <c r="F459" s="25" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="460" customHeight="1" ht="15.0">
       <c r="A460" s="78"/>
       <c r="B460" s="79"/>
-      <c r="C460" s="80"/>
-      <c r="D460" s="81"/>
+      <c r="C460" s="12"/>
+      <c r="D460" s="52"/>
       <c r="E460" s="77" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F460" s="25" t="s">
         <v>1005</v>
-      </c>
-      <c r="F460" s="25" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="461" customHeight="1" ht="15.0">
       <c r="A461" s="78"/>
       <c r="B461" s="79"/>
-      <c r="C461" s="80"/>
-      <c r="D461" s="81"/>
+      <c r="C461" s="12"/>
+      <c r="D461" s="52"/>
       <c r="E461" s="77" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F461" s="25" t="s">
         <v>1007</v>
       </c>
-      <c r="F461" s="25" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="462" customHeight="1" ht="30.0">
+    </row>
+    <row r="462" customHeight="1" ht="15.0">
       <c r="A462" s="78"/>
       <c r="B462" s="79"/>
-      <c r="C462" s="80"/>
-      <c r="D462" s="81"/>
+      <c r="C462" s="12"/>
+      <c r="D462" s="52"/>
       <c r="E462" s="77" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F462" s="25" t="s">
         <v>1009</v>
       </c>
-      <c r="F462" s="25" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="463" customHeight="1" ht="77.0">
+    </row>
+    <row r="463" customHeight="1" ht="15.0">
       <c r="A463" s="78"/>
       <c r="B463" s="79"/>
-      <c r="C463" s="83" t="s">
-        <v>73</v>
-      </c>
-      <c r="D463" s="84"/>
+      <c r="C463" s="12"/>
+      <c r="D463" s="52"/>
       <c r="E463" s="77" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F463" s="25" t="s">
         <v>1011</v>
       </c>
-      <c r="F463" s="25" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="464" customHeight="1" ht="117.0">
+    </row>
+    <row r="464" customHeight="1" ht="15.0">
       <c r="A464" s="78"/>
       <c r="B464" s="79"/>
-      <c r="C464" s="81"/>
-      <c r="D464" s="84"/>
+      <c r="C464" s="12"/>
+      <c r="D464" s="52"/>
       <c r="E464" s="77" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F464" s="25" t="s">
         <v>1013</v>
       </c>
-      <c r="F464" s="25" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="465" customHeight="1" ht="150.0">
+    </row>
+    <row r="465" customHeight="1" ht="15.0">
       <c r="A465" s="78"/>
       <c r="B465" s="79"/>
-      <c r="C465" s="81"/>
-      <c r="D465" s="84"/>
+      <c r="C465" s="12"/>
+      <c r="D465" s="52"/>
       <c r="E465" s="77" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F465" s="25" t="s">
         <v>1015</v>
       </c>
-      <c r="F465" s="25" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="466" customHeight="1" ht="40.0">
+    </row>
+    <row r="466" customHeight="1" ht="15.0">
       <c r="A466" s="78"/>
       <c r="B466" s="79"/>
-      <c r="C466" s="81"/>
-      <c r="D466" s="84"/>
+      <c r="C466" s="12"/>
+      <c r="D466" s="52"/>
       <c r="E466" s="77" t="s">
-        <v>1017</v>
+        <v>436</v>
       </c>
       <c r="F466" s="25" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="467" customHeight="1" ht="15.0">
       <c r="A467" s="78"/>
       <c r="B467" s="79"/>
-      <c r="C467" s="81"/>
-      <c r="D467" s="84"/>
+      <c r="C467" s="12"/>
+      <c r="D467" s="52"/>
       <c r="E467" s="77" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="F467" s="25" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="468" customHeight="1" ht="15.0">
       <c r="A468" s="78"/>
       <c r="B468" s="79"/>
-      <c r="C468" s="81"/>
-      <c r="D468" s="84"/>
+      <c r="C468" s="12"/>
+      <c r="D468" s="52"/>
       <c r="E468" s="77" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="F468" s="25" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="469" customHeight="1" ht="15.0">
       <c r="A469" s="78"/>
       <c r="B469" s="79"/>
-      <c r="C469" s="85"/>
-      <c r="D469" s="86"/>
+      <c r="C469" s="12"/>
+      <c r="D469" s="52"/>
       <c r="E469" s="77" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="F469" s="25" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="470" customHeight="1" ht="64.0">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="470" customHeight="1" ht="15.0">
       <c r="A470" s="78"/>
       <c r="B470" s="79"/>
-      <c r="C470" s="79"/>
-      <c r="D470" s="87"/>
+      <c r="C470" s="12"/>
+      <c r="D470" s="52"/>
       <c r="E470" s="77" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="F470" s="25" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="471" customHeight="1" ht="53.0">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="471" customHeight="1" ht="30.0">
       <c r="A471" s="78"/>
       <c r="B471" s="79"/>
-      <c r="C471" s="88"/>
-      <c r="D471" s="89" t="s">
-        <v>1027</v>
-      </c>
+      <c r="C471" s="12"/>
+      <c r="D471" s="52"/>
       <c r="E471" s="77" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="F471" s="25" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="472" customHeight="1" ht="53.0">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="472" customHeight="1" ht="77.0">
       <c r="A472" s="78"/>
       <c r="B472" s="79"/>
-      <c r="C472" s="88"/>
-      <c r="D472" s="90"/>
+      <c r="C472" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="D472" s="81"/>
       <c r="E472" s="77" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="F472" s="25" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="473" customHeight="1" ht="63.0">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="473" customHeight="1" ht="117.0">
       <c r="A473" s="78"/>
       <c r="B473" s="79"/>
-      <c r="C473" s="88"/>
-      <c r="D473" s="90"/>
+      <c r="C473" s="52"/>
+      <c r="D473" s="81"/>
       <c r="E473" s="77" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="F473" s="25" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="474" customHeight="1" ht="53.0">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="474" customHeight="1" ht="150.0">
       <c r="A474" s="78"/>
       <c r="B474" s="79"/>
-      <c r="C474" s="88"/>
-      <c r="D474" s="90"/>
+      <c r="C474" s="52"/>
+      <c r="D474" s="81"/>
       <c r="E474" s="77" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="F474" s="25" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="475" customHeight="1" ht="60.0">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="475" customHeight="1" ht="40.0">
       <c r="A475" s="78"/>
       <c r="B475" s="79"/>
-      <c r="C475" s="88"/>
-      <c r="D475" s="90"/>
+      <c r="C475" s="52"/>
+      <c r="D475" s="81"/>
       <c r="E475" s="77" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F475" s="25" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="476" customHeight="1" ht="94.0">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="476" customHeight="1" ht="15.0">
       <c r="A476" s="78"/>
       <c r="B476" s="79"/>
-      <c r="C476" s="88"/>
-      <c r="D476" s="90"/>
+      <c r="C476" s="52"/>
+      <c r="D476" s="81"/>
       <c r="E476" s="77" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="F476" s="25" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="477" customHeight="1" ht="24.0">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="477" customHeight="1" ht="15.0">
       <c r="A477" s="78"/>
       <c r="B477" s="79"/>
-      <c r="C477" s="88"/>
-      <c r="D477" s="90"/>
+      <c r="C477" s="52"/>
+      <c r="D477" s="81"/>
       <c r="E477" s="77" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F477" s="25" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="478" customHeight="1" ht="15.0">
+      <c r="A478" s="78"/>
+      <c r="B478" s="79"/>
+      <c r="C478" s="53"/>
+      <c r="D478" s="82"/>
+      <c r="E478" s="77" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F478" s="25" t="s">
         <v>1040</v>
       </c>
-      <c r="F477" s="25" t="s">
+    </row>
+    <row r="479" customHeight="1" ht="64.0">
+      <c r="A479" s="78"/>
+      <c r="B479" s="79"/>
+      <c r="C479" s="79"/>
+      <c r="D479" s="83"/>
+      <c r="E479" s="77" t="s">
         <v>1041</v>
       </c>
-    </row>
-    <row r="478" customHeight="1" ht="38.0">
-      <c r="A478" s="91"/>
-      <c r="B478" s="92"/>
-      <c r="C478" s="88"/>
-      <c r="D478" s="90"/>
-      <c r="E478" s="77" t="s">
+      <c r="F479" s="25" t="s">
         <v>1042</v>
       </c>
-      <c r="F478" s="25" t="s">
+    </row>
+    <row r="480" customHeight="1" ht="53.0">
+      <c r="A480" s="78"/>
+      <c r="B480" s="79"/>
+      <c r="C480" s="84"/>
+      <c r="D480" s="85" t="s">
         <v>1043</v>
       </c>
-    </row>
-    <row r="479" customHeight="1" ht="113.0">
-      <c r="A479" s="93">
+      <c r="E480" s="77" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F480" s="25" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="481" customHeight="1" ht="53.0">
+      <c r="A481" s="78"/>
+      <c r="B481" s="79"/>
+      <c r="C481" s="84"/>
+      <c r="D481" s="86"/>
+      <c r="E481" s="77" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F481" s="25" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="482" customHeight="1" ht="63.0">
+      <c r="A482" s="78"/>
+      <c r="B482" s="79"/>
+      <c r="C482" s="84"/>
+      <c r="D482" s="86"/>
+      <c r="E482" s="77" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F482" s="25" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="483" customHeight="1" ht="53.0">
+      <c r="A483" s="78"/>
+      <c r="B483" s="79"/>
+      <c r="C483" s="84"/>
+      <c r="D483" s="86"/>
+      <c r="E483" s="77" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F483" s="25" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="484" customHeight="1" ht="60.0">
+      <c r="A484" s="78"/>
+      <c r="B484" s="79"/>
+      <c r="C484" s="84"/>
+      <c r="D484" s="86"/>
+      <c r="E484" s="77" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F484" s="25" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="485" customHeight="1" ht="94.0">
+      <c r="A485" s="78"/>
+      <c r="B485" s="79"/>
+      <c r="C485" s="84"/>
+      <c r="D485" s="86"/>
+      <c r="E485" s="77" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F485" s="25" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="486" customHeight="1" ht="24.0">
+      <c r="A486" s="78"/>
+      <c r="B486" s="79"/>
+      <c r="C486" s="84"/>
+      <c r="D486" s="86"/>
+      <c r="E486" s="77" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F486" s="25" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="487" customHeight="1" ht="38.0">
+      <c r="A487" s="87"/>
+      <c r="B487" s="88"/>
+      <c r="C487" s="84"/>
+      <c r="D487" s="86"/>
+      <c r="E487" s="77" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F487" s="25" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="488" customHeight="1" ht="113.0">
+      <c r="A488" s="89">
         <v>38.0</v>
       </c>
-      <c r="B479" s="77"/>
-      <c r="C479" s="25"/>
-      <c r="D479" s="25"/>
-      <c r="E479" s="25" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F479" s="25" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="480" customHeight="1" ht="24.0">
-      <c r="A480" s="94"/>
-      <c r="B480" s="77"/>
-      <c r="C480" s="25"/>
-      <c r="D480" s="25"/>
-      <c r="E480" s="25" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F480" s="25" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="481" customHeight="1" ht="40.0">
-      <c r="A481" s="94"/>
-      <c r="B481" s="77"/>
-      <c r="C481" s="25"/>
-      <c r="D481" s="25"/>
-      <c r="E481" s="25" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F481" s="25" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="482" customHeight="1" ht="28.0">
-      <c r="A482" s="94"/>
-      <c r="B482" s="77"/>
-      <c r="C482" s="25"/>
-      <c r="D482" s="25"/>
-      <c r="E482" s="25" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F482" s="25" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="483" customHeight="1" ht="68.0">
-      <c r="A483" s="94"/>
-      <c r="B483" s="77"/>
-      <c r="C483" s="25"/>
-      <c r="D483" s="25"/>
-      <c r="E483" s="25" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F483" s="25" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="484" customHeight="1" ht="15.0">
-      <c r="A484" s="94"/>
-      <c r="B484" s="77"/>
-      <c r="C484" s="25"/>
-      <c r="D484" s="25"/>
-      <c r="E484" s="25" t="s">
-        <v>1054</v>
-      </c>
-      <c r="F484" s="25" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="485" customHeight="1" ht="40.0">
-      <c r="A485" s="94"/>
-      <c r="B485" s="95">
-        <v>46109</v>
-      </c>
-      <c r="C485" s="76" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D485" s="25"/>
-      <c r="E485" s="25" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F485" s="25" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="486" customHeight="1" ht="29.0">
-      <c r="A486" s="94"/>
-      <c r="B486" s="94"/>
-      <c r="C486" s="80"/>
-      <c r="D486" s="25"/>
-      <c r="E486" s="25" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F486" s="25" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="487" customHeight="1" ht="15.0">
-      <c r="A487" s="94"/>
-      <c r="B487" s="94"/>
-      <c r="C487" s="80"/>
-      <c r="D487" s="25"/>
-      <c r="E487" s="25" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F487" s="25" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="488" customHeight="1" ht="15.0">
-      <c r="A488" s="94"/>
-      <c r="B488" s="94"/>
-      <c r="C488" s="80"/>
+      <c r="B488" s="77"/>
+      <c r="C488" s="25"/>
       <c r="D488" s="25"/>
       <c r="E488" s="25" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="F488" s="25" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="489" customHeight="1" ht="15.0">
-      <c r="A489" s="94"/>
-      <c r="B489" s="94"/>
-      <c r="C489" s="80"/>
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="489" customHeight="1" ht="24.0">
+      <c r="A489" s="90"/>
+      <c r="B489" s="77"/>
+      <c r="C489" s="25"/>
       <c r="D489" s="25"/>
       <c r="E489" s="25" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="F489" s="25" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="490" customHeight="1" ht="15.0">
-      <c r="A490" s="94"/>
-      <c r="B490" s="94"/>
-      <c r="C490" s="80"/>
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="490" customHeight="1" ht="40.0">
+      <c r="A490" s="90"/>
+      <c r="B490" s="77"/>
+      <c r="C490" s="25"/>
       <c r="D490" s="25"/>
       <c r="E490" s="25" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="F490" s="25" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="491" customHeight="1" ht="151.0">
-      <c r="A491" s="94"/>
-      <c r="B491" s="94"/>
-      <c r="C491" s="80"/>
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="491" customHeight="1" ht="28.0">
+      <c r="A491" s="90"/>
+      <c r="B491" s="77"/>
+      <c r="C491" s="25"/>
       <c r="D491" s="25"/>
       <c r="E491" s="25" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F491" s="25" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="492" customHeight="1" ht="84.0">
-      <c r="A492" s="94"/>
-      <c r="B492" s="94"/>
-      <c r="C492" s="80"/>
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="492" customHeight="1" ht="68.0">
+      <c r="A492" s="90"/>
+      <c r="B492" s="77"/>
+      <c r="C492" s="25"/>
       <c r="D492" s="25"/>
       <c r="E492" s="25" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F492" s="25" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="493" customHeight="1" ht="15.0">
+      <c r="A493" s="90"/>
+      <c r="B493" s="77"/>
+      <c r="C493" s="25"/>
+      <c r="D493" s="25"/>
+      <c r="E493" s="25" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F493" s="25" t="s">
         <v>1071</v>
       </c>
-      <c r="F492" s="25" t="s">
+    </row>
+    <row r="494" customHeight="1" ht="40.0">
+      <c r="A494" s="90"/>
+      <c r="B494" s="91">
+        <v>46109.0</v>
+      </c>
+      <c r="C494" s="76" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="493" customHeight="1" ht="15.0">
-      <c r="A493" s="94"/>
-      <c r="B493" s="94"/>
-      <c r="C493" s="80"/>
-      <c r="D493" s="25"/>
-      <c r="E493" s="25"/>
-      <c r="F493" s="25"/>
-    </row>
-    <row r="494" customHeight="1" ht="15.0">
-      <c r="A494" s="94"/>
-      <c r="B494" s="94"/>
-      <c r="C494" s="80"/>
       <c r="D494" s="25"/>
-      <c r="E494" s="25"/>
-      <c r="F494" s="25"/>
-    </row>
-    <row r="495" customHeight="1" ht="15.0">
-      <c r="A495" s="94"/>
-      <c r="B495" s="94"/>
-      <c r="C495" s="80"/>
+      <c r="E494" s="25" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F494" s="25" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="495" customHeight="1" ht="29.0">
+      <c r="A495" s="90"/>
+      <c r="B495" s="90"/>
+      <c r="C495" s="12"/>
       <c r="D495" s="25"/>
-      <c r="E495" s="25"/>
-      <c r="F495" s="25"/>
+      <c r="E495" s="25" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F495" s="25" t="s">
+        <v>1076</v>
+      </c>
     </row>
     <row r="496" customHeight="1" ht="15.0">
-      <c r="A496" s="94"/>
-      <c r="B496" s="94"/>
-      <c r="C496" s="80"/>
+      <c r="A496" s="90"/>
+      <c r="B496" s="90"/>
+      <c r="C496" s="12"/>
       <c r="D496" s="25"/>
-      <c r="E496" s="25"/>
-      <c r="F496" s="25"/>
+      <c r="E496" s="25" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F496" s="25" t="s">
+        <v>1078</v>
+      </c>
     </row>
     <row r="497" customHeight="1" ht="15.0">
-      <c r="A497" s="96"/>
-      <c r="B497" s="96"/>
-      <c r="C497" s="97"/>
+      <c r="A497" s="90"/>
+      <c r="B497" s="90"/>
+      <c r="C497" s="12"/>
       <c r="D497" s="25"/>
-      <c r="E497" s="25"/>
-      <c r="F497" s="25"/>
+      <c r="E497" s="25" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F497" s="25" t="s">
+        <v>1080</v>
+      </c>
     </row>
     <row r="498" customHeight="1" ht="15.0">
-      <c r="A498" s="77"/>
-      <c r="B498" s="77"/>
-      <c r="C498" s="25"/>
+      <c r="A498" s="90"/>
+      <c r="B498" s="90"/>
+      <c r="C498" s="12"/>
       <c r="D498" s="25"/>
-      <c r="E498" s="25"/>
-      <c r="F498" s="25"/>
+      <c r="E498" s="25" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F498" s="25" t="s">
+        <v>1082</v>
+      </c>
     </row>
     <row r="499" customHeight="1" ht="15.0">
-      <c r="A499" s="77"/>
-      <c r="B499" s="77"/>
-      <c r="C499" s="25"/>
+      <c r="A499" s="90"/>
+      <c r="B499" s="90"/>
+      <c r="C499" s="12"/>
       <c r="D499" s="25"/>
-      <c r="E499" s="25"/>
-      <c r="F499" s="25"/>
+      <c r="E499" s="25" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F499" s="25" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="500" customHeight="1" ht="151.0">
+      <c r="A500" s="90"/>
+      <c r="B500" s="90"/>
+      <c r="C500" s="12"/>
+      <c r="D500" s="25"/>
+      <c r="E500" s="25" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F500" s="25" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="501" customHeight="1" ht="84.0">
+      <c r="A501" s="90"/>
+      <c r="B501" s="90"/>
+      <c r="C501" s="12"/>
+      <c r="D501" s="54"/>
+      <c r="E501" s="25" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F501" s="25" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="502" customHeight="1" ht="15.0">
+      <c r="A502" s="90"/>
+      <c r="B502" s="92">
+        <v>46111</v>
+      </c>
+      <c r="C502" s="92" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E502" s="77" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F502" s="25" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="503" customHeight="1" ht="15.0">
+      <c r="A503" s="90"/>
+      <c r="B503" s="92"/>
+      <c r="C503" s="92"/>
+      <c r="D503" s="93" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E503" s="25" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F503" s="25" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="504" customHeight="1" ht="15.0">
+      <c r="A504" s="90"/>
+      <c r="B504" s="92"/>
+      <c r="C504" s="92"/>
+      <c r="D504" s="94"/>
+      <c r="E504" s="54" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F504" s="54" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="505" customHeight="1" ht="15.0">
+      <c r="A505" s="90"/>
+      <c r="B505" s="92"/>
+      <c r="C505" s="92"/>
+      <c r="D505" s="94"/>
+      <c r="G505" s="95"/>
+    </row>
+    <row r="506" customHeight="1" ht="15.0">
+      <c r="A506" s="96"/>
+      <c r="B506" s="92"/>
+      <c r="C506" s="92"/>
+      <c r="D506" s="94"/>
+      <c r="E506" s="50" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F506" s="50" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="507" customHeight="1" ht="15.0">
+      <c r="A507" s="77"/>
+      <c r="B507" s="92"/>
+      <c r="C507" s="92"/>
+      <c r="D507" s="94"/>
+      <c r="E507" s="25" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F507" s="25" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="508" customHeight="1" ht="15.0">
+      <c r="A508" s="77"/>
+      <c r="B508" s="92"/>
+      <c r="C508" s="92"/>
+      <c r="D508" s="94"/>
+      <c r="E508" s="25" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F508" s="25" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="509" customHeight="1" ht="15.0">
+      <c r="A509" s="97">
+        <v>39.0</v>
+      </c>
+      <c r="B509" s="92"/>
+      <c r="C509" s="92"/>
+      <c r="D509" s="94"/>
+      <c r="E509" s="25" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F509" s="25" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="510" customHeight="1" ht="15.0">
+      <c r="A510" s="98"/>
+      <c r="B510" s="92"/>
+      <c r="C510" s="92"/>
+      <c r="D510" s="94"/>
+      <c r="E510" s="25" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F510" s="25" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="511" customHeight="1" ht="15.0">
+      <c r="A511" s="98"/>
+      <c r="B511" s="92"/>
+      <c r="C511" s="92"/>
+      <c r="D511" s="94"/>
+      <c r="E511" s="25" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F511" s="25" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="512" customHeight="1" ht="15.0">
+      <c r="A512" s="98"/>
+      <c r="B512" s="92"/>
+      <c r="C512" s="92"/>
+      <c r="D512" s="99"/>
+      <c r="E512" s="25" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F512" s="25" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G512" s="95"/>
+    </row>
+    <row r="513" customHeight="1" ht="15.0">
+      <c r="A513" s="98"/>
+      <c r="B513" s="92"/>
+      <c r="C513" s="92"/>
+      <c r="D513" s="76" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E513" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F513" s="25" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G513" s="95"/>
+      <c r="H513" s="95"/>
+    </row>
+    <row r="514" customHeight="1" ht="15.0">
+      <c r="A514" s="98"/>
+      <c r="B514" s="92"/>
+      <c r="C514" s="92"/>
+      <c r="D514" s="100"/>
+      <c r="E514" s="25" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F514" s="25" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G514" s="95"/>
+    </row>
+    <row r="515" customHeight="1" ht="15.0">
+      <c r="A515" s="98"/>
+      <c r="B515" s="92"/>
+      <c r="C515" s="92"/>
+      <c r="D515" s="100"/>
+      <c r="E515" s="25" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F515" s="25" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="516" customHeight="1" ht="15.0">
+      <c r="A516" s="98"/>
+      <c r="B516" s="92"/>
+      <c r="C516" s="92"/>
+      <c r="D516" s="100"/>
+      <c r="E516" s="25" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F516" s="25" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="517" customHeight="1" ht="15.0">
+      <c r="A517" s="98"/>
+      <c r="B517" s="92"/>
+      <c r="C517" s="92"/>
+      <c r="D517" s="100"/>
+      <c r="E517" s="25" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F517" s="25" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="518" customHeight="1" ht="15.0">
+      <c r="A518" s="98"/>
+      <c r="B518" s="92"/>
+      <c r="C518" s="92"/>
+      <c r="D518" s="100"/>
+      <c r="E518" s="25" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F518" s="25" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="519" customHeight="1" ht="15.0">
+      <c r="A519" s="98"/>
+      <c r="B519" s="92"/>
+      <c r="C519" s="92"/>
+      <c r="D519" s="100"/>
+      <c r="E519" s="25" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F519" s="25" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="520" customHeight="1" ht="15.0">
+      <c r="A520" s="98"/>
+      <c r="B520" s="92"/>
+      <c r="C520" s="92"/>
+      <c r="D520" s="101"/>
+      <c r="E520" s="25" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F520" s="25" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="521" customHeight="1" ht="15.0">
+      <c r="A521" s="98"/>
+      <c r="B521" s="92"/>
+      <c r="C521" s="92"/>
+      <c r="D521" s="76" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E521" s="25" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F521" s="25" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="522" customHeight="1" ht="15.0">
+      <c r="A522" s="98"/>
+      <c r="B522" s="92"/>
+      <c r="C522" s="92"/>
+      <c r="D522" s="100"/>
+      <c r="E522" s="25" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F522" s="25" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="523" customHeight="1" ht="15.0">
+      <c r="A523" s="98"/>
+      <c r="B523" s="92"/>
+      <c r="C523" s="92"/>
+      <c r="D523" s="100"/>
+      <c r="E523" s="25" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F523" s="25" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="524" customHeight="1" ht="15.0">
+      <c r="A524" s="98"/>
+      <c r="B524" s="92"/>
+      <c r="C524" s="92"/>
+      <c r="D524" s="100"/>
+      <c r="E524" s="25" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F524" s="25" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="525" customHeight="1" ht="15.0">
+      <c r="A525" s="98"/>
+      <c r="B525" s="92"/>
+      <c r="C525" s="92"/>
+      <c r="D525" s="100"/>
+      <c r="E525" s="25" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F525" s="25" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="526" customHeight="1" ht="15.0">
+      <c r="A526" s="98"/>
+      <c r="B526" s="92"/>
+      <c r="C526" s="92"/>
+      <c r="D526" s="101"/>
+      <c r="E526" s="25" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F526" s="25" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="527" customHeight="1" ht="15.0">
+      <c r="A527" s="98"/>
+      <c r="B527" s="92"/>
+      <c r="C527" s="92"/>
+      <c r="D527" s="76" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E527" s="25" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F527" s="25" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="528" customHeight="1" ht="15.0">
+      <c r="A528" s="98"/>
+      <c r="B528" s="92"/>
+      <c r="C528" s="92"/>
+      <c r="D528" s="100"/>
+      <c r="E528" s="25" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F528" s="25" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="529" customHeight="1" ht="15.0">
+      <c r="A529" s="98"/>
+      <c r="B529" s="92"/>
+      <c r="C529" s="92"/>
+      <c r="D529" s="100"/>
+      <c r="E529" s="25" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F529" s="25" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="530" customHeight="1" ht="15.0">
+      <c r="A530" s="98"/>
+      <c r="B530" s="92"/>
+      <c r="C530" s="92"/>
+      <c r="D530" s="100"/>
+      <c r="E530" s="25" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F530" s="25" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="531" customHeight="1" ht="15.0">
+      <c r="A531" s="98"/>
+      <c r="B531" s="92"/>
+      <c r="C531" s="92"/>
+      <c r="D531" s="101"/>
+      <c r="E531" s="25" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F531" s="25" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="532" customHeight="1" ht="15.0">
+      <c r="A532" s="98"/>
+      <c r="B532" s="92"/>
+      <c r="C532" s="92"/>
+      <c r="D532" s="76" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E532" s="25" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F532" s="25" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="533" customHeight="1" ht="15.0">
+      <c r="A533" s="98"/>
+      <c r="B533" s="92"/>
+      <c r="C533" s="92"/>
+      <c r="D533" s="100"/>
+      <c r="E533" s="25" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F533" s="25" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="534" customHeight="1" ht="15.0">
+      <c r="A534" s="98"/>
+      <c r="B534" s="92"/>
+      <c r="C534" s="92"/>
+      <c r="D534" s="100"/>
+      <c r="E534" s="25" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F534" s="25" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="535" customHeight="1" ht="15.0">
+      <c r="A535" s="98"/>
+      <c r="B535" s="92"/>
+      <c r="C535" s="92"/>
+      <c r="D535" s="101"/>
+      <c r="E535" s="25" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F535" s="25" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="536" customHeight="1" ht="15.0">
+      <c r="B536" s="92"/>
+      <c r="C536" s="92"/>
+      <c r="D536" s="76" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E536" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F536" s="25" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="537" customHeight="1" ht="15.0">
+      <c r="B537" s="92"/>
+      <c r="C537" s="92"/>
+      <c r="D537" s="100"/>
+      <c r="E537" s="25" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F537" s="25" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="538" customHeight="1" ht="15.0">
+      <c r="D538" s="100"/>
+      <c r="E538" s="25" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F538" s="25" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="539" customHeight="1" ht="15.0">
+      <c r="D539" s="101"/>
+      <c r="E539" s="25"/>
+      <c r="F539" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="151">
+  <mergeCells count="160">
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="D127:D130"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:A15"/>
+    <mergeCell ref="A16:A26"/>
+    <mergeCell ref="B62:B70"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="C71:C82"/>
     <mergeCell ref="A32:A57"/>
-    <mergeCell ref="C71:C82"/>
-    <mergeCell ref="A16:A26"/>
+    <mergeCell ref="C83:C112"/>
     <mergeCell ref="D113:D125"/>
-    <mergeCell ref="C83:C112"/>
-    <mergeCell ref="B62:B70"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="A3:A15"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D127:D130"/>
     <mergeCell ref="A62:A70"/>
     <mergeCell ref="B16:B26"/>
+    <mergeCell ref="B3:B15"/>
     <mergeCell ref="C113:C125"/>
     <mergeCell ref="C127:C130"/>
     <mergeCell ref="D71:D82"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="B3:B15"/>
     <mergeCell ref="D83:D112"/>
     <mergeCell ref="B27:B31"/>
     <mergeCell ref="B32:B57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="D62:D70"/>
+    <mergeCell ref="A71:A82"/>
     <mergeCell ref="D58:D61"/>
-    <mergeCell ref="A71:A82"/>
     <mergeCell ref="B127:B130"/>
+    <mergeCell ref="B113:B125"/>
+    <mergeCell ref="C3:C15"/>
+    <mergeCell ref="C16:C26"/>
     <mergeCell ref="C27:C31"/>
     <mergeCell ref="C32:C57"/>
-    <mergeCell ref="C16:C26"/>
-    <mergeCell ref="C3:C15"/>
-    <mergeCell ref="B113:B125"/>
-    <mergeCell ref="D62:D70"/>
     <mergeCell ref="A83:A112"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="B83:B112"/>
+    <mergeCell ref="A113:A125"/>
     <mergeCell ref="C62:C70"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="B71:B82"/>
-    <mergeCell ref="B83:B112"/>
-    <mergeCell ref="D16:D26"/>
-    <mergeCell ref="D3:D15"/>
-    <mergeCell ref="A113:A125"/>
+    <mergeCell ref="A127:A130"/>
     <mergeCell ref="D27:D31"/>
     <mergeCell ref="D32:D57"/>
-    <mergeCell ref="A127:A130"/>
+    <mergeCell ref="B71:B82"/>
+    <mergeCell ref="D3:D15"/>
+    <mergeCell ref="D16:D26"/>
+    <mergeCell ref="A155:A168"/>
     <mergeCell ref="B175:B188"/>
+    <mergeCell ref="B169:B174"/>
+    <mergeCell ref="A142:A148"/>
     <mergeCell ref="A134:A141"/>
     <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A142:A148"/>
     <mergeCell ref="A149:A154"/>
+    <mergeCell ref="B189:B216"/>
+    <mergeCell ref="D226:D230"/>
+    <mergeCell ref="C217:C225"/>
     <mergeCell ref="D231:D243"/>
-    <mergeCell ref="A155:A168"/>
-    <mergeCell ref="B169:B174"/>
-    <mergeCell ref="D244:D251"/>
-    <mergeCell ref="D252:D254"/>
-    <mergeCell ref="D255:D265"/>
-    <mergeCell ref="B189:B216"/>
-    <mergeCell ref="C217:C225"/>
-    <mergeCell ref="D226:D230"/>
+    <mergeCell ref="D244:D253"/>
+    <mergeCell ref="D254:D256"/>
     <mergeCell ref="D217:D225"/>
-    <mergeCell ref="C231:C243"/>
     <mergeCell ref="A169:A174"/>
-    <mergeCell ref="B155:B168"/>
     <mergeCell ref="A175:A188"/>
     <mergeCell ref="A189:A216"/>
-    <mergeCell ref="C244:C251"/>
-    <mergeCell ref="B149:B154"/>
-    <mergeCell ref="C252:C254"/>
-    <mergeCell ref="C255:C265"/>
+    <mergeCell ref="C254:C256"/>
     <mergeCell ref="B142:B148"/>
     <mergeCell ref="B131:B133"/>
     <mergeCell ref="B134:B141"/>
+    <mergeCell ref="B149:B154"/>
+    <mergeCell ref="B155:B168"/>
+    <mergeCell ref="C231:C243"/>
     <mergeCell ref="C226:C230"/>
+    <mergeCell ref="C244:C253"/>
     <mergeCell ref="D169:D174"/>
+    <mergeCell ref="A217:A225"/>
     <mergeCell ref="C155:C168"/>
+    <mergeCell ref="B231:B243"/>
+    <mergeCell ref="B244:B253"/>
+    <mergeCell ref="B254:B256"/>
+    <mergeCell ref="B226:B230"/>
+    <mergeCell ref="C142:C148"/>
     <mergeCell ref="C149:C154"/>
-    <mergeCell ref="C142:C148"/>
     <mergeCell ref="C131:C133"/>
     <mergeCell ref="C134:C141"/>
-    <mergeCell ref="B226:B230"/>
-    <mergeCell ref="A217:A225"/>
     <mergeCell ref="D189:D216"/>
     <mergeCell ref="D175:D188"/>
-    <mergeCell ref="B252:B254"/>
-    <mergeCell ref="B255:B265"/>
-    <mergeCell ref="B244:B251"/>
-    <mergeCell ref="B231:B243"/>
     <mergeCell ref="C169:C174"/>
-    <mergeCell ref="B217:B225"/>
-    <mergeCell ref="A226:A230"/>
-    <mergeCell ref="A231:A243"/>
-    <mergeCell ref="A255:A265"/>
-    <mergeCell ref="A252:A254"/>
-    <mergeCell ref="A244:A251"/>
+    <mergeCell ref="D149:D154"/>
     <mergeCell ref="D134:D141"/>
-    <mergeCell ref="C175:C188"/>
-    <mergeCell ref="C189:C216"/>
-    <mergeCell ref="D131:D133"/>
     <mergeCell ref="D155:D168"/>
     <mergeCell ref="D142:D148"/>
-    <mergeCell ref="D149:D154"/>
-    <mergeCell ref="D357:D374"/>
-    <mergeCell ref="D375:D396"/>
-    <mergeCell ref="B320:B348"/>
-    <mergeCell ref="C349:C356"/>
-    <mergeCell ref="A266:A271"/>
-    <mergeCell ref="A272:A284"/>
-    <mergeCell ref="B307:B319"/>
-    <mergeCell ref="A285:A306"/>
-    <mergeCell ref="C357:C374"/>
-    <mergeCell ref="B285:B306"/>
-    <mergeCell ref="A320:A348"/>
-    <mergeCell ref="A307:A319"/>
-    <mergeCell ref="B266:B271"/>
-    <mergeCell ref="D349:D356"/>
-    <mergeCell ref="C375:C422"/>
-    <mergeCell ref="B272:B284"/>
-    <mergeCell ref="B375:B396"/>
-    <mergeCell ref="D307:D319"/>
-    <mergeCell ref="C285:C306"/>
-    <mergeCell ref="B357:B374"/>
-    <mergeCell ref="C266:C271"/>
-    <mergeCell ref="A349:A356"/>
-    <mergeCell ref="C272:C284"/>
-    <mergeCell ref="D320:D348"/>
-    <mergeCell ref="D266:D271"/>
-    <mergeCell ref="C320:C348"/>
-    <mergeCell ref="D272:D284"/>
-    <mergeCell ref="B349:B356"/>
-    <mergeCell ref="D285:D306"/>
-    <mergeCell ref="C307:C319"/>
-    <mergeCell ref="A357:A374"/>
-    <mergeCell ref="A375:A396"/>
-    <mergeCell ref="B424:B438"/>
-    <mergeCell ref="C470:C478"/>
-    <mergeCell ref="E266:E271"/>
-    <mergeCell ref="C463:C469"/>
-    <mergeCell ref="A409:A422"/>
-    <mergeCell ref="A397:A408"/>
-    <mergeCell ref="B439:B478"/>
-    <mergeCell ref="B397:B408"/>
-    <mergeCell ref="B409:B422"/>
-    <mergeCell ref="A424:A438"/>
-    <mergeCell ref="C485:C497"/>
-    <mergeCell ref="D471:D478"/>
-    <mergeCell ref="A439:A478"/>
-    <mergeCell ref="A479:A497"/>
-    <mergeCell ref="B485:B497"/>
-    <mergeCell ref="D439:D469"/>
-    <mergeCell ref="D424:D438"/>
-    <mergeCell ref="C424:C438"/>
-    <mergeCell ref="D406:D408"/>
-    <mergeCell ref="C439:C462"/>
-    <mergeCell ref="D397:D405"/>
-    <mergeCell ref="D409:D422"/>
+    <mergeCell ref="D131:D133"/>
+    <mergeCell ref="A226:A230"/>
+    <mergeCell ref="B217:B225"/>
+    <mergeCell ref="C189:C216"/>
+    <mergeCell ref="C175:C188"/>
+    <mergeCell ref="A231:A243"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="A244:A253"/>
+    <mergeCell ref="A287:A308"/>
+    <mergeCell ref="D356:D365"/>
+    <mergeCell ref="A257:A267"/>
+    <mergeCell ref="D366:D383"/>
+    <mergeCell ref="C327:C355"/>
+    <mergeCell ref="A274:A286"/>
+    <mergeCell ref="B309:B326"/>
+    <mergeCell ref="D384:D405"/>
+    <mergeCell ref="A268:A273"/>
+    <mergeCell ref="D327:D355"/>
+    <mergeCell ref="C366:C383"/>
+    <mergeCell ref="B257:B267"/>
+    <mergeCell ref="B274:B286"/>
+    <mergeCell ref="B268:B273"/>
+    <mergeCell ref="A309:A326"/>
+    <mergeCell ref="C384:C431"/>
+    <mergeCell ref="B287:B308"/>
+    <mergeCell ref="C356:C365"/>
+    <mergeCell ref="C274:C286"/>
+    <mergeCell ref="C257:C267"/>
+    <mergeCell ref="B356:B365"/>
+    <mergeCell ref="C268:C273"/>
+    <mergeCell ref="B384:B405"/>
+    <mergeCell ref="C287:C308"/>
+    <mergeCell ref="B366:B383"/>
+    <mergeCell ref="D309:D326"/>
+    <mergeCell ref="A327:A355"/>
+    <mergeCell ref="A356:A365"/>
+    <mergeCell ref="B327:B355"/>
+    <mergeCell ref="A366:A383"/>
+    <mergeCell ref="D274:D286"/>
+    <mergeCell ref="D287:D308"/>
+    <mergeCell ref="A384:A405"/>
+    <mergeCell ref="D257:D267"/>
+    <mergeCell ref="C309:C326"/>
+    <mergeCell ref="D268:D273"/>
+    <mergeCell ref="B448:B487"/>
+    <mergeCell ref="B418:B431"/>
+    <mergeCell ref="D503:D512"/>
+    <mergeCell ref="C479:C487"/>
+    <mergeCell ref="B433:B447"/>
+    <mergeCell ref="E268:E273"/>
+    <mergeCell ref="C472:C478"/>
+    <mergeCell ref="A406:A417"/>
+    <mergeCell ref="A418:A431"/>
+    <mergeCell ref="C494:C501"/>
+    <mergeCell ref="A433:A447"/>
+    <mergeCell ref="D480:D487"/>
+    <mergeCell ref="C502:C537"/>
+    <mergeCell ref="A448:A487"/>
+    <mergeCell ref="B406:B417"/>
+    <mergeCell ref="B502:B537"/>
+    <mergeCell ref="D448:D478"/>
+    <mergeCell ref="B494:B501"/>
+    <mergeCell ref="D433:D447"/>
+    <mergeCell ref="D418:D431"/>
+    <mergeCell ref="A509:A535"/>
+    <mergeCell ref="A488:A506"/>
+    <mergeCell ref="C433:C447"/>
+    <mergeCell ref="C448:C471"/>
+    <mergeCell ref="D415:D417"/>
+    <mergeCell ref="D406:D414"/>
+    <mergeCell ref="D532:D535"/>
+    <mergeCell ref="D521:D526"/>
+    <mergeCell ref="D527:D531"/>
+    <mergeCell ref="D513:D520"/>
+    <mergeCell ref="D536:D539"/>
   </mergeCells>
-  <conditionalFormatting sqref="F256:F256">
+  <conditionalFormatting sqref="F258:F258">
     <cfRule priority="1" type="colorScale">
       <colorScale>
         <cfvo type="min"/>
@@ -10825,7 +11696,8 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F408" r:id="rId1"/>
+    <hyperlink ref="F362" r:id="rId1"/>
+    <hyperlink ref="F417" r:id="rId2"/>
   </hyperlinks>
   <extLst/>
 </worksheet>
